--- a/label.xlsx
+++ b/label.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18288" windowHeight="9060" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="L0" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="L3" sheetId="4" r:id="rId5"/>
     <sheet name="L4" sheetId="5" r:id="rId6"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId7"/>
-    <sheet name="最小二乘法优化" sheetId="8" r:id="rId8"/>
+    <sheet name="球心降噪" sheetId="8" r:id="rId8"/>
+    <sheet name="旋转轴与速度" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -135,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
   <si>
     <t>序号</t>
   </si>
@@ -1445,11 +1446,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1457,6 +1455,12 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -5016,9 +5020,9 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>最小二乘法优化!$A$2:$A$19</c:f>
+              <c:f>球心降噪!$B$2:$B$19</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00_ </c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>884.558479532164</c:v>
@@ -5079,9 +5083,9 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>最小二乘法优化!$B$2:$B$19</c:f>
+              <c:f>球心降噪!$C$2:$C$19</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00_ </c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>517.09649122807</c:v>
@@ -5190,9 +5194,9 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>最小二乘法优化!$D$2:$D$19</c:f>
+              <c:f>球心降噪!$E$2:$E$19</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00_ </c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>884.556923951664</c:v>
@@ -5253,9 +5257,9 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>最小二乘法优化!$E$2:$E$19</c:f>
+              <c:f>球心降噪!$F$2:$F$19</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00_ </c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>517.094107579775</c:v>
@@ -5516,7 +5520,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5789,71 +5793,71 @@
           </c:dLbls>
           <c:xVal>
             <c:strRef>
-              <c:f>最小二乘法优化!$1:$18</c:f>
+              <c:f>球心降噪!$1:$18</c:f>
               <c:strCache>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>x0 y0 联合优化相较于原始点距离 x1 y1 分布优化相较于原始点距离</c:v>
+                  <c:v>序号 x0 y0 联合优化相较于原始点距离 x1 y1 分布优化相较于原始点距离</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>884.5584795 517.0964912 0.905399335 884.556924 517.0941076 0.907679136</c:v>
+                  <c:v>25 884.56 517.10 0.91 884.56 517.09 0.91</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>880.8195734 519.5361197 0.497733528 880.8182009 519.5340165 0.500191516</c:v>
+                  <c:v>45 880.82 519.54 0.50 880.82 519.53 0.50</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>877.0806674 521.9757482 0.420033353 877.0794778 521.9739254 0.421329813</c:v>
+                  <c:v>65 877.08 521.98 0.42 877.08 521.97 0.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>873.3417613 524.4153767 0.352082192 873.3407547 524.4138343 0.351480156</c:v>
+                  <c:v>85 873.34 524.42 0.35 873.34 524.41 0.35</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>869.6028552 526.8550052 0.369604993 869.6020316 526.8537432 0.368163994</c:v>
+                  <c:v>105 869.60 526.86 0.37 869.60 526.85 0.37</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>865.8639491 529.2946336 0.468260528 865.8633086 529.2936521 0.467145252</c:v>
+                  <c:v>125 865.86 529.29 0.47 865.86 529.29 0.47</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>862.125043 531.7342621 0.442121585 862.1245855 531.7335611 0.442138926</c:v>
+                  <c:v>145 862.13 531.73 0.44 862.12 531.73 0.44</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>858.3861369 534.1738906 0.683442284 858.3858624 534.17347 0.683073339</c:v>
+                  <c:v>165 858.39 534.17 0.68 858.39 534.17 0.68</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>854.6472308 536.6135191 0.185912612 854.6471393 536.6133789 0.185754538</c:v>
+                  <c:v>185 854.65 536.61 0.19 854.65 536.61 0.19</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>850.9083247 539.0531476 0.105967067 850.9084162 539.0532878 0.105958359</c:v>
+                  <c:v>205 850.91 539.05 0.11 850.91 539.05 0.11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>847.1694186 541.4927761 0.521086289 847.1696932 541.4931967 0.521573345</c:v>
+                  <c:v>225 847.17 541.49 0.52 847.17 541.49 0.52</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>843.4305126 543.9324045 0.610175997 843.4309701 543.9331056 0.610995648</c:v>
+                  <c:v>245 843.43 543.93 0.61 843.43 543.93 0.61</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>839.6916065 546.372033 0.483234045 839.692247 546.3730145 0.483582201</c:v>
+                  <c:v>265 839.69 546.37 0.48 839.69 546.37 0.48</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>835.9527004 548.8116615 0.194187132 835.9535239 548.8129234 0.192763238</c:v>
+                  <c:v>285 835.95 548.81 0.19 835.95 548.81 0.19</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>832.2137943 551.25129 0.327970528 832.2148008 551.2528324 0.327461828</c:v>
+                  <c:v>305 832.21 551.25 0.33 832.21 551.25 0.33</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>828.4748882 553.6909185 0.310099973 828.4760778 553.6927413 0.308188587</c:v>
+                  <c:v>325 828.47 553.69 0.31 828.48 553.69 0.31</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>824.7359821 556.130547 0.4540936 824.7373547 556.1326502 0.451584385</c:v>
+                  <c:v>345 824.74 556.13 0.45 824.74 556.13 0.45</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>最小二乘法优化!$C$2:$C$19</c:f>
+              <c:f>球心降噪!$D$2:$D$19</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00_ </c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.905399335451789</c:v>
@@ -5959,71 +5963,71 @@
           </c:dLbls>
           <c:xVal>
             <c:strRef>
-              <c:f>最小二乘法优化!$1:$18</c:f>
+              <c:f>球心降噪!$1:$18</c:f>
               <c:strCache>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>x0 y0 联合优化相较于原始点距离 x1 y1 分布优化相较于原始点距离</c:v>
+                  <c:v>序号 x0 y0 联合优化相较于原始点距离 x1 y1 分布优化相较于原始点距离</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>884.5584795 517.0964912 0.905399335 884.556924 517.0941076 0.907679136</c:v>
+                  <c:v>25 884.56 517.10 0.91 884.56 517.09 0.91</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>880.8195734 519.5361197 0.497733528 880.8182009 519.5340165 0.500191516</c:v>
+                  <c:v>45 880.82 519.54 0.50 880.82 519.53 0.50</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>877.0806674 521.9757482 0.420033353 877.0794778 521.9739254 0.421329813</c:v>
+                  <c:v>65 877.08 521.98 0.42 877.08 521.97 0.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>873.3417613 524.4153767 0.352082192 873.3407547 524.4138343 0.351480156</c:v>
+                  <c:v>85 873.34 524.42 0.35 873.34 524.41 0.35</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>869.6028552 526.8550052 0.369604993 869.6020316 526.8537432 0.368163994</c:v>
+                  <c:v>105 869.60 526.86 0.37 869.60 526.85 0.37</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>865.8639491 529.2946336 0.468260528 865.8633086 529.2936521 0.467145252</c:v>
+                  <c:v>125 865.86 529.29 0.47 865.86 529.29 0.47</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>862.125043 531.7342621 0.442121585 862.1245855 531.7335611 0.442138926</c:v>
+                  <c:v>145 862.13 531.73 0.44 862.12 531.73 0.44</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>858.3861369 534.1738906 0.683442284 858.3858624 534.17347 0.683073339</c:v>
+                  <c:v>165 858.39 534.17 0.68 858.39 534.17 0.68</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>854.6472308 536.6135191 0.185912612 854.6471393 536.6133789 0.185754538</c:v>
+                  <c:v>185 854.65 536.61 0.19 854.65 536.61 0.19</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>850.9083247 539.0531476 0.105967067 850.9084162 539.0532878 0.105958359</c:v>
+                  <c:v>205 850.91 539.05 0.11 850.91 539.05 0.11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>847.1694186 541.4927761 0.521086289 847.1696932 541.4931967 0.521573345</c:v>
+                  <c:v>225 847.17 541.49 0.52 847.17 541.49 0.52</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>843.4305126 543.9324045 0.610175997 843.4309701 543.9331056 0.610995648</c:v>
+                  <c:v>245 843.43 543.93 0.61 843.43 543.93 0.61</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>839.6916065 546.372033 0.483234045 839.692247 546.3730145 0.483582201</c:v>
+                  <c:v>265 839.69 546.37 0.48 839.69 546.37 0.48</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>835.9527004 548.8116615 0.194187132 835.9535239 548.8129234 0.192763238</c:v>
+                  <c:v>285 835.95 548.81 0.19 835.95 548.81 0.19</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>832.2137943 551.25129 0.327970528 832.2148008 551.2528324 0.327461828</c:v>
+                  <c:v>305 832.21 551.25 0.33 832.21 551.25 0.33</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>828.4748882 553.6909185 0.310099973 828.4760778 553.6927413 0.308188587</c:v>
+                  <c:v>325 828.47 553.69 0.31 828.48 553.69 0.31</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>824.7359821 556.130547 0.4540936 824.7373547 556.1326502 0.451584385</c:v>
+                  <c:v>345 824.74 556.13 0.45 824.74 556.13 0.45</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>最小二乘法优化!$F$2:$F$19</c:f>
+              <c:f>球心降噪!$G$2:$G$19</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00_ </c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0.907679135649873</c:v>
@@ -6245,7 +6249,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6368,6 +6372,572 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>标志点位置图</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>-XY</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US"/>
+              <a:t>平面投影</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>旋转轴与速度!$B$2:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>9.44152046783597</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13.680426556588</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.419332645339</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.65823873409</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22.897144822841</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26.136050911593</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28.874957000344</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31.613863089095</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>33.852769177847</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>35.591675266598</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37.330581355349</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>38.569487444101</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39.8083935328521</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>40.547299621603</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40.786205710354</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>41.525111799106</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>41.264017887857</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40.502923976608</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>旋转轴与速度!$C$2:$C$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>-36.90350877193</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-36.463880288958</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-35.524251805986</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-34.0846233230139</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-32.144994840041</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-29.705366357069</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-27.765737874097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-25.326109391125</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-22.386480908153</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-18.946852425181</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-15.507223942209</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-12.067595459236</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-9.12796697626402</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-5.68833849329201</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1.74871001032</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.69091847265202</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.13054695562403</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.57017543859604</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"YUAN"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>YUAN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>旋转轴与速度!$E$2:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>47.44</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44.5818885096479</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.3519385786961</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.7418076465493</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.27093753917763</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-8.19652875776856</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-23.6763646574306</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-36.3033468523216</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-44.5560030448154</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-47.4399398331545</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-44.6076608905174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-36.4004380967454</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-23.8071904135063</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-8.3453253409821</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.12209918549612</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>23.6108616121494</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>36.254663040877</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44.5300045616798</c:v>
+                </c:pt>
+                <c:pt idx="18" c:formatCode="General">
+                  <c:v>47.4397593327705</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>旋转轴与速度!$F$2:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.2175465750319</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.4809803249618</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41.0716467855168</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46.7134369557949</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46.7265504432231</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>41.1094071546692</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.5388376877712</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16.2885294815216</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0755554543581351</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-16.1465225320068</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-30.4230456457766</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-41.0337822362874</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-46.7002049776354</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-46.7395454066571</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-41.1470632479638</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-30.5966175874469</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-16.3594710714245</c:v>
+                </c:pt>
+                <c:pt idx="18" c:formatCode="General">
+                  <c:v>-0.151110717066466</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="-92832768"/>
+        <c:axId val="-92843104"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="-92832768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0_ " sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-92843104"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="-92843104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0_ " sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-92832768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{634241fc-8f45-4b1e-aaae-5c52da3a8e38}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:externalData r:id="rId1">
+    <c:autoUpdate val="0"/>
+  </c:externalData>
 </c:chartSpace>
 </file>
 
@@ -6691,6 +7261,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -10837,6 +11447,522 @@
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -11075,13 +12201,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>391795</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>153670</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>35560</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>151130</xdr:rowOff>
@@ -11092,7 +12218,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6507480" y="153670"/>
+        <a:off x="7193280" y="153670"/>
         <a:ext cx="5815965" cy="2923540"/>
       </xdr:xfrm>
       <a:graphic>
@@ -11105,13 +12231,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>408940</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>52705</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
@@ -11122,12 +12248,47 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6524625" y="3355340"/>
+        <a:off x="7210425" y="3355340"/>
         <a:ext cx="5815965" cy="3131185"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>14286</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4334510" y="19050"/>
+        <a:ext cx="3681095" cy="4339590"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11390,31 +12551,31 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -11954,22 +13115,22 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -11977,23 +13138,23 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <f>(L0!B2+L0!D2)/2</f>
         <v>884.5</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>(L0!C2+L0!E2)/2</f>
         <v>518</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <f>(L0!D2-L0!B2+L0!E2-L0!C2)/4</f>
         <v>48.75</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <f>(L0!F2+L0!H2)/2</f>
         <v>894</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <f>(L0!G2+L0!I2)/2</f>
         <v>554</v>
       </c>
@@ -12002,23 +13163,23 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f>(L0!B3+L0!D3)/2</f>
         <v>881</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>(L0!C3+L0!E3)/2</f>
         <v>520</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>(L0!D3-L0!B3+L0!E3-L0!C3)/4</f>
         <v>48</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f>(L0!F3+L0!H3)/2</f>
         <v>894.5</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f>(L0!G3+L0!I3)/2</f>
         <v>556</v>
       </c>
@@ -12027,23 +13188,23 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f>(L0!B4+L0!D4)/2</f>
         <v>877.5</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f>(L0!C4+L0!E4)/2</f>
         <v>522</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f>(L0!D4-L0!B4+L0!E4-L0!C4)/4</f>
         <v>48.25</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f>(L0!F4+L0!H4)/2</f>
         <v>893.5</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <f>(L0!G4+L0!I4)/2</f>
         <v>557.5</v>
       </c>
@@ -12052,23 +13213,23 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>(L0!B5+L0!D5)/2</f>
         <v>873</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f>(L0!C5+L0!E5)/2</f>
         <v>524.5</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f>(L0!D5-L0!B5+L0!E5-L0!C5)/4</f>
         <v>47.75</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f>(L0!F5+L0!H5)/2</f>
         <v>893</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f>(L0!G5+L0!I5)/2</f>
         <v>558.5</v>
       </c>
@@ -12077,23 +13238,23 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f>(L0!B6+L0!D6)/2</f>
         <v>869.5</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f>(L0!C6+L0!E6)/2</f>
         <v>526.5</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <f>(L0!D6-L0!B6+L0!E6-L0!C6)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <f>(L0!F6+L0!H6)/2</f>
         <v>892.5</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <f>(L0!G6+L0!I6)/2</f>
         <v>559</v>
       </c>
@@ -12102,23 +13263,23 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f>(L0!B7+L0!D7)/2</f>
         <v>865.5</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f>(L0!C7+L0!E7)/2</f>
         <v>529</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <f>(L0!D7-L0!B7+L0!E7-L0!C7)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <f>(L0!F7+L0!H7)/2</f>
         <v>892</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <f>(L0!G7+L0!I7)/2</f>
         <v>559</v>
       </c>
@@ -12127,23 +13288,23 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>(L0!B8+L0!D8)/2</f>
         <v>862.5</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f>(L0!C8+L0!E8)/2</f>
         <v>531.5</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <f>(L0!D8-L0!B8+L0!E8-L0!C8)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <f>(L0!F8+L0!H8)/2</f>
         <v>891</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <f>(L0!G8+L0!I8)/2</f>
         <v>559.5</v>
       </c>
@@ -12152,23 +13313,23 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f>(L0!B9+L0!D9)/2</f>
         <v>858.5</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f>(L0!C9+L0!E9)/2</f>
         <v>533.5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <f>(L0!D9-L0!B9+L0!E9-L0!C9)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f>(L0!F9+L0!H9)/2</f>
         <v>890</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <f>(L0!G9+L0!I9)/2</f>
         <v>559.5</v>
       </c>
@@ -12177,23 +13338,23 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f>(L0!B10+L0!D10)/2</f>
         <v>854.5</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f>(L0!C10+L0!E10)/2</f>
         <v>536.5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <f>(L0!D10-L0!B10+L0!E10-L0!C10)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f>(L0!F10+L0!H10)/2</f>
         <v>888.5</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <f>(L0!G10+L0!I10)/2</f>
         <v>559</v>
       </c>
@@ -12202,23 +13363,23 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f>(L0!B11+L0!D11)/2</f>
         <v>851</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f>(L0!C11+L0!E11)/2</f>
         <v>539</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <f>(L0!D11-L0!B11+L0!E11-L0!C11)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f>(L0!F11+L0!H11)/2</f>
         <v>886.5</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <f>(L0!G11+L0!I11)/2</f>
         <v>558</v>
       </c>
@@ -12227,23 +13388,23 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f>(L0!B12+L0!D12)/2</f>
         <v>847</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>(L0!C12+L0!E12)/2</f>
         <v>541</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <f>(L0!D12-L0!B12+L0!E12-L0!C12)/4</f>
         <v>47</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f>(L0!F12+L0!H12)/2</f>
         <v>884.5</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <f>(L0!G12+L0!I12)/2</f>
         <v>557</v>
       </c>
@@ -12252,23 +13413,23 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>(L0!B13+L0!D13)/2</f>
         <v>843</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f>(L0!C13+L0!E13)/2</f>
         <v>543.5</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <f>(L0!D13-L0!B13+L0!E13-L0!C13)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f>(L0!F13+L0!H13)/2</f>
         <v>882</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f>(L0!G13+L0!I13)/2</f>
         <v>556</v>
       </c>
@@ -12277,23 +13438,23 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>(L0!B14+L0!D14)/2</f>
         <v>840</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f>(L0!C14+L0!E14)/2</f>
         <v>546</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <f>(L0!D14-L0!B14+L0!E14-L0!C14)/4</f>
         <v>47</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f>(L0!F14+L0!H14)/2</f>
         <v>879.5</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <f>(L0!G14+L0!I14)/2</f>
         <v>555.5</v>
       </c>
@@ -12302,23 +13463,23 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <f>(L0!B15+L0!D15)/2</f>
         <v>836</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <f>(L0!C15+L0!E15)/2</f>
         <v>549</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <f>(L0!D15-L0!B15+L0!E15-L0!C15)/4</f>
         <v>47</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f>(L0!F15+L0!H15)/2</f>
         <v>876.5</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <f>(L0!G15+L0!I15)/2</f>
         <v>554.5</v>
       </c>
@@ -12327,23 +13488,23 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <f>(L0!B16+L0!D16)/2</f>
         <v>832</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f>(L0!C16+L0!E16)/2</f>
         <v>551.5</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <f>(L0!D16-L0!B16+L0!E16-L0!C16)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f>(L0!F16+L0!H16)/2</f>
         <v>873</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <f>(L0!G16+L0!I16)/2</f>
         <v>553</v>
       </c>
@@ -12352,23 +13513,23 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <f>(L0!B17+L0!D17)/2</f>
         <v>828.5</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <f>(L0!C17+L0!E17)/2</f>
         <v>554</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <f>(L0!D17-L0!B17+L0!E17-L0!C17)/4</f>
         <v>46.75</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <f>(L0!F17+L0!H17)/2</f>
         <v>870</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <f>(L0!G17+L0!I17)/2</f>
         <v>552</v>
       </c>
@@ -12377,23 +13538,23 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f>(L0!B18+L0!D18)/2</f>
         <v>825</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f>(L0!C18+L0!E18)/2</f>
         <v>556.5</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f>(L0!D18-L0!B18+L0!E18-L0!C18)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <f>(L0!F18+L0!H18)/2</f>
         <v>866</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <f>(L0!G18+L0!I18)/2</f>
         <v>551</v>
       </c>
@@ -12402,29 +13563,29 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <f>(L0!B19+L0!D19)/2</f>
         <v>821</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <f>(L0!C19+L0!E19)/2</f>
         <v>559</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <f>(L0!D19-L0!B19+L0!E19-L0!C19)/4</f>
         <v>47</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <f>(L0!F19+L0!H19)/2</f>
         <v>861.5</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <f>(L0!G19+L0!I19)/2</f>
         <v>550</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <f>AVERAGE(D2:D19)</f>
         <v>47.4444444444444</v>
       </c>
@@ -12444,22 +13605,22 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -12467,23 +13628,23 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <f>'L1'!E2-'L1'!B2</f>
         <v>9.5</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>-('L1'!F2-'L1'!C2)</f>
         <v>-36</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <f>SQRT(47.44*47.44-B2*B2-C2*C2)</f>
         <v>29.3990408006792</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <f>COS(3.14/9*((A2-25)/20))*47.44</f>
         <v>47.44</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <f>SIN(3.14/9*((A2-25)/20))*47.44</f>
         <v>0</v>
       </c>
@@ -12492,23 +13653,23 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f>'L1'!E3-'L1'!B3</f>
         <v>13.5</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>-('L1'!F3-'L1'!C3)</f>
         <v>-36</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f t="shared" ref="D3:D19" si="0">SQRT(47.44*47.44-B3*B3-C3*C3)</f>
         <v>27.7903508434133</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f t="shared" ref="E3:E20" si="1">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f t="shared" ref="F3:F20" si="2">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
@@ -12517,23 +13678,23 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f>'L1'!E4-'L1'!B4</f>
         <v>16</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f>-('L1'!F4-'L1'!C4)</f>
         <v>-35.5</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f t="shared" si="0"/>
         <v>27.0980368292613</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f t="shared" si="1"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <f t="shared" si="2"/>
         <v>30.4809803249618</v>
       </c>
@@ -12542,23 +13703,23 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>'L1'!E5-'L1'!B5</f>
         <v>20</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f>-('L1'!F5-'L1'!C5)</f>
         <v>-34</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f t="shared" si="0"/>
         <v>26.3543848344066</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f t="shared" si="1"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f t="shared" si="2"/>
         <v>41.0716467855168</v>
       </c>
@@ -12567,23 +13728,23 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f>'L1'!E6-'L1'!B6</f>
         <v>23</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f>-('L1'!F6-'L1'!C6)</f>
         <v>-32.5</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <f t="shared" si="0"/>
         <v>25.7934797962586</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <f t="shared" si="1"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <f t="shared" si="2"/>
         <v>46.7134369557949</v>
       </c>
@@ -12592,23 +13753,23 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f>'L1'!E7-'L1'!B7</f>
         <v>26.5</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f>-('L1'!F7-'L1'!C7)</f>
         <v>-30</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <f t="shared" si="0"/>
         <v>25.461806691592</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <f t="shared" si="1"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <f t="shared" si="2"/>
         <v>46.7265504432231</v>
       </c>
@@ -12617,23 +13778,23 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>'L1'!E8-'L1'!B8</f>
         <v>28.5</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f>-('L1'!F8-'L1'!C8)</f>
         <v>-28</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <f t="shared" si="0"/>
         <v>25.5793588660858</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <f t="shared" si="1"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <f t="shared" si="2"/>
         <v>41.1094071546692</v>
       </c>
@@ -12642,23 +13803,23 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f>'L1'!E9-'L1'!B9</f>
         <v>31.5</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f>-('L1'!F9-'L1'!C9)</f>
         <v>-26</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <f t="shared" si="0"/>
         <v>24.1309676556909</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f t="shared" si="1"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <f t="shared" si="2"/>
         <v>30.5388376877712</v>
       </c>
@@ -12667,23 +13828,23 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f>'L1'!E10-'L1'!B10</f>
         <v>34</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f>-('L1'!F10-'L1'!C10)</f>
         <v>-22.5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <f t="shared" si="0"/>
         <v>24.2549706245957</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f t="shared" si="1"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <f t="shared" si="2"/>
         <v>16.2885294815216</v>
       </c>
@@ -12692,23 +13853,23 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f>'L1'!E11-'L1'!B11</f>
         <v>35.5</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f>-('L1'!F11-'L1'!C11)</f>
         <v>-19</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <f t="shared" si="0"/>
         <v>25.0859243401554</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f t="shared" si="1"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <f t="shared" si="2"/>
         <v>0.0755554543581351</v>
       </c>
@@ -12717,23 +13878,23 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f>'L1'!E12-'L1'!B12</f>
         <v>37.5</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>-('L1'!F12-'L1'!C12)</f>
         <v>-16</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <f t="shared" si="0"/>
         <v>24.2549706245957</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f t="shared" si="1"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <f t="shared" si="2"/>
         <v>-16.1465225320068</v>
       </c>
@@ -12742,23 +13903,23 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>'L1'!E13-'L1'!B13</f>
         <v>39</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f>-('L1'!F13-'L1'!C13)</f>
         <v>-12.5</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <f t="shared" si="0"/>
         <v>23.9437591033655</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f t="shared" si="1"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f t="shared" si="2"/>
         <v>-30.4230456457766</v>
       </c>
@@ -12767,23 +13928,23 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>'L1'!E14-'L1'!B14</f>
         <v>39.5</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f>-('L1'!F14-'L1'!C14)</f>
         <v>-9.5</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <f t="shared" si="0"/>
         <v>24.4959915088163</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f t="shared" si="1"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <f t="shared" si="2"/>
         <v>-41.0337822362874</v>
       </c>
@@ -12792,23 +13953,23 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <f>'L1'!E15-'L1'!B15</f>
         <v>40.5</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <f>-('L1'!F15-'L1'!C15)</f>
         <v>-5.5</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <f t="shared" si="0"/>
         <v>24.0843019413061</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f t="shared" si="1"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <f t="shared" si="2"/>
         <v>-46.7002049776354</v>
       </c>
@@ -12817,23 +13978,23 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <f>'L1'!E16-'L1'!B16</f>
         <v>41</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f>-('L1'!F16-'L1'!C16)</f>
         <v>-1.5</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <f t="shared" si="0"/>
         <v>23.8181359472147</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f t="shared" si="1"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <f t="shared" si="2"/>
         <v>-46.7395454066571</v>
       </c>
@@ -12842,23 +14003,23 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <f>'L1'!E17-'L1'!B17</f>
         <v>41.5</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <f>-('L1'!F17-'L1'!C17)</f>
         <v>2</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <f t="shared" si="0"/>
         <v>22.8976767380448</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <f t="shared" si="1"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <f t="shared" si="2"/>
         <v>-41.1470632479638</v>
       </c>
@@ -12867,23 +14028,23 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f>'L1'!E18-'L1'!B18</f>
         <v>41</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f>-('L1'!F18-'L1'!C18)</f>
         <v>5.5</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f t="shared" si="0"/>
         <v>23.2229111008934</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <f t="shared" si="1"/>
         <v>36.254663040877</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <f t="shared" si="2"/>
         <v>-30.5966175874469</v>
       </c>
@@ -12892,23 +14053,23 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <f>'L1'!E19-'L1'!B19</f>
         <v>40.5</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <f>-('L1'!F19-'L1'!C19)</f>
         <v>9</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <f t="shared" si="0"/>
         <v>23.0065990533151</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <f t="shared" si="1"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <f t="shared" si="2"/>
         <v>-16.3594710714245</v>
       </c>
@@ -12927,7 +14088,7 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12951,34 +14112,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -12986,38 +14147,38 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <f>COS(A2*3.1416/9)*47.44</f>
         <v>47.44</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>SIN(A2*3.1416/9)*47.44</f>
         <v>0</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <f>COS(A2*3.1416/18+3.1416/30)*47.44</f>
         <v>47.1801175019494</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <f>SIN(A2*3.1416/18+3.1416/30)*47.44</f>
         <v>4.95884185090085</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <f>D2*COS(-3.1416/30)-E2*SIN(-3.1416/30)</f>
         <v>47.44</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <f>(D2*SIN(-3.1416/30)+E2*COS(-3.1416/30))*0.8</f>
         <v>0</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <f>G2*COS(3.1416/30)-H2*SIN(3.1416/30)</f>
         <v>47.1801175019494</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <f>G2*SIN(3.1416/30)+H2*COS(3.1416/30)</f>
         <v>4.95884185090085</v>
       </c>
@@ -13026,35 +14187,35 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f t="shared" ref="B3:B20" si="0">COS(A3*3.1416/9)*47.44</f>
         <v>44.579004685768</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f t="shared" ref="C3:C20" si="1">SIN(A3*3.1416/9)*47.44</f>
         <v>16.2254719877812</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f t="shared" ref="D3:D20" si="2">COS(A3*3.1416/18+3.1416/30)*47.44</f>
         <v>45.6022463163357</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f t="shared" ref="E3:E20" si="3">SIN(A3*3.1416/18+3.1416/30)*47.44</f>
         <v>13.0762659388775</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G20" si="4">D3*COS(-3.1416/30)-E3*SIN(-3.1416/30)</f>
         <v>46.7192764407414</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <f t="shared" ref="H3:H20" si="5">(D3*SIN(-3.1416/30)+E3*COS(-3.1416/30))*0.8</f>
         <v>6.5903108929923</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <f t="shared" ref="I3:I20" si="6">G3*COS(3.1416/30)-H3*SIN(3.1416/30)</f>
         <v>45.77446548511</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <f t="shared" ref="J3:J20" si="7">G3*SIN(3.1416/30)+H3*COS(3.1416/30)</f>
         <v>11.4377138609593</v>
       </c>
@@ -13063,35 +14224,35 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f t="shared" si="0"/>
         <v>36.3410985992296</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f t="shared" si="1"/>
         <v>30.4939035317073</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f t="shared" si="2"/>
         <v>42.6387674884245</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f t="shared" si="3"/>
         <v>20.7963724497344</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <f t="shared" si="4"/>
         <v>44.579004685768</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f t="shared" si="5"/>
         <v>12.980377590225</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <f t="shared" si="6"/>
         <v>42.9779730092661</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <f t="shared" si="7"/>
         <v>17.5690551018925</v>
       </c>
@@ -13100,35 +14261,35 @@
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f t="shared" si="0"/>
         <v>23.7198993926896</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f t="shared" si="1"/>
         <v>41.0843032410273</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f t="shared" si="2"/>
         <v>38.3797252428634</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f t="shared" si="3"/>
         <v>27.8845887594261</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <f t="shared" si="4"/>
         <v>41.0842161126946</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f t="shared" si="5"/>
         <v>18.9760402428815</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f t="shared" si="6"/>
         <v>38.8756104795876</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <f t="shared" si="7"/>
         <v>23.1665670036247</v>
       </c>
@@ -13137,35 +14298,35 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f t="shared" si="0"/>
         <v>8.23771700670016</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f t="shared" si="1"/>
         <v>46.7193066998808</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <f t="shared" si="2"/>
         <v>32.9545290267963</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <f t="shared" si="3"/>
         <v>34.1255419974839</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <f t="shared" si="4"/>
         <v>36.3410985992296</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <f t="shared" si="5"/>
         <v>24.3951228253659</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <f t="shared" si="6"/>
         <v>33.5920266871267</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <f t="shared" si="7"/>
         <v>28.0601712060882</v>
       </c>
@@ -13174,35 +14335,35 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f t="shared" si="0"/>
         <v>-8.23806022566945</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f t="shared" si="1"/>
         <v>46.7192461809717</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <f t="shared" si="2"/>
         <v>26.5280214509534</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <f t="shared" si="3"/>
         <v>39.3296030732291</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <f t="shared" si="4"/>
         <v>30.4937700431928</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f t="shared" si="5"/>
         <v>29.0729684874772</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <f t="shared" si="6"/>
         <v>27.287761400709</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <f t="shared" si="7"/>
         <v>32.1011773282373</v>
       </c>
@@ -13211,35 +14372,35 @@
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f t="shared" si="0"/>
         <v>-23.7202012141941</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f t="shared" si="1"/>
         <v>41.0841289838076</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <f t="shared" si="2"/>
         <v>19.2954696069731</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <f t="shared" si="3"/>
         <v>43.338648486615</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <f t="shared" si="4"/>
         <v>23.7198993926896</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f t="shared" si="5"/>
         <v>32.8674425928218</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <f t="shared" si="6"/>
         <v>20.1543674245393</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <f t="shared" si="7"/>
         <v>35.1668008711117</v>
       </c>
@@ -13248,35 +14409,35 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f t="shared" si="0"/>
         <v>-36.3413226189731</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f t="shared" si="1"/>
         <v>30.4936365542668</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <f t="shared" si="2"/>
         <v>11.4766319479547</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f t="shared" si="3"/>
         <v>46.0308648531742</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <f t="shared" si="4"/>
         <v>16.2253082398443</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f t="shared" si="5"/>
         <v>35.663251427963</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <f t="shared" si="6"/>
         <v>12.4085903360248</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <f t="shared" si="7"/>
         <v>37.1638939801089</v>
       </c>
@@ -13285,35 +14446,35 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f t="shared" si="0"/>
         <v>-44.5791238835381</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f t="shared" si="1"/>
         <v>16.2251444916884</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <f t="shared" si="2"/>
         <v>3.30908100791483</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f t="shared" si="3"/>
         <v>47.3244501593316</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <f t="shared" si="4"/>
         <v>8.23771700670016</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f t="shared" si="5"/>
         <v>37.3754453599046</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <f t="shared" si="6"/>
         <v>4.28578275036188</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <f t="shared" si="7"/>
         <v>38.0317757086149</v>
       </c>
@@ -13322,35 +14483,35 @@
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>-47.4399999987198</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f t="shared" si="1"/>
         <v>-0.000348513700203172</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <f t="shared" si="2"/>
         <v>-4.95901515311578</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f t="shared" si="3"/>
         <v>47.1800992867879</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <f t="shared" si="4"/>
         <v>-0.000174256850099752</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f t="shared" si="5"/>
         <v>37.951999999744</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <f t="shared" si="6"/>
         <v>-3.9672467829423</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <f t="shared" si="7"/>
         <v>37.7440757864617</v>
       </c>
@@ -13359,35 +14520,35 @@
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>-44.578885485592</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f t="shared" si="1"/>
         <v>-16.2257994829984</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <f t="shared" si="2"/>
         <v>-13.0764334451932</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f t="shared" si="3"/>
         <v>45.6021982842213</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <f t="shared" si="4"/>
         <v>-8.23806022566945</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f t="shared" si="5"/>
         <v>37.3753969447774</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <f t="shared" si="6"/>
         <v>-12.0997329679388</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <f t="shared" si="7"/>
         <v>36.3095358709803</v>
       </c>
@@ -13396,35 +14557,35 @@
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f t="shared" si="0"/>
         <v>-36.3408745775248</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f t="shared" si="1"/>
         <v>-30.4941705075021</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <f t="shared" si="2"/>
         <v>-20.7965290705324</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f t="shared" si="3"/>
         <v>42.6386910987955</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <f t="shared" si="4"/>
         <v>-16.2256357354993</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f t="shared" si="5"/>
         <v>35.6631560687846</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <f t="shared" si="6"/>
         <v>-19.8645731744052</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <f t="shared" si="7"/>
         <v>33.7717439349273</v>
       </c>
@@ -13433,35 +14594,35 @@
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f t="shared" si="0"/>
         <v>-23.7195975699048</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f t="shared" si="1"/>
         <v>-41.0844774960296</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <f t="shared" si="2"/>
         <v>-27.8847297358406</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f t="shared" si="3"/>
         <v>38.3796228167908</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <f t="shared" si="4"/>
         <v>-23.7202012141941</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <f t="shared" si="5"/>
         <v>32.8673031870461</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <f t="shared" si="6"/>
         <v>-27.0258355612507</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <f t="shared" si="7"/>
         <v>30.2078098618107</v>
       </c>
@@ -13470,35 +14631,35 @@
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <f t="shared" si="0"/>
         <v>-8.23737378728626</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <f t="shared" si="1"/>
         <v>-46.7193672162683</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <f t="shared" si="2"/>
         <v>-34.1256630459979</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f t="shared" si="3"/>
         <v>32.954403676459</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <f t="shared" si="4"/>
         <v>-30.4940370198104</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f t="shared" si="5"/>
         <v>29.0727892708979</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <f t="shared" si="6"/>
         <v>-33.3659277795616</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
         <f t="shared" si="7"/>
         <v>25.7260224901691</v>
       </c>
@@ -13507,35 +14668,35 @@
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <f t="shared" si="0"/>
         <v>8.23840344419414</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f t="shared" si="1"/>
         <v>-46.7191856595413</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <f t="shared" si="2"/>
         <v>-39.3297005158276</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f t="shared" si="3"/>
         <v>26.5278769850757</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <f t="shared" si="4"/>
         <v>-36.3413226189731</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f t="shared" si="5"/>
         <v>24.3949092434134</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <f t="shared" si="6"/>
         <v>-38.6922084368585</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <f t="shared" si="7"/>
         <v>20.4625592966607</v>
       </c>
@@ -13544,35 +14705,35 @@
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <f t="shared" si="0"/>
         <v>23.7205030344186</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <f t="shared" si="1"/>
         <v>-41.0839547243707</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <f t="shared" si="2"/>
         <v>-43.3387193625401</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <f t="shared" si="3"/>
         <v>19.2953104150981</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <f t="shared" si="4"/>
         <v>-41.0843903688056</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <f t="shared" si="5"/>
         <v>18.9757987851658</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="2">
         <f t="shared" si="6"/>
         <v>-42.8428404356316</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
         <f t="shared" si="7"/>
         <v>14.5773486930415</v>
       </c>
@@ -13581,35 +14742,35 @@
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f t="shared" si="0"/>
         <v>36.3415466367552</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f t="shared" si="1"/>
         <v>-30.4933695751805</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f t="shared" si="2"/>
         <v>-46.0309070088867</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <f t="shared" si="3"/>
         <v>11.4764628670696</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <f t="shared" si="4"/>
         <v>-44.5791238835381</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f t="shared" si="5"/>
         <v>12.9801155933507</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <f t="shared" si="6"/>
         <v>-45.6917083345937</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
         <f t="shared" si="7"/>
         <v>8.24921065963301</v>
       </c>
@@ -13618,35 +14779,35 @@
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <f t="shared" si="0"/>
         <v>44.5792430789022</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <f t="shared" si="1"/>
         <v>-16.2248169947199</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <f t="shared" si="2"/>
         <v>-47.3244623139455</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <f t="shared" si="3"/>
         <v>3.30890717548068</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <f t="shared" si="4"/>
         <v>-46.7193369583897</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <f t="shared" si="5"/>
         <v>6.59003631763904</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="2">
         <f t="shared" si="6"/>
         <v>-47.1522503204229</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <f t="shared" si="7"/>
         <v>1.67042336536092</v>
       </c>
@@ -13655,35 +14816,35 @@
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="2">
         <f t="shared" si="0"/>
         <v>47.4399999948794</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <f t="shared" si="1"/>
         <v>0.000697027400387534</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <f t="shared" si="2"/>
         <v>-47.1800810709899</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <f t="shared" si="3"/>
         <v>-4.9591884552638</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="2">
         <f t="shared" si="4"/>
         <v>-47.4399999987198</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="2">
         <f t="shared" si="5"/>
         <v>-0.000278810960160314</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="2">
         <f t="shared" si="6"/>
         <v>-47.1800883569272</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="2">
         <f t="shared" si="7"/>
         <v>-4.95911913436445</v>
       </c>
@@ -13737,34 +14898,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -13772,31 +14933,31 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <f>'L2'!C2*'L2'!D3-'L2'!D2*'L2'!C3</f>
         <v>57.9128384615722</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>'L2'!D2*'L2'!B3-'L2'!B2*'L2'!D3</f>
         <v>132.878717796743</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <f>'L2'!B2*'L2'!C3-'L2'!C2*'L2'!B3</f>
         <v>144</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <f>SQRT(B2*B2+C2*C2+D2*D2)</f>
         <v>204.319970883863</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <f>B2/E2*47.44</f>
         <v>13.4464832034389</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <f>C2/E2*47.44</f>
         <v>30.8524239946206</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <f>-D2/E2*47.44</f>
         <v>-33.4346171372695</v>
       </c>
@@ -13813,31 +14974,31 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f>'L2'!C3*'L2'!D4-'L2'!D3*'L2'!C4</f>
         <v>11.0281290877654</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>'L2'!D3*'L2'!B4-'L2'!B3*'L2'!D4</f>
         <v>78.8221162995853</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>'L2'!B3*'L2'!C4-'L2'!C3*'L2'!B4</f>
         <v>96.75</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f t="shared" ref="E3:E19" si="0">SQRT(B3*B3+C3*C3+D3*D3)</f>
         <v>125.280118730474</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f t="shared" ref="F3:F19" si="1">B3/E3*47.44</f>
         <v>4.17603726134023</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G19" si="2">C3/E3*47.44</f>
         <v>29.8476824187646</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <f t="shared" ref="H3:H19" si="3">-D3/E3*47.44</f>
         <v>-36.6364595317351</v>
       </c>
@@ -13854,31 +15015,31 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f>'L2'!C4*'L2'!D5-'L2'!D4*'L2'!C5</f>
         <v>-14.2474094265501</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f>'L2'!D4*'L2'!B5-'L2'!B4*'L2'!D5</f>
         <v>120.29057923472</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f>'L2'!B4*'L2'!C5-'L2'!C4*'L2'!B5</f>
         <v>166</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f t="shared" si="0"/>
         <v>205.496501498182</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <f t="shared" si="1"/>
         <v>-3.28909299315501</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <f t="shared" si="2"/>
         <v>27.7697432184539</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f t="shared" si="3"/>
         <v>-38.3220149374157</v>
       </c>
@@ -13895,31 +15056,31 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>'L2'!C5*'L2'!D6-'L2'!D5*'L2'!C6</f>
         <v>-20.4608059545781</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f>'L2'!D5*'L2'!B6-'L2'!B5*'L2'!D6</f>
         <v>90.2812552661798</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f>'L2'!B5*'L2'!C6-'L2'!C5*'L2'!B6</f>
         <v>132</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f t="shared" si="0"/>
         <v>161.224531733691</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f t="shared" si="1"/>
         <v>-6.02055173643493</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <f t="shared" si="2"/>
         <v>26.5650810318499</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f t="shared" si="3"/>
         <v>-38.8407392638214</v>
       </c>
@@ -13936,31 +15097,31 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f>'L2'!C6*'L2'!D7-'L2'!D6*'L2'!C7</f>
         <v>-53.704323588982</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f>'L2'!D6*'L2'!B7-'L2'!B6*'L2'!D7</f>
         <v>97.905660694237</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <f>'L2'!B6*'L2'!C7-'L2'!C6*'L2'!B7</f>
         <v>171.25</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
         <v>204.441275842539</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <f t="shared" si="1"/>
         <v>-12.4619311856749</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <f t="shared" si="2"/>
         <v>22.7187221572219</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <f t="shared" si="3"/>
         <v>-39.7380615363465</v>
       </c>
@@ -13977,31 +15138,31 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f>'L2'!C7*'L2'!D8-'L2'!D7*'L2'!C8</f>
         <v>-54.4501786179981</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f>'L2'!D7*'L2'!B8-'L2'!B7*'L2'!D8</f>
         <v>47.8084807590982</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <f>'L2'!B7*'L2'!C8-'L2'!C7*'L2'!B8</f>
         <v>113</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <f t="shared" si="0"/>
         <v>134.23662981476</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <f t="shared" si="1"/>
         <v>-19.243007495066</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <f t="shared" si="2"/>
         <v>16.8957931254784</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f t="shared" si="3"/>
         <v>-39.9348524124714</v>
       </c>
@@ -14018,31 +15179,31 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>'L2'!C8*'L2'!D9-'L2'!D8*'L2'!C9</f>
         <v>-10.6037638411143</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f>'L2'!D8*'L2'!B9-'L2'!B8*'L2'!D9</f>
         <v>118.017226094512</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <f>'L2'!B8*'L2'!C9-'L2'!C8*'L2'!B9</f>
         <v>141</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <f t="shared" si="0"/>
         <v>184.177917956093</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <f t="shared" si="1"/>
         <v>-2.73128593375882</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <f t="shared" si="2"/>
         <v>30.3985258822307</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f t="shared" si="3"/>
         <v>-36.3183603888639</v>
       </c>
@@ -14059,31 +15220,31 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f>'L2'!C9*'L2'!D10-'L2'!D9*'L2'!C10</f>
         <v>-87.6824639864429</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f>'L2'!D9*'L2'!B10-'L2'!B9*'L2'!D10</f>
         <v>56.421325618726</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <f>'L2'!B9*'L2'!C10-'L2'!C9*'L2'!B10</f>
         <v>175.25</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f t="shared" si="0"/>
         <v>203.921904108676</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <f t="shared" si="1"/>
         <v>-20.3982799675117</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <f t="shared" si="2"/>
         <v>13.1257487960975</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f t="shared" si="3"/>
         <v>-40.7698233122092</v>
       </c>
@@ -14100,31 +15261,31 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f>'L2'!C10*'L2'!D11-'L2'!D10*'L2'!C11</f>
         <v>-103.588855786178</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f>'L2'!D10*'L2'!B11-'L2'!B10*'L2'!D11</f>
         <v>8.13002960786366</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <f>'L2'!B10*'L2'!C11-'L2'!C10*'L2'!B11</f>
         <v>152.75</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f t="shared" si="0"/>
         <v>184.741199856757</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <f t="shared" si="1"/>
         <v>-26.6007545815804</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <f t="shared" si="2"/>
         <v>2.08772382606643</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f t="shared" si="3"/>
         <v>-39.2249265763061</v>
       </c>
@@ -14141,31 +15302,31 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f>'L2'!C11*'L2'!D12-'L2'!D11*'L2'!C12</f>
         <v>-59.4696524248319</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f>'L2'!D11*'L2'!B12-'L2'!B11*'L2'!D12</f>
         <v>79.6707055826802</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <f>'L2'!B11*'L2'!C12-'L2'!C11*'L2'!B12</f>
         <v>144.5</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f t="shared" si="0"/>
         <v>175.397579480369</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <f t="shared" si="1"/>
         <v>-16.0848303573641</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <f t="shared" si="2"/>
         <v>21.5486341604011</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f t="shared" si="3"/>
         <v>-39.0830935085238</v>
       </c>
@@ -14182,31 +15343,31 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f>'L2'!C12*'L2'!D13-'L2'!D12*'L2'!C13</f>
         <v>-79.9130128464018</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>'L2'!D12*'L2'!B13-'L2'!B12*'L2'!D13</f>
         <v>48.052887983026</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <f>'L2'!B12*'L2'!C13-'L2'!C12*'L2'!B13</f>
         <v>155.25</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f t="shared" si="0"/>
         <v>181.101441644451</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <f t="shared" si="1"/>
         <v>-20.9334243560367</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <f t="shared" si="2"/>
         <v>12.5875806686854</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f t="shared" si="3"/>
         <v>-40.6681467199998</v>
       </c>
@@ -14223,31 +15384,31 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>'L2'!C13*'L2'!D14-'L2'!D13*'L2'!C14</f>
         <v>-78.7341823782315</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f>'L2'!D13*'L2'!B14-'L2'!B13*'L2'!D14</f>
         <v>-9.56518426089838</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <f>'L2'!B13*'L2'!C14-'L2'!C13*'L2'!B14</f>
         <v>123.25</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f t="shared" si="0"/>
         <v>146.564411521739</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f t="shared" si="1"/>
         <v>-25.4846969550265</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <f t="shared" si="2"/>
         <v>-3.09606088289526</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f t="shared" si="3"/>
         <v>-39.8935863030622</v>
       </c>
@@ -14264,31 +15425,31 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>'L2'!C14*'L2'!D15-'L2'!D14*'L2'!C15</f>
         <v>-94.0729151439183</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f>'L2'!D14*'L2'!B15-'L2'!B14*'L2'!D15</f>
         <v>40.7577294254691</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <f>'L2'!B14*'L2'!C15-'L2'!C14*'L2'!B15</f>
         <v>167.5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f t="shared" si="0"/>
         <v>196.385223149795</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <f t="shared" si="1"/>
         <v>-22.7248212612383</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <f t="shared" si="2"/>
         <v>9.84568315748187</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <f t="shared" si="3"/>
         <v>-40.4623111278539</v>
       </c>
@@ -14305,31 +15466,31 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <f>'L2'!C15*'L2'!D16-'L2'!D15*'L2'!C16</f>
         <v>-94.8732947977217</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <f>'L2'!D15*'L2'!B16-'L2'!B15*'L2'!D16</f>
         <v>22.8218737313549</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <f>'L2'!B15*'L2'!C16-'L2'!C15*'L2'!B16</f>
         <v>164.75</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f t="shared" si="0"/>
         <v>191.479352637263</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <f t="shared" si="1"/>
         <v>-23.50534949703</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <f t="shared" si="2"/>
         <v>5.65423725797986</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f t="shared" si="3"/>
         <v>-40.8176646325209</v>
       </c>
@@ -14346,31 +15507,31 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <f>'L2'!C16*'L2'!D17-'L2'!D16*'L2'!C17</f>
         <v>-81.9827870014967</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f>'L2'!D16*'L2'!B17-'L2'!B16*'L2'!D17</f>
         <v>49.6478955495716</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <f>'L2'!B16*'L2'!C17-'L2'!C16*'L2'!B17</f>
         <v>144.25</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f t="shared" si="0"/>
         <v>173.188202245517</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <f t="shared" si="1"/>
         <v>-22.4568611771688</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <f t="shared" si="2"/>
         <v>13.5996340070136</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f t="shared" si="3"/>
         <v>-39.5131995786806</v>
       </c>
@@ -14387,31 +15548,31 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <f>'L2'!C17*'L2'!D18-'L2'!D17*'L2'!C18</f>
         <v>-79.4913998574598</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <f>'L2'!D17*'L2'!B18-'L2'!B17*'L2'!D18</f>
         <v>-24.9460644272376</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <f>'L2'!B17*'L2'!C18-'L2'!C17*'L2'!B18</f>
         <v>146.25</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <f t="shared" si="0"/>
         <v>168.315926999516</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <f t="shared" si="1"/>
         <v>-22.404724713002</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <f t="shared" si="2"/>
         <v>-7.03107137586305</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <f t="shared" si="3"/>
         <v>-41.2206980271091</v>
       </c>
@@ -14428,31 +15589,31 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f>'L2'!C18*'L2'!D19-'L2'!D18*'L2'!C19</f>
         <v>-82.4699051148075</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f>'L2'!D18*'L2'!B19-'L2'!B18*'L2'!D19</f>
         <v>-2.74266159973683</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f>'L2'!B18*'L2'!C19-'L2'!C18*'L2'!B19</f>
         <v>146.25</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <f t="shared" si="0"/>
         <v>167.92221396318</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <f t="shared" si="1"/>
         <v>-23.2987179379634</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <f t="shared" si="2"/>
         <v>-0.774834152198856</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f t="shared" si="3"/>
         <v>-41.3173447172469</v>
       </c>
@@ -14469,31 +15630,31 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <f>-('L2'!C19*'L2'!D2-'L2'!D19*'L2'!C2)</f>
         <v>-1092.82893312546</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <f>-('L2'!D19*'L2'!B2-'L2'!B19*'L2'!D2)</f>
         <v>972.098461421014</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <f>-('L2'!B19*'L2'!C2-'L2'!C19*'L2'!B2)</f>
         <v>1543.5</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <f t="shared" si="0"/>
         <v>2126.41546875798</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <f t="shared" si="1"/>
         <v>-24.3808443595236</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <f t="shared" si="2"/>
         <v>21.687366221404</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <f t="shared" si="3"/>
         <v>-34.435246110568</v>
       </c>
@@ -14520,7 +15681,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -14562,34 +15723,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -14597,31 +15758,31 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <f>'L2'!C2*'L2'!D4-'L2'!D2*'L2'!C4</f>
         <v>68.1366225707045</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>'L2'!D2*'L2'!B4-'L2'!B2*'L2'!D4</f>
         <v>212.953302932885</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <f>'L2'!B2*'L2'!C4-'L2'!C2*'L2'!B4</f>
         <v>238.75</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <f>SQRT(B2*B2+C2*C2+D2*D2)</f>
         <v>327.098259037506</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <f>B2/E2*47.44</f>
         <v>9.88205007347221</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <f>C2/E2*47.44</f>
         <v>30.8852291689442</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <f>-D2/E2*47.44</f>
         <v>-34.6265982378747</v>
       </c>
@@ -14638,39 +15799,39 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f>'L2'!C3*'L2'!D5-'L2'!D3*'L2'!C5</f>
         <v>-3.88592536258534</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>'L2'!D3*'L2'!B5-'L2'!B3*'L2'!D5</f>
         <v>200.022821603777</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>'L2'!B3*'L2'!C5-'L2'!C3*'L2'!B5</f>
         <v>261</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f t="shared" ref="E3:E19" si="0">SQRT(B3*B3+C3*C3+D3*D3)</f>
         <v>328.85442003759</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f t="shared" ref="F3:F19" si="1">B3/E3*47.44</f>
         <v>-0.560577228002519</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G19" si="2">C3/E3*47.44</f>
         <v>28.8549646247677</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <f t="shared" ref="H3:H19" si="3">-D3/E3*47.44</f>
         <v>-37.6514325049506</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <f t="shared" ref="I3:I19" si="4">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <f t="shared" ref="J3:J19" si="5">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
@@ -14679,39 +15840,39 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f>'L2'!C4*'L2'!D6-'L2'!D4*'L2'!C6</f>
         <v>-34.9823358161882</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f>'L2'!D4*'L2'!B6-'L2'!B4*'L2'!D6</f>
         <v>210.559170332872</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f>'L2'!B4*'L2'!C6-'L2'!C4*'L2'!B6</f>
         <v>296.5</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f t="shared" si="0"/>
         <v>365.337074535865</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <f t="shared" si="1"/>
         <v>-4.54255022769952</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <f t="shared" si="2"/>
         <v>27.3416735853641</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f t="shared" si="3"/>
         <v>-38.5013210550005</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <f t="shared" si="4"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <f t="shared" si="5"/>
         <v>30.4809803249618</v>
       </c>
@@ -14720,39 +15881,39 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>'L2'!C5*'L2'!D7-'L2'!D5*'L2'!C7</f>
         <v>-75.06988248193</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f>'L2'!D5*'L2'!B7-'L2'!B5*'L2'!D7</f>
         <v>189.155064279935</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f>'L2'!B5*'L2'!C7-'L2'!C5*'L2'!B7</f>
         <v>301</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f t="shared" si="0"/>
         <v>363.340233938656</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f t="shared" si="1"/>
         <v>-9.801598865993</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <f t="shared" si="2"/>
         <v>24.6972820823227</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f t="shared" si="3"/>
         <v>-39.3004645954262</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f t="shared" si="4"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <f t="shared" si="5"/>
         <v>41.0716467855168</v>
       </c>
@@ -14761,39 +15922,39 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f>'L2'!C6*'L2'!D8-'L2'!D6*'L2'!C8</f>
         <v>-109.111728852548</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f>'L2'!D6*'L2'!B8-'L2'!B6*'L2'!D8</f>
         <v>146.788920273397</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <f>'L2'!B6*'L2'!C8-'L2'!C6*'L2'!B8</f>
         <v>282.25</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
         <v>336.329331144671</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <f t="shared" si="1"/>
         <v>-15.3904519690503</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <f t="shared" si="2"/>
         <v>20.7049035957395</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <f t="shared" si="3"/>
         <v>-39.8119900944363</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <f t="shared" si="4"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <f t="shared" si="5"/>
         <v>46.7134369557949</v>
       </c>
@@ -14802,39 +15963,39 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f>'L2'!C7*'L2'!D9-'L2'!D7*'L2'!C9</f>
         <v>-61.922055689335</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f>'L2'!D7*'L2'!B9-'L2'!B7*'L2'!D9</f>
         <v>162.576267909339</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <f>'L2'!B7*'L2'!C9-'L2'!C7*'L2'!B9</f>
         <v>256</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <f t="shared" si="0"/>
         <v>309.517986340249</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <f t="shared" si="1"/>
         <v>-9.49082913285954</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <f t="shared" si="2"/>
         <v>24.918158200799</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f t="shared" si="3"/>
         <v>-39.2372674156958</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <f t="shared" si="4"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <f t="shared" si="5"/>
         <v>46.7265504432231</v>
       </c>
@@ -14843,39 +16004,39 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>'L2'!C8*'L2'!D10-'L2'!D8*'L2'!C10</f>
         <v>-103.603603001749</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f>'L2'!D8*'L2'!B10-'L2'!B8*'L2'!D10</f>
         <v>178.43153864594</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <f>'L2'!B8*'L2'!C10-'L2'!C8*'L2'!B10</f>
         <v>310.75</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <f t="shared" si="0"/>
         <v>373.010835014885</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <f t="shared" si="1"/>
         <v>-13.17644010584</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <f t="shared" si="2"/>
         <v>22.6931536533667</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f t="shared" si="3"/>
         <v>-39.5215865496554</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <f t="shared" si="4"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <f t="shared" si="5"/>
         <v>41.1094071546692</v>
       </c>
@@ -14884,39 +16045,39 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f>'L2'!C9*'L2'!D11-'L2'!D9*'L2'!C11</f>
         <v>-193.745647385913</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f>'L2'!D9*'L2'!B11-'L2'!B9*'L2'!D11</f>
         <v>66.4427350621318</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <f>'L2'!B9*'L2'!C11-'L2'!C9*'L2'!B11</f>
         <v>324.5</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f t="shared" si="0"/>
         <v>383.734625651013</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <f t="shared" si="1"/>
         <v>-23.9522130597272</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <f t="shared" si="2"/>
         <v>8.21412283554039</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f t="shared" si="3"/>
         <v>-40.1169948473722</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <f t="shared" si="4"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <f t="shared" si="5"/>
         <v>30.5388376877712</v>
       </c>
@@ -14925,39 +16086,39 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f>'L2'!C10*'L2'!D12-'L2'!D10*'L2'!C12</f>
         <v>-157.657309059872</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f>'L2'!D10*'L2'!B12-'L2'!B10*'L2'!D12</f>
         <v>84.892397186085</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <f>'L2'!B10*'L2'!C12-'L2'!C10*'L2'!B12</f>
         <v>299.75</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f t="shared" si="0"/>
         <v>349.159861238373</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <f t="shared" si="1"/>
         <v>-21.4207403888679</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <f t="shared" si="2"/>
         <v>11.534244824775</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f t="shared" si="3"/>
         <v>-40.7267317313196</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <f t="shared" si="4"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <f t="shared" si="5"/>
         <v>16.2885294815216</v>
       </c>
@@ -14966,39 +16127,39 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f>'L2'!C11*'L2'!D13-'L2'!D11*'L2'!C13</f>
         <v>-141.357368712002</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f>'L2'!D11*'L2'!B13-'L2'!B11*'L2'!D13</f>
         <v>128.347601096585</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <f>'L2'!B11*'L2'!C13-'L2'!C11*'L2'!B13</f>
         <v>297.25</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f t="shared" si="0"/>
         <v>353.288232037849</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <f t="shared" si="1"/>
         <v>-18.9816500057634</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <f t="shared" si="2"/>
         <v>17.2346816108205</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f t="shared" si="3"/>
         <v>-39.9151138396516</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <f t="shared" si="4"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <f t="shared" si="5"/>
         <v>0.0755554543581351</v>
       </c>
@@ -15007,39 +16168,39 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f>'L2'!C12*'L2'!D14-'L2'!D12*'L2'!C14</f>
         <v>-161.513643207402</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>'L2'!D12*'L2'!B14-'L2'!B12*'L2'!D14</f>
         <v>39.4716580909189</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <f>'L2'!B12*'L2'!C14-'L2'!C12*'L2'!B14</f>
         <v>275.75</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f t="shared" si="0"/>
         <v>321.998029861324</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <f t="shared" si="1"/>
         <v>-23.7958202323754</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <f t="shared" si="2"/>
         <v>5.81536309597809</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f t="shared" si="3"/>
         <v>-40.6262734142624</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <f t="shared" si="4"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <f t="shared" si="5"/>
         <v>-16.1465225320068</v>
       </c>
@@ -15048,39 +16209,39 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>'L2'!C13*'L2'!D15-'L2'!D13*'L2'!C15</f>
         <v>-169.363099197816</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f>'L2'!D13*'L2'!B15-'L2'!B13*'L2'!D15</f>
         <v>30.4344679753649</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <f>'L2'!B13*'L2'!C15-'L2'!C13*'L2'!B15</f>
         <v>291.75</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f t="shared" si="0"/>
         <v>338.715483423526</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f t="shared" si="1"/>
         <v>-23.7207503617366</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <f t="shared" si="2"/>
         <v>4.26260750219672</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f t="shared" si="3"/>
         <v>-40.862082418281</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <f t="shared" si="4"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <f t="shared" si="5"/>
         <v>-30.4230456457766</v>
       </c>
@@ -15089,39 +16250,39 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>'L2'!C14*'L2'!D16-'L2'!D14*'L2'!C16</f>
         <v>-189.528304235315</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f>'L2'!D14*'L2'!B16-'L2'!B14*'L2'!D16</f>
         <v>63.5192819464876</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <f>'L2'!B14*'L2'!C16-'L2'!C14*'L2'!B16</f>
         <v>330.25</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f t="shared" si="0"/>
         <v>386.03204502387</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <f t="shared" si="1"/>
         <v>-23.2913895849433</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <f t="shared" si="2"/>
         <v>7.80597044826949</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <f t="shared" si="3"/>
         <v>-40.5848690593322</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <f t="shared" si="4"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <f t="shared" si="5"/>
         <v>-41.0337822362874</v>
       </c>
@@ -15130,39 +16291,39 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <f>'L2'!C15*'L2'!D17-'L2'!D15*'L2'!C17</f>
         <v>-174.105825941859</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <f>'L2'!D15*'L2'!B17-'L2'!B15*'L2'!D17</f>
         <v>72.1426226733871</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <f>'L2'!B15*'L2'!C17-'L2'!C15*'L2'!B17</f>
         <v>309.25</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f t="shared" si="0"/>
         <v>362.150464769951</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <f t="shared" si="1"/>
         <v>-22.8070406810841</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <f t="shared" si="2"/>
         <v>9.45034275131892</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f t="shared" si="3"/>
         <v>-40.5102890295042</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <f t="shared" si="4"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
         <f t="shared" si="5"/>
         <v>-46.7002049776354</v>
       </c>
@@ -15171,39 +16332,39 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <f>'L2'!C16*'L2'!D18-'L2'!D16*'L2'!C18</f>
         <v>-165.834114361021</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f>'L2'!D16*'L2'!B18-'L2'!B16*'L2'!D18</f>
         <v>24.4042186991734</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <f>'L2'!B16*'L2'!C18-'L2'!C16*'L2'!B18</f>
         <v>287</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f t="shared" si="0"/>
         <v>332.363534967694</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <f t="shared" si="1"/>
         <v>-23.6703776364984</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <f t="shared" si="2"/>
         <v>3.48334282580464</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f t="shared" si="3"/>
         <v>-40.9650234383367</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <f t="shared" si="4"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <f t="shared" si="5"/>
         <v>-46.7395454066571</v>
       </c>
@@ -15212,39 +16373,39 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <f>'L2'!C17*'L2'!D19-'L2'!D17*'L2'!C19</f>
         <v>-160.065892535773</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <f>'L2'!D17*'L2'!B19-'L2'!B17*'L2'!D19</f>
         <v>-27.417952821761</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <f>'L2'!B17*'L2'!C19-'L2'!C17*'L2'!B19</f>
         <v>292.5</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <f t="shared" si="0"/>
         <v>334.558042931582</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <f t="shared" si="1"/>
         <v>-22.6971854430951</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <f t="shared" si="2"/>
         <v>-3.88783862574884</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <f t="shared" si="3"/>
         <v>-41.4762110586525</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="2">
         <f t="shared" si="4"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
         <f t="shared" si="5"/>
         <v>-41.1470632479638</v>
       </c>
@@ -15253,39 +16414,39 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f>-('L2'!C18*'L2'!D2-'L2'!D18*'L2'!C2)</f>
         <v>-997.719524035898</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f>-('L2'!D18*'L2'!B2-'L2'!B18*'L2'!D2)</f>
         <v>984.74301736936</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f>-('L2'!B18*'L2'!C2-'L2'!C18*'L2'!B2)</f>
         <v>1528.25</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <f t="shared" si="0"/>
         <v>2073.81559483965</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <f t="shared" si="1"/>
         <v>-22.8235405009204</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <f t="shared" si="2"/>
         <v>22.5266937235153</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f t="shared" si="3"/>
         <v>-34.9598007558651</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <f t="shared" si="4"/>
         <v>36.254663040877</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
         <f t="shared" si="5"/>
         <v>-30.5966175874469</v>
       </c>
@@ -15294,45 +16455,45 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <f>-('L2'!C19*'L2'!D3-'L2'!D19*'L2'!C3)</f>
         <v>-1078.35072351006</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <f>-('L2'!D19*'L2'!B3-'L2'!B19*'L2'!D3)</f>
         <v>814.920121938485</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <f>-('L2'!B19*'L2'!C3-'L2'!C19*'L2'!B3)</f>
         <v>1579.5</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <f t="shared" si="0"/>
         <v>2078.88319489935</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <f t="shared" si="1"/>
         <v>-24.6079041135326</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <f t="shared" si="2"/>
         <v>18.596432295771</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <f t="shared" si="3"/>
         <v>-36.0441029990759</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="2">
         <f t="shared" si="4"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <f t="shared" si="5"/>
         <v>-16.3594710714245</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -15358,46 +16519,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -15405,31 +16566,31 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <f>'L2'!C2*'L2'!D4-'L2'!D2*'L2'!C4</f>
         <v>68.1366225707045</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <f>'L2'!D2*'L2'!B4-'L2'!B2*'L2'!D4</f>
         <v>212.953302932885</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <f>'L2'!B2*'L2'!C4-'L2'!C2*'L2'!B4</f>
         <v>238.75</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <f>SQRT(B2*B2+C2*C2+D2*D2)</f>
         <v>327.098259037506</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <f>B2/E2*47.44</f>
         <v>9.88205007347221</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <f>C2/E2*47.44</f>
         <v>30.8852291689442</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <f>-D2/E2*47.44</f>
         <v>-34.6265982378747</v>
       </c>
@@ -15462,39 +16623,39 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f>'L2'!C3*'L2'!D5-'L2'!D3*'L2'!C5</f>
         <v>-3.88592536258534</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>'L2'!D3*'L2'!B5-'L2'!B3*'L2'!D5</f>
         <v>200.022821603777</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>'L2'!B3*'L2'!C5-'L2'!C3*'L2'!B5</f>
         <v>261</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f t="shared" ref="E3:E19" si="0">SQRT(B3*B3+C3*C3+D3*D3)</f>
         <v>328.85442003759</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f t="shared" ref="F3:F19" si="1">B3/E3*47.44</f>
         <v>-0.560577228002519</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G19" si="2">C3/E3*47.44</f>
         <v>28.8549646247677</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <f t="shared" ref="H3:H19" si="3">-D3/E3*47.44</f>
         <v>-37.6514325049506</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <f t="shared" ref="I3:I19" si="4">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <f t="shared" ref="J3:J19" si="5">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
@@ -15507,39 +16668,39 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f>'L2'!C4*'L2'!D6-'L2'!D4*'L2'!C6</f>
         <v>-34.9823358161882</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f>'L2'!D4*'L2'!B6-'L2'!B4*'L2'!D6</f>
         <v>210.559170332872</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f>'L2'!B4*'L2'!C6-'L2'!C4*'L2'!B6</f>
         <v>296.5</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f t="shared" si="0"/>
         <v>365.337074535865</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <f t="shared" si="1"/>
         <v>-4.54255022769952</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <f t="shared" si="2"/>
         <v>27.3416735853641</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f t="shared" si="3"/>
         <v>-38.5013210550005</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <f t="shared" si="4"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <f t="shared" si="5"/>
         <v>30.4809803249618</v>
       </c>
@@ -15552,39 +16713,39 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>'L2'!C5*'L2'!D7-'L2'!D5*'L2'!C7</f>
         <v>-75.06988248193</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f>'L2'!D5*'L2'!B7-'L2'!B5*'L2'!D7</f>
         <v>189.155064279935</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f>'L2'!B5*'L2'!C7-'L2'!C5*'L2'!B7</f>
         <v>301</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f t="shared" si="0"/>
         <v>363.340233938656</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f t="shared" si="1"/>
         <v>-9.801598865993</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <f t="shared" si="2"/>
         <v>24.6972820823227</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f t="shared" si="3"/>
         <v>-39.3004645954262</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f t="shared" si="4"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <f t="shared" si="5"/>
         <v>41.0716467855168</v>
       </c>
@@ -15597,39 +16758,39 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f>'L2'!C6*'L2'!D8-'L2'!D6*'L2'!C8</f>
         <v>-109.111728852548</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <f>'L2'!D6*'L2'!B8-'L2'!B6*'L2'!D8</f>
         <v>146.788920273397</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <f>'L2'!B6*'L2'!C8-'L2'!C6*'L2'!B8</f>
         <v>282.25</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
         <v>336.329331144671</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <f t="shared" si="1"/>
         <v>-15.3904519690503</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <f t="shared" si="2"/>
         <v>20.7049035957395</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <f t="shared" si="3"/>
         <v>-39.8119900944363</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <f t="shared" si="4"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <f t="shared" si="5"/>
         <v>46.7134369557949</v>
       </c>
@@ -15642,39 +16803,39 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f>'L2'!C7*'L2'!D9-'L2'!D7*'L2'!C9</f>
         <v>-61.922055689335</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <f>'L2'!D7*'L2'!B9-'L2'!B7*'L2'!D9</f>
         <v>162.576267909339</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <f>'L2'!B7*'L2'!C9-'L2'!C7*'L2'!B9</f>
         <v>256</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <f t="shared" si="0"/>
         <v>309.517986340249</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <f t="shared" si="1"/>
         <v>-9.49082913285954</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <f t="shared" si="2"/>
         <v>24.918158200799</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f t="shared" si="3"/>
         <v>-39.2372674156958</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <f t="shared" si="4"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <f t="shared" si="5"/>
         <v>46.7265504432231</v>
       </c>
@@ -15687,39 +16848,39 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>'L2'!C8*'L2'!D10-'L2'!D8*'L2'!C10</f>
         <v>-103.603603001749</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <f>'L2'!D8*'L2'!B10-'L2'!B8*'L2'!D10</f>
         <v>178.43153864594</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <f>'L2'!B8*'L2'!C10-'L2'!C8*'L2'!B10</f>
         <v>310.75</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <f t="shared" si="0"/>
         <v>373.010835014885</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <f t="shared" si="1"/>
         <v>-13.17644010584</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <f t="shared" si="2"/>
         <v>22.6931536533667</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <f t="shared" si="3"/>
         <v>-39.5215865496554</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <f t="shared" si="4"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <f t="shared" si="5"/>
         <v>41.1094071546692</v>
       </c>
@@ -15732,39 +16893,39 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f>'L2'!C9*'L2'!D11-'L2'!D9*'L2'!C11</f>
         <v>-193.745647385913</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <f>'L2'!D9*'L2'!B11-'L2'!B9*'L2'!D11</f>
         <v>66.4427350621318</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <f>'L2'!B9*'L2'!C11-'L2'!C9*'L2'!B11</f>
         <v>324.5</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <f t="shared" si="0"/>
         <v>383.734625651013</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <f t="shared" si="1"/>
         <v>-23.9522130597272</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <f t="shared" si="2"/>
         <v>8.21412283554039</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <f t="shared" si="3"/>
         <v>-40.1169948473722</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <f t="shared" si="4"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <f t="shared" si="5"/>
         <v>30.5388376877712</v>
       </c>
@@ -15777,39 +16938,39 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f>'L2'!C10*'L2'!D12-'L2'!D10*'L2'!C12</f>
         <v>-157.657309059872</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <f>'L2'!D10*'L2'!B12-'L2'!B10*'L2'!D12</f>
         <v>84.892397186085</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <f>'L2'!B10*'L2'!C12-'L2'!C10*'L2'!B12</f>
         <v>299.75</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <f t="shared" si="0"/>
         <v>349.159861238373</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <f t="shared" si="1"/>
         <v>-21.4207403888679</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <f t="shared" si="2"/>
         <v>11.534244824775</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f t="shared" si="3"/>
         <v>-40.7267317313196</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <f t="shared" si="4"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <f t="shared" si="5"/>
         <v>16.2885294815216</v>
       </c>
@@ -15822,39 +16983,39 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f>'L2'!C11*'L2'!D13-'L2'!D11*'L2'!C13</f>
         <v>-141.357368712002</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <f>'L2'!D11*'L2'!B13-'L2'!B11*'L2'!D13</f>
         <v>128.347601096585</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <f>'L2'!B11*'L2'!C13-'L2'!C11*'L2'!B13</f>
         <v>297.25</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <f t="shared" si="0"/>
         <v>353.288232037849</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <f t="shared" si="1"/>
         <v>-18.9816500057634</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <f t="shared" si="2"/>
         <v>17.2346816108205</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <f t="shared" si="3"/>
         <v>-39.9151138396516</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <f t="shared" si="4"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <f t="shared" si="5"/>
         <v>0.0755554543581351</v>
       </c>
@@ -15867,39 +17028,39 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f>'L2'!C12*'L2'!D14-'L2'!D12*'L2'!C14</f>
         <v>-161.513643207402</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>'L2'!D12*'L2'!B14-'L2'!B12*'L2'!D14</f>
         <v>39.4716580909189</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <f>'L2'!B12*'L2'!C14-'L2'!C12*'L2'!B14</f>
         <v>275.75</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <f t="shared" si="0"/>
         <v>321.998029861324</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <f t="shared" si="1"/>
         <v>-23.7958202323754</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <f t="shared" si="2"/>
         <v>5.81536309597809</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <f t="shared" si="3"/>
         <v>-40.6262734142624</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <f t="shared" si="4"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <f t="shared" si="5"/>
         <v>-16.1465225320068</v>
       </c>
@@ -15912,39 +17073,39 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>'L2'!C13*'L2'!D15-'L2'!D13*'L2'!C15</f>
         <v>-169.363099197816</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <f>'L2'!D13*'L2'!B15-'L2'!B13*'L2'!D15</f>
         <v>30.4344679753649</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <f>'L2'!B13*'L2'!C15-'L2'!C13*'L2'!B15</f>
         <v>291.75</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f t="shared" si="0"/>
         <v>338.715483423526</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f t="shared" si="1"/>
         <v>-23.7207503617366</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <f t="shared" si="2"/>
         <v>4.26260750219672</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f t="shared" si="3"/>
         <v>-40.862082418281</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <f t="shared" si="4"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <f t="shared" si="5"/>
         <v>-30.4230456457766</v>
       </c>
@@ -15957,39 +17118,39 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>'L2'!C14*'L2'!D16-'L2'!D14*'L2'!C16</f>
         <v>-189.528304235315</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <f>'L2'!D14*'L2'!B16-'L2'!B14*'L2'!D16</f>
         <v>63.5192819464876</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <f>'L2'!B14*'L2'!C16-'L2'!C14*'L2'!B16</f>
         <v>330.25</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <f t="shared" si="0"/>
         <v>386.03204502387</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <f t="shared" si="1"/>
         <v>-23.2913895849433</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <f t="shared" si="2"/>
         <v>7.80597044826949</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <f t="shared" si="3"/>
         <v>-40.5848690593322</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <f t="shared" si="4"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <f t="shared" si="5"/>
         <v>-41.0337822362874</v>
       </c>
@@ -16002,39 +17163,39 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <f>'L2'!C15*'L2'!D17-'L2'!D15*'L2'!C17</f>
         <v>-174.105825941859</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <f>'L2'!D15*'L2'!B17-'L2'!B15*'L2'!D17</f>
         <v>72.1426226733871</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <f>'L2'!B15*'L2'!C17-'L2'!C15*'L2'!B17</f>
         <v>309.25</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f t="shared" si="0"/>
         <v>362.150464769951</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <f t="shared" si="1"/>
         <v>-22.8070406810841</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <f t="shared" si="2"/>
         <v>9.45034275131892</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f t="shared" si="3"/>
         <v>-40.5102890295042</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <f t="shared" si="4"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
         <f t="shared" si="5"/>
         <v>-46.7002049776354</v>
       </c>
@@ -16047,39 +17208,39 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <f>'L2'!C16*'L2'!D18-'L2'!D16*'L2'!C18</f>
         <v>-165.834114361021</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <f>'L2'!D16*'L2'!B18-'L2'!B16*'L2'!D18</f>
         <v>24.4042186991734</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <f>'L2'!B16*'L2'!C18-'L2'!C16*'L2'!B18</f>
         <v>287</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f t="shared" si="0"/>
         <v>332.363534967694</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <f t="shared" si="1"/>
         <v>-23.6703776364984</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <f t="shared" si="2"/>
         <v>3.48334282580464</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f t="shared" si="3"/>
         <v>-40.9650234383367</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <f t="shared" si="4"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <f t="shared" si="5"/>
         <v>-46.7395454066571</v>
       </c>
@@ -16092,39 +17253,39 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <f>'L2'!C17*'L2'!D19-'L2'!D17*'L2'!C19</f>
         <v>-160.065892535773</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <f>'L2'!D17*'L2'!B19-'L2'!B17*'L2'!D19</f>
         <v>-27.417952821761</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <f>'L2'!B17*'L2'!C19-'L2'!C17*'L2'!B19</f>
         <v>292.5</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <f t="shared" si="0"/>
         <v>334.558042931582</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <f t="shared" si="1"/>
         <v>-22.6971854430951</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <f t="shared" si="2"/>
         <v>-3.88783862574884</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <f t="shared" si="3"/>
         <v>-41.4762110586525</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="2">
         <f t="shared" si="4"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
         <f t="shared" si="5"/>
         <v>-41.1470632479638</v>
       </c>
@@ -16137,39 +17298,39 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f>-('L2'!C18*'L2'!D2-'L2'!D18*'L2'!C2)</f>
         <v>-997.719524035898</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <f>-('L2'!D18*'L2'!B2-'L2'!B18*'L2'!D2)</f>
         <v>984.74301736936</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f>-('L2'!B18*'L2'!C2-'L2'!C18*'L2'!B2)</f>
         <v>1528.25</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <f t="shared" si="0"/>
         <v>2073.81559483965</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <f t="shared" si="1"/>
         <v>-22.8235405009204</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <f t="shared" si="2"/>
         <v>22.5266937235153</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <f t="shared" si="3"/>
         <v>-34.9598007558651</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <f t="shared" si="4"/>
         <v>36.254663040877</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
         <f t="shared" si="5"/>
         <v>-30.5966175874469</v>
       </c>
@@ -16182,39 +17343,39 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <f>-('L2'!C19*'L2'!D3-'L2'!D19*'L2'!C3)</f>
         <v>-1078.35072351006</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <f>-('L2'!D19*'L2'!B3-'L2'!B19*'L2'!D3)</f>
         <v>814.920121938485</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <f>-('L2'!B19*'L2'!C3-'L2'!C19*'L2'!B3)</f>
         <v>1579.5</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <f t="shared" si="0"/>
         <v>2078.88319489935</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <f t="shared" si="1"/>
         <v>-24.6079041135326</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <f t="shared" si="2"/>
         <v>18.596432295771</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <f t="shared" si="3"/>
         <v>-36.0441029990759</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="2">
         <f t="shared" si="4"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <f t="shared" si="5"/>
         <v>-16.3594710714245</v>
       </c>
@@ -16224,17 +17385,17 @@
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -16249,427 +17410,487 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="12.8888888888889"/>
-    <col min="3" max="3" width="23.8055555555556" customWidth="1"/>
-    <col min="6" max="6" width="22.4814814814815" customWidth="1"/>
+    <col min="1" max="1" width="10" style="3"/>
+    <col min="2" max="2" width="12.8888888888889" style="4"/>
+    <col min="3" max="3" width="10" style="4"/>
+    <col min="4" max="4" width="23.8055555555556" style="4" customWidth="1"/>
+    <col min="5" max="6" width="10" style="4"/>
+    <col min="7" max="7" width="22.4814814814815" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1">
+    <row r="2" spans="1:7">
+      <c r="A2" s="3">
+        <v>25</v>
+      </c>
+      <c r="B2" s="4">
         <v>884.558479532164</v>
       </c>
-      <c r="B2">
+      <c r="C2" s="4">
         <v>517.09649122807</v>
       </c>
-      <c r="C2">
-        <f>SQRT((A2-'L1'!B2)^2+(B2-'L1'!C2)^2)</f>
+      <c r="D2" s="4">
+        <f>SQRT((B2-'L1'!B2)^2+(C2-'L1'!C2)^2)</f>
         <v>0.905399335451789</v>
       </c>
-      <c r="D2">
+      <c r="E2" s="4">
         <v>884.556923951664</v>
       </c>
-      <c r="E2">
+      <c r="F2" s="4">
         <v>517.094107579775</v>
       </c>
-      <c r="F2">
-        <f>SQRT((D2-'L1'!B2)^2+(E2-'L1'!C2)^2)</f>
+      <c r="G2" s="4">
+        <f>SQRT((E2-'L1'!B2)^2+(F2-'L1'!C2)^2)</f>
         <v>0.907679135649873</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
+    <row r="3" spans="1:7">
+      <c r="A3" s="3">
+        <v>45</v>
+      </c>
+      <c r="B3" s="4">
         <v>880.819573443412</v>
       </c>
-      <c r="B3">
+      <c r="C3" s="4">
         <v>519.536119711042</v>
       </c>
-      <c r="C3">
-        <f>SQRT((A3-'L1'!B3)^2+(B3-'L1'!C3)^2)</f>
+      <c r="D3" s="4">
+        <f>SQRT((B3-'L1'!B3)^2+(C3-'L1'!C3)^2)</f>
         <v>0.497733527910207</v>
       </c>
-      <c r="D3">
+      <c r="E3" s="4">
         <v>880.818200872383</v>
       </c>
-      <c r="E3">
+      <c r="F3" s="4">
         <v>519.534016491958</v>
       </c>
-      <c r="F3">
-        <f>SQRT((D3-'L1'!B3)^2+(E3-'L1'!C3)^2)</f>
+      <c r="G3" s="4">
+        <f>SQRT((E3-'L1'!B3)^2+(F3-'L1'!C3)^2)</f>
         <v>0.500191515891052</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
+    <row r="4" spans="1:7">
+      <c r="A4" s="3">
+        <v>65</v>
+      </c>
+      <c r="B4" s="4">
         <v>877.080667354661</v>
       </c>
-      <c r="B4">
+      <c r="C4" s="4">
         <v>521.975748194014</v>
       </c>
-      <c r="C4">
-        <f>SQRT((A4-'L1'!B4)^2+(B4-'L1'!C4)^2)</f>
+      <c r="D4" s="4">
+        <f>SQRT((B4-'L1'!B4)^2+(C4-'L1'!C4)^2)</f>
         <v>0.420033352890632</v>
       </c>
-      <c r="D4">
+      <c r="E4" s="4">
         <v>877.079477793103</v>
       </c>
-      <c r="E4">
+      <c r="F4" s="4">
         <v>521.973925404142</v>
       </c>
-      <c r="F4">
-        <f>SQRT((D4-'L1'!B4)^2+(E4-'L1'!C4)^2)</f>
+      <c r="G4" s="4">
+        <f>SQRT((E4-'L1'!B4)^2+(F4-'L1'!C4)^2)</f>
         <v>0.42132981266777</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
+    <row r="5" spans="1:7">
+      <c r="A5" s="3">
+        <v>85</v>
+      </c>
+      <c r="B5" s="4">
         <v>873.34176126591</v>
       </c>
-      <c r="B5">
+      <c r="C5" s="4">
         <v>524.415376676986</v>
       </c>
-      <c r="C5">
-        <f>SQRT((A5-'L1'!B5)^2+(B5-'L1'!C5)^2)</f>
+      <c r="D5" s="4">
+        <f>SQRT((B5-'L1'!B5)^2+(C5-'L1'!C5)^2)</f>
         <v>0.352082191646118</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="4">
         <v>873.340754713822</v>
       </c>
-      <c r="E5">
+      <c r="F5" s="4">
         <v>524.413834316325</v>
       </c>
-      <c r="F5">
-        <f>SQRT((D5-'L1'!B5)^2+(E5-'L1'!C5)^2)</f>
+      <c r="G5" s="4">
+        <f>SQRT((E5-'L1'!B5)^2+(F5-'L1'!C5)^2)</f>
         <v>0.351480155961998</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
+    <row r="6" spans="1:7">
+      <c r="A6" s="3">
+        <v>105</v>
+      </c>
+      <c r="B6" s="4">
         <v>869.602855177159</v>
       </c>
-      <c r="B6">
+      <c r="C6" s="4">
         <v>526.855005159959</v>
       </c>
-      <c r="C6">
-        <f>SQRT((A6-'L1'!B6)^2+(B6-'L1'!C6)^2)</f>
+      <c r="D6" s="4">
+        <f>SQRT((B6-'L1'!B6)^2+(C6-'L1'!C6)^2)</f>
         <v>0.369604993291355</v>
       </c>
-      <c r="D6">
+      <c r="E6" s="4">
         <v>869.602031634541</v>
       </c>
-      <c r="E6">
+      <c r="F6" s="4">
         <v>526.853743228508</v>
       </c>
-      <c r="F6">
-        <f>SQRT((D6-'L1'!B6)^2+(E6-'L1'!C6)^2)</f>
+      <c r="G6" s="4">
+        <f>SQRT((E6-'L1'!B6)^2+(F6-'L1'!C6)^2)</f>
         <v>0.368163993571367</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
+    <row r="7" spans="1:7">
+      <c r="A7" s="3">
+        <v>125</v>
+      </c>
+      <c r="B7" s="4">
         <v>865.863949088407</v>
       </c>
-      <c r="B7">
+      <c r="C7" s="4">
         <v>529.294633642931</v>
       </c>
-      <c r="C7">
-        <f>SQRT((A7-'L1'!B7)^2+(B7-'L1'!C7)^2)</f>
+      <c r="D7" s="4">
+        <f>SQRT((B7-'L1'!B7)^2+(C7-'L1'!C7)^2)</f>
         <v>0.468260528444466</v>
       </c>
-      <c r="D7">
+      <c r="E7" s="4">
         <v>865.86330855526</v>
       </c>
-      <c r="E7">
+      <c r="F7" s="4">
         <v>529.293652140692</v>
       </c>
-      <c r="F7">
-        <f>SQRT((D7-'L1'!B7)^2+(E7-'L1'!C7)^2)</f>
+      <c r="G7" s="4">
+        <f>SQRT((E7-'L1'!B7)^2+(F7-'L1'!C7)^2)</f>
         <v>0.467145251563241</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
+    <row r="8" spans="1:7">
+      <c r="A8" s="3">
+        <v>145</v>
+      </c>
+      <c r="B8" s="4">
         <v>862.125042999656</v>
       </c>
-      <c r="B8">
+      <c r="C8" s="4">
         <v>531.734262125903</v>
       </c>
-      <c r="C8">
-        <f>SQRT((A8-'L1'!B8)^2+(B8-'L1'!C8)^2)</f>
+      <c r="D8" s="4">
+        <f>SQRT((B8-'L1'!B8)^2+(C8-'L1'!C8)^2)</f>
         <v>0.442121584792659</v>
       </c>
-      <c r="D8">
+      <c r="E8" s="4">
         <v>862.12458547598</v>
       </c>
-      <c r="E8">
+      <c r="F8" s="4">
         <v>531.733561052875</v>
       </c>
-      <c r="F8">
-        <f>SQRT((D8-'L1'!B8)^2+(E8-'L1'!C8)^2)</f>
+      <c r="G8" s="4">
+        <f>SQRT((E8-'L1'!B8)^2+(F8-'L1'!C8)^2)</f>
         <v>0.442138926430636</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
+    <row r="9" spans="1:7">
+      <c r="A9" s="3">
+        <v>165</v>
+      </c>
+      <c r="B9" s="4">
         <v>858.386136910905</v>
       </c>
-      <c r="B9">
+      <c r="C9" s="4">
         <v>534.173890608875</v>
       </c>
-      <c r="C9">
-        <f>SQRT((A9-'L1'!B9)^2+(B9-'L1'!C9)^2)</f>
+      <c r="D9" s="4">
+        <f>SQRT((B9-'L1'!B9)^2+(C9-'L1'!C9)^2)</f>
         <v>0.683442284167582</v>
       </c>
-      <c r="D9">
+      <c r="E9" s="4">
         <v>858.385862396699</v>
       </c>
-      <c r="E9">
+      <c r="F9" s="4">
         <v>534.173469965058</v>
       </c>
-      <c r="F9">
-        <f>SQRT((D9-'L1'!B9)^2+(E9-'L1'!C9)^2)</f>
+      <c r="G9" s="4">
+        <f>SQRT((E9-'L1'!B9)^2+(F9-'L1'!C9)^2)</f>
         <v>0.68307333890473</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
+    <row r="10" spans="1:7">
+      <c r="A10" s="3">
+        <v>185</v>
+      </c>
+      <c r="B10" s="4">
         <v>854.647230822153</v>
       </c>
-      <c r="B10">
+      <c r="C10" s="4">
         <v>536.613519091847</v>
       </c>
-      <c r="C10">
-        <f>SQRT((A10-'L1'!B10)^2+(B10-'L1'!C10)^2)</f>
+      <c r="D10" s="4">
+        <f>SQRT((B10-'L1'!B10)^2+(C10-'L1'!C10)^2)</f>
         <v>0.185912611744398</v>
       </c>
-      <c r="D10">
+      <c r="E10" s="4">
         <v>854.647139317418</v>
       </c>
-      <c r="E10">
+      <c r="F10" s="4">
         <v>536.613378877242</v>
       </c>
-      <c r="F10">
-        <f>SQRT((D10-'L1'!B10)^2+(E10-'L1'!C10)^2)</f>
+      <c r="G10" s="4">
+        <f>SQRT((E10-'L1'!B10)^2+(F10-'L1'!C10)^2)</f>
         <v>0.185754538396484</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
+    <row r="11" spans="1:7">
+      <c r="A11" s="3">
+        <v>205</v>
+      </c>
+      <c r="B11" s="4">
         <v>850.908324733402</v>
       </c>
-      <c r="B11">
+      <c r="C11" s="4">
         <v>539.053147574819</v>
       </c>
-      <c r="C11">
-        <f>SQRT((A11-'L1'!B11)^2+(B11-'L1'!C11)^2)</f>
+      <c r="D11" s="4">
+        <f>SQRT((B11-'L1'!B11)^2+(C11-'L1'!C11)^2)</f>
         <v>0.10596706665264</v>
       </c>
-      <c r="D11">
+      <c r="E11" s="4">
         <v>850.908416238137</v>
       </c>
-      <c r="E11">
+      <c r="F11" s="4">
         <v>539.053287789425</v>
       </c>
-      <c r="F11">
-        <f>SQRT((D11-'L1'!B11)^2+(E11-'L1'!C11)^2)</f>
+      <c r="G11" s="4">
+        <f>SQRT((E11-'L1'!B11)^2+(F11-'L1'!C11)^2)</f>
         <v>0.105958359456848</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
+    <row r="12" spans="1:7">
+      <c r="A12" s="3">
+        <v>225</v>
+      </c>
+      <c r="B12" s="4">
         <v>847.169418644651</v>
       </c>
-      <c r="B12">
+      <c r="C12" s="4">
         <v>541.492776057791</v>
       </c>
-      <c r="C12">
-        <f>SQRT((A12-'L1'!B12)^2+(B12-'L1'!C12)^2)</f>
+      <c r="D12" s="4">
+        <f>SQRT((B12-'L1'!B12)^2+(C12-'L1'!C12)^2)</f>
         <v>0.521086288715682</v>
       </c>
-      <c r="D12">
+      <c r="E12" s="4">
         <v>847.169693158857</v>
       </c>
-      <c r="E12">
+      <c r="F12" s="4">
         <v>541.493196701608</v>
       </c>
-      <c r="F12">
-        <f>SQRT((D12-'L1'!B12)^2+(E12-'L1'!C12)^2)</f>
+      <c r="G12" s="4">
+        <f>SQRT((E12-'L1'!B12)^2+(F12-'L1'!C12)^2)</f>
         <v>0.521573345407762</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
+    <row r="13" spans="1:7">
+      <c r="A13" s="3">
+        <v>245</v>
+      </c>
+      <c r="B13" s="4">
         <v>843.430512555899</v>
       </c>
-      <c r="B13">
+      <c r="C13" s="4">
         <v>543.932404540764</v>
       </c>
-      <c r="C13">
-        <f>SQRT((A13-'L1'!B13)^2+(B13-'L1'!C13)^2)</f>
+      <c r="D13" s="4">
+        <f>SQRT((B13-'L1'!B13)^2+(C13-'L1'!C13)^2)</f>
         <v>0.610175997282732</v>
       </c>
-      <c r="D13">
+      <c r="E13" s="4">
         <v>843.430970079576</v>
       </c>
-      <c r="E13">
+      <c r="F13" s="4">
         <v>543.933105613792</v>
       </c>
-      <c r="F13">
-        <f>SQRT((D13-'L1'!B13)^2+(E13-'L1'!C13)^2)</f>
+      <c r="G13" s="4">
+        <f>SQRT((E13-'L1'!B13)^2+(F13-'L1'!C13)^2)</f>
         <v>0.610995648256113</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
+    <row r="14" spans="1:7">
+      <c r="A14" s="3">
+        <v>265</v>
+      </c>
+      <c r="B14" s="4">
         <v>839.691606467148</v>
       </c>
-      <c r="B14">
+      <c r="C14" s="4">
         <v>546.372033023736</v>
       </c>
-      <c r="C14">
-        <f>SQRT((A14-'L1'!B14)^2+(B14-'L1'!C14)^2)</f>
+      <c r="D14" s="4">
+        <f>SQRT((B14-'L1'!B14)^2+(C14-'L1'!C14)^2)</f>
         <v>0.483234044594445</v>
       </c>
-      <c r="D14">
+      <c r="E14" s="4">
         <v>839.692247000295</v>
       </c>
-      <c r="E14">
+      <c r="F14" s="4">
         <v>546.373014525975</v>
       </c>
-      <c r="F14">
-        <f>SQRT((D14-'L1'!B14)^2+(E14-'L1'!C14)^2)</f>
+      <c r="G14" s="4">
+        <f>SQRT((E14-'L1'!B14)^2+(F14-'L1'!C14)^2)</f>
         <v>0.483582201301707</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
+    <row r="15" spans="1:7">
+      <c r="A15" s="3">
+        <v>285</v>
+      </c>
+      <c r="B15" s="4">
         <v>835.952700378397</v>
       </c>
-      <c r="B15">
+      <c r="C15" s="4">
         <v>548.811661506708</v>
       </c>
-      <c r="C15">
-        <f>SQRT((A15-'L1'!B15)^2+(B15-'L1'!C15)^2)</f>
+      <c r="D15" s="4">
+        <f>SQRT((B15-'L1'!B15)^2+(C15-'L1'!C15)^2)</f>
         <v>0.194187132064121</v>
       </c>
-      <c r="D15">
+      <c r="E15" s="4">
         <v>835.953523921014</v>
       </c>
-      <c r="E15">
+      <c r="F15" s="4">
         <v>548.812923438158</v>
       </c>
-      <c r="F15">
-        <f>SQRT((D15-'L1'!B15)^2+(E15-'L1'!C15)^2)</f>
+      <c r="G15" s="4">
+        <f>SQRT((E15-'L1'!B15)^2+(F15-'L1'!C15)^2)</f>
         <v>0.192763237959237</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>305</v>
+      </c>
+      <c r="B16" s="4">
         <v>832.213794289646</v>
       </c>
-      <c r="B16">
+      <c r="C16" s="4">
         <v>551.25128998968</v>
       </c>
-      <c r="C16">
-        <f>SQRT((A16-'L1'!B16)^2+(B16-'L1'!C16)^2)</f>
+      <c r="D16" s="4">
+        <f>SQRT((B16-'L1'!B16)^2+(C16-'L1'!C16)^2)</f>
         <v>0.327970528429927</v>
       </c>
-      <c r="D16">
+      <c r="E16" s="4">
         <v>832.214800841734</v>
       </c>
-      <c r="E16">
+      <c r="F16" s="4">
         <v>551.252832350341</v>
       </c>
-      <c r="F16">
-        <f>SQRT((D16-'L1'!B16)^2+(E16-'L1'!C16)^2)</f>
+      <c r="G16" s="4">
+        <f>SQRT((E16-'L1'!B16)^2+(F16-'L1'!C16)^2)</f>
         <v>0.327461827771715</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
+    <row r="17" spans="1:7">
+      <c r="A17" s="3">
+        <v>325</v>
+      </c>
+      <c r="B17" s="4">
         <v>828.474888200894</v>
       </c>
-      <c r="B17">
+      <c r="C17" s="4">
         <v>553.690918472652</v>
       </c>
-      <c r="C17">
-        <f>SQRT((A17-'L1'!B17)^2+(B17-'L1'!C17)^2)</f>
+      <c r="D17" s="4">
+        <f>SQRT((B17-'L1'!B17)^2+(C17-'L1'!C17)^2)</f>
         <v>0.310099972592874</v>
       </c>
-      <c r="D17">
+      <c r="E17" s="4">
         <v>828.476077762453</v>
       </c>
-      <c r="E17">
+      <c r="F17" s="4">
         <v>553.692741262525</v>
       </c>
-      <c r="F17">
-        <f>SQRT((D17-'L1'!B17)^2+(E17-'L1'!C17)^2)</f>
+      <c r="G17" s="4">
+        <f>SQRT((E17-'L1'!B17)^2+(F17-'L1'!C17)^2)</f>
         <v>0.308188587076107</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
+    <row r="18" spans="1:7">
+      <c r="A18" s="3">
+        <v>345</v>
+      </c>
+      <c r="B18" s="4">
         <v>824.735982112143</v>
       </c>
-      <c r="B18">
+      <c r="C18" s="4">
         <v>556.130546955624</v>
       </c>
-      <c r="C18">
-        <f>SQRT((A18-'L1'!B18)^2+(B18-'L1'!C18)^2)</f>
+      <c r="D18" s="4">
+        <f>SQRT((B18-'L1'!B18)^2+(C18-'L1'!C18)^2)</f>
         <v>0.454093599500305</v>
       </c>
-      <c r="D18">
+      <c r="E18" s="4">
         <v>824.737354683172</v>
       </c>
-      <c r="E18">
+      <c r="F18" s="4">
         <v>556.132650174708</v>
       </c>
-      <c r="F18">
-        <f>SQRT((D18-'L1'!B18)^2+(E18-'L1'!C18)^2)</f>
+      <c r="G18" s="4">
+        <f>SQRT((E18-'L1'!B18)^2+(F18-'L1'!C18)^2)</f>
         <v>0.451584384798342</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
+    <row r="19" spans="1:7">
+      <c r="A19" s="3">
+        <v>365</v>
+      </c>
+      <c r="B19" s="4">
         <v>820.997076023392</v>
       </c>
-      <c r="B19">
+      <c r="C19" s="4">
         <v>558.570175438596</v>
       </c>
-      <c r="C19">
-        <f>SQRT((A19-'L1'!B19)^2+(B19-'L1'!C19)^2)</f>
+      <c r="D19" s="4">
+        <f>SQRT((B19-'L1'!B19)^2+(C19-'L1'!C19)^2)</f>
         <v>0.429834506787568</v>
       </c>
-      <c r="D19">
+      <c r="E19" s="4">
         <v>820.998631603891</v>
       </c>
-      <c r="E19">
+      <c r="F19" s="4">
         <v>558.572559086891</v>
       </c>
-      <c r="F19">
-        <f>SQRT((D19-'L1'!B19)^2+(E19-'L1'!C19)^2)</f>
+      <c r="G19" s="4">
+        <f>SQRT((E19-'L1'!B19)^2+(F19-'L1'!C19)^2)</f>
         <v>0.427443103473829</v>
       </c>
     </row>
@@ -16678,4 +17899,506 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2">
+        <f>'L1'!E2-球心降噪!B2</f>
+        <v>9.44152046783597</v>
+      </c>
+      <c r="C2" s="2">
+        <f>-('L1'!F2-球心降噪!C2)</f>
+        <v>-36.90350877193</v>
+      </c>
+      <c r="D2" s="2">
+        <f t="shared" ref="D2:D19" si="0">SQRT(47.44*47.44-B2*B2-C2*C2)</f>
+        <v>28.2761795788526</v>
+      </c>
+      <c r="E2" s="2">
+        <f t="shared" ref="E2:E20" si="1">COS(3.14/9*((A2-25)/20))*47.44</f>
+        <v>47.44</v>
+      </c>
+      <c r="F2" s="2">
+        <f t="shared" ref="F2:F20" si="2">SIN(3.14/9*((A2-25)/20))*47.44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>45</v>
+      </c>
+      <c r="B3" s="2">
+        <f>'L1'!E3-球心降噪!B3</f>
+        <v>13.680426556588</v>
+      </c>
+      <c r="C3" s="2">
+        <f>-('L1'!F3-球心降噪!C3)</f>
+        <v>-36.463880288958</v>
+      </c>
+      <c r="D3" s="2">
+        <f t="shared" si="0"/>
+        <v>27.0884655066016</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" si="1"/>
+        <v>44.5818885096479</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" si="2"/>
+        <v>16.2175465750319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>65</v>
+      </c>
+      <c r="B4" s="2">
+        <f>'L1'!E4-球心降噪!B4</f>
+        <v>16.419332645339</v>
+      </c>
+      <c r="C4" s="2">
+        <f>-('L1'!F4-球心降噪!C4)</f>
+        <v>-35.524251805986</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" si="0"/>
+        <v>26.8139264022748</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" si="1"/>
+        <v>36.3519385786961</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="2"/>
+        <v>30.4809803249618</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>85</v>
+      </c>
+      <c r="B5" s="2">
+        <f>'L1'!E5-球心降噪!B5</f>
+        <v>19.65823873409</v>
+      </c>
+      <c r="C5" s="2">
+        <f>-('L1'!F5-球心降噪!C5)</f>
+        <v>-34.0846233230139</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>26.5018056517245</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="1"/>
+        <v>23.7418076465493</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="2"/>
+        <v>41.0716467855168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>105</v>
+      </c>
+      <c r="B6" s="2">
+        <f>'L1'!E6-球心降噪!B6</f>
+        <v>22.897144822841</v>
+      </c>
+      <c r="C6" s="2">
+        <f>-('L1'!F6-球心降噪!C6)</f>
+        <v>-32.144994840041</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>26.3243929786725</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="1"/>
+        <v>8.27093753917763</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="2"/>
+        <v>46.7134369557949</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>125</v>
+      </c>
+      <c r="B7" s="2">
+        <f>'L1'!E7-球心降噪!B7</f>
+        <v>26.136050911593</v>
+      </c>
+      <c r="C7" s="2">
+        <f>-('L1'!F7-球心降噪!C7)</f>
+        <v>-29.705366357069</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>26.1734914052163</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="1"/>
+        <v>-8.19652875776856</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="2"/>
+        <v>46.7265504432231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>145</v>
+      </c>
+      <c r="B8" s="2">
+        <f>'L1'!E8-球心降噪!B8</f>
+        <v>28.874957000344</v>
+      </c>
+      <c r="C8" s="2">
+        <f>-('L1'!F8-球心降噪!C8)</f>
+        <v>-27.765737874097</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>25.4136628319339</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="1"/>
+        <v>-23.6763646574306</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="2"/>
+        <v>41.1094071546692</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>165</v>
+      </c>
+      <c r="B9" s="2">
+        <f>'L1'!E9-球心降噪!B9</f>
+        <v>31.613863089095</v>
+      </c>
+      <c r="C9" s="2">
+        <f>-('L1'!F9-球心降噪!C9)</f>
+        <v>-25.326109391125</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>24.6922142322782</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="1"/>
+        <v>-36.3033468523216</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="2"/>
+        <v>30.5388376877712</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>185</v>
+      </c>
+      <c r="B10" s="2">
+        <f>'L1'!E10-球心降噪!B10</f>
+        <v>33.852769177847</v>
+      </c>
+      <c r="C10" s="2">
+        <f>-('L1'!F10-球心降噪!C10)</f>
+        <v>-22.386480908153</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>24.5639795542236</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="1"/>
+        <v>-44.5560030448154</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="2"/>
+        <v>16.2885294815216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>205</v>
+      </c>
+      <c r="B11" s="2">
+        <f>'L1'!E11-球心降噪!B11</f>
+        <v>35.591675266598</v>
+      </c>
+      <c r="C11" s="2">
+        <f>-('L1'!F11-球心降噪!C11)</f>
+        <v>-18.946852425181</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>24.996060387498</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="1"/>
+        <v>-47.4399398331545</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="2"/>
+        <v>0.0755554543581351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>225</v>
+      </c>
+      <c r="B12" s="2">
+        <f>'L1'!E12-球心降噪!B12</f>
+        <v>37.330581355349</v>
+      </c>
+      <c r="C12" s="2">
+        <f>-('L1'!F12-球心降噪!C12)</f>
+        <v>-15.507223942209</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>24.8295650642103</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="1"/>
+        <v>-44.6076608905174</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="2"/>
+        <v>-16.1465225320068</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>245</v>
+      </c>
+      <c r="B13" s="2">
+        <f>'L1'!E13-球心降噪!B13</f>
+        <v>38.569487444101</v>
+      </c>
+      <c r="C13" s="2">
+        <f>-('L1'!F13-球心降噪!C13)</f>
+        <v>-12.067595459236</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>24.845952952776</v>
+      </c>
+      <c r="E13" s="2">
+        <f t="shared" si="1"/>
+        <v>-36.4004380967454</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="2"/>
+        <v>-30.4230456457766</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>265</v>
+      </c>
+      <c r="B14" s="2">
+        <f>'L1'!E14-球心降噪!B14</f>
+        <v>39.8083935328521</v>
+      </c>
+      <c r="C14" s="2">
+        <f>-('L1'!F14-球心降噪!C14)</f>
+        <v>-9.12796697626402</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>24.1355675966781</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="1"/>
+        <v>-23.8071904135063</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="2"/>
+        <v>-41.0337822362874</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>285</v>
+      </c>
+      <c r="B15" s="2">
+        <f>'L1'!E15-球心降噪!B15</f>
+        <v>40.547299621603</v>
+      </c>
+      <c r="C15" s="2">
+        <f>-('L1'!F15-球心降噪!C15)</f>
+        <v>-5.68833849329201</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>23.9606531334538</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="1"/>
+        <v>-8.3453253409821</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="2"/>
+        <v>-46.7002049776354</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>305</v>
+      </c>
+      <c r="B16" s="2">
+        <f>'L1'!E16-球心降噪!B16</f>
+        <v>40.786205710354</v>
+      </c>
+      <c r="C16" s="2">
+        <f>-('L1'!F16-球心降噪!C16)</f>
+        <v>-1.74871001032</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>24.1656995978286</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="1"/>
+        <v>8.12209918549612</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="2"/>
+        <v>-46.7395454066571</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>325</v>
+      </c>
+      <c r="B17" s="2">
+        <f>'L1'!E17-球心降噪!B17</f>
+        <v>41.525111799106</v>
+      </c>
+      <c r="C17" s="2">
+        <f>-('L1'!F17-球心降噪!C17)</f>
+        <v>1.69091847265202</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="0"/>
+        <v>22.877051488131</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="1"/>
+        <v>23.6108616121494</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="2"/>
+        <v>-41.1470632479638</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>345</v>
+      </c>
+      <c r="B18" s="2">
+        <f>'L1'!E18-球心降噪!B18</f>
+        <v>41.264017887857</v>
+      </c>
+      <c r="C18" s="2">
+        <f>-('L1'!F18-球心降噪!C18)</f>
+        <v>5.13054695562403</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="0"/>
+        <v>22.8366353845472</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="1"/>
+        <v>36.254663040877</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="2"/>
+        <v>-30.5966175874469</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>365</v>
+      </c>
+      <c r="B19" s="2">
+        <f>'L1'!E19-球心降噪!B19</f>
+        <v>40.502923976608</v>
+      </c>
+      <c r="C19" s="2">
+        <f>-('L1'!F19-球心降噪!C19)</f>
+        <v>8.57017543859604</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="0"/>
+        <v>23.1650349081713</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="1"/>
+        <v>44.5300045616798</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="2"/>
+        <v>-16.3594710714245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>385</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="1"/>
+        <v>47.4397593327705</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>-0.151110717066466</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/label.xlsx
+++ b/label.xlsx
@@ -20,7 +20,7 @@
     <sheet name="L4" sheetId="5" r:id="rId6"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId7"/>
     <sheet name="球心降噪" sheetId="8" r:id="rId8"/>
-    <sheet name="旋转轴与速度" sheetId="9" r:id="rId9"/>
+    <sheet name="旋转轴与投影" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
   <si>
     <t>序号</t>
   </si>
@@ -499,6 +499,15 @@
     </r>
   </si>
   <si>
+    <t>X6去噪</t>
+  </si>
+  <si>
+    <t>Y6去噪</t>
+  </si>
+  <si>
+    <t>Z6去噪</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -820,17 +829,60 @@
   <si>
     <t>分布优化相较于原始点距离</t>
   </si>
+  <si>
+    <t>平面方程</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>X6(降噪)</t>
+  </si>
+  <si>
+    <t>Y6(降噪)</t>
+  </si>
+  <si>
+    <t>Z6(降噪)</t>
+  </si>
+  <si>
+    <t>X6(未降噪)</t>
+  </si>
+  <si>
+    <t>Y6(未降噪)</t>
+  </si>
+  <si>
+    <t>X6(对比)</t>
+  </si>
+  <si>
+    <t>Y6(对比)</t>
+  </si>
+  <si>
+    <t>球心降噪</t>
+  </si>
+  <si>
+    <t>球心未降噪</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1446,9 +1498,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1456,11 +1523,8 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1974,13 +2038,197 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.0276903713027061"/>
+          <c:y val="0.113283796115239"/>
+          <c:w val="0.944241661422278"/>
+          <c:h val="0.74814235432147"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="smooth"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"YUAN"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>YUAN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'L2'!$E$2:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>47.44</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44.5818885096479</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.3519385786961</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.7418076465493</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.27093753917763</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-8.19652875776856</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-23.6763646574306</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-36.3033468523216</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-44.5560030448154</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-47.4399398331545</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-44.6076608905174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-36.4004380967454</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-23.8071904135063</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-8.3453253409821</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.12209918549612</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>23.6108616121494</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>36.254663040877</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44.5300045616798</c:v>
+                </c:pt>
+                <c:pt idx="18" c:formatCode="General">
+                  <c:v>47.4397593327705</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'L2'!$F$2:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.2175465750319</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.4809803249618</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41.0716467855168</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46.7134369557949</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46.7265504432231</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>41.1094071546692</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.5388376877712</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16.2885294815216</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0755554543581351</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-16.1465225320068</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-30.4230456457766</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-41.0337822362874</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-46.7002049776354</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-46.7395454066571</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-41.1470632479638</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-30.5966175874469</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-16.3594710714245</c:v>
+                </c:pt>
+                <c:pt idx="18" c:formatCode="General">
+                  <c:v>-0.151110717066466</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"降噪前"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>降噪前</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -2137,15 +2385,15 @@
           <c:smooth val="1"/>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="2"/>
+          <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>"YUAN"</c:f>
+              <c:f>"降噪后"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>YUAN</c:v>
+                  <c:v>降噪后</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2153,146 +2401,152 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:delete val="1"/>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L2'!$E$2:$E$20</c:f>
+              <c:f>'L2'!$H$2:$H$19</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>47.44</c:v>
+                  <c:v>9.44152046783597</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.5818885096479</c:v>
+                  <c:v>13.680426556588</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>36.3519385786961</c:v>
+                  <c:v>16.419332645339</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23.7418076465493</c:v>
+                  <c:v>19.65823873409</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.27093753917763</c:v>
+                  <c:v>22.897144822841</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-8.19652875776856</c:v>
+                  <c:v>26.136050911593</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-23.6763646574306</c:v>
+                  <c:v>28.874957000344</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-36.3033468523216</c:v>
+                  <c:v>31.613863089095</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-44.5560030448154</c:v>
+                  <c:v>33.852769177847</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-47.4399398331545</c:v>
+                  <c:v>35.591675266598</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-44.6076608905174</c:v>
+                  <c:v>37.330581355349</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-36.4004380967454</c:v>
+                  <c:v>38.569487444101</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-23.8071904135063</c:v>
+                  <c:v>39.8083935328521</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-8.3453253409821</c:v>
+                  <c:v>40.547299621603</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.12209918549612</c:v>
+                  <c:v>40.786205710354</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>23.6108616121494</c:v>
+                  <c:v>41.525111799106</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>36.254663040877</c:v>
+                  <c:v>41.264017887857</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>44.5300045616798</c:v>
-                </c:pt>
-                <c:pt idx="18" c:formatCode="General">
-                  <c:v>47.4397593327705</c:v>
+                  <c:v>40.502923976608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L2'!$F$2:$F$20</c:f>
+              <c:f>'L2'!$I$2:$I$19</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-36.90350877193</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.2175465750319</c:v>
+                  <c:v>-36.463880288958</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30.4809803249618</c:v>
+                  <c:v>-35.524251805986</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41.0716467855168</c:v>
+                  <c:v>-34.0846233230139</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.7134369557949</c:v>
+                  <c:v>-32.144994840041</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.7265504432231</c:v>
+                  <c:v>-29.705366357069</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>41.1094071546692</c:v>
+                  <c:v>-27.765737874097</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30.5388376877712</c:v>
+                  <c:v>-25.326109391125</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16.2885294815216</c:v>
+                  <c:v>-22.386480908153</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0755554543581351</c:v>
+                  <c:v>-18.946852425181</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-16.1465225320068</c:v>
+                  <c:v>-15.507223942209</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-30.4230456457766</c:v>
+                  <c:v>-12.067595459236</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-41.0337822362874</c:v>
+                  <c:v>-9.12796697626402</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-46.7002049776354</c:v>
+                  <c:v>-5.68833849329201</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-46.7395454066571</c:v>
+                  <c:v>-1.74871001032</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-41.1470632479638</c:v>
+                  <c:v>1.69091847265202</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-30.5966175874469</c:v>
+                  <c:v>5.13054695562403</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-16.3594710714245</c:v>
-                </c:pt>
-                <c:pt idx="18" c:formatCode="General">
-                  <c:v>-0.151110717066466</c:v>
+                  <c:v>8.57017543859604</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2440,6 +2694,46 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.294021397105098"/>
+          <c:y val="0.90196845261374"/>
+          <c:w val="0.406041535556954"/>
+          <c:h val="0.0778255768478686"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -6388,39 +6682,39 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
+  <c:clrMapOvr bg1="lt1" tx1="dk1" bg2="lt2" tx2="dk2" accent1="accent1" accent2="accent2" accent3="accent3" accent4="accent4" accent5="accent5" accent6="accent6" hlink="hlink" folHlink="folHlink"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr lang="zh-CN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="zh-CN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:cs typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:sym typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="zh-CN" altLang="en-US"/>
-              <a:t>标志点位置图</a:t>
+              <a:t>拟合平面经旋转后在</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-CN"/>
-              <a:t>-XY</a:t>
+              <a:t>XY</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="zh-CN" altLang="en-US"/>
-              <a:t>平面投影</a:t>
+              <a:rPr altLang="en-US"/>
+              <a:t>平面上的投影</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -6441,8 +6735,194 @@
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"圆"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>圆</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'L2'!$E$2:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>47.44</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44.5818885096479</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.3519385786961</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23.7418076465493</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.27093753917763</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-8.19652875776856</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-23.6763646574306</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-36.3033468523216</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-44.5560030448154</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-47.4399398331545</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-44.6076608905174</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-36.4004380967454</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-23.8071904135063</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-8.3453253409821</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.12209918549612</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>23.6108616121494</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>36.254663040877</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44.5300045616798</c:v>
+                </c:pt>
+                <c:pt idx="18" c:formatCode="General">
+                  <c:v>47.4397593327705</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'L2'!$F$2:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.2175465750319</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.4809803249618</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>41.0716467855168</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46.7134369557949</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46.7265504432231</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>41.1094071546692</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.5388376877712</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16.2885294815216</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0755554543581351</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-16.1465225320068</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-30.4230456457766</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-41.0337822362874</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-46.7002049776354</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-46.7395454066571</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-41.1470632479638</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-30.5966175874469</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-16.3594710714245</c:v>
+                </c:pt>
+                <c:pt idx="18" c:formatCode="General">
+                  <c:v>-0.151110717066466</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"降噪后投影"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>降噪后投影</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -6472,126 +6952,126 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>旋转轴与速度!$B$2:$B$19</c:f>
+              <c:f>旋转轴与投影!$H$2:$H$20</c:f>
               <c:numCache>
-                <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="18"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>9.44152046783597</c:v>
+                  <c:v>37.5518708493067</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.680426556588</c:v>
+                  <c:v>38.8752401167859</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.419332645339</c:v>
+                  <c:v>39.1314806914079</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.65823873409</c:v>
+                  <c:v>39.1344588684106</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>22.897144822841</c:v>
+                  <c:v>38.6807080739839</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26.136050911593</c:v>
+                  <c:v>37.7702283081298</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>28.874957000344</c:v>
+                  <c:v>37.1130109398945</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>31.613863089095</c:v>
+                  <c:v>35.9990646002306</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33.852769177847</c:v>
+                  <c:v>34.224922715329</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>35.591675266598</c:v>
+                  <c:v>31.790585285189</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>37.330581355349</c:v>
+                  <c:v>29.356247855049</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38.569487444101</c:v>
+                  <c:v>26.7184438510991</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>39.8083935328521</c:v>
+                  <c:v>24.5373688185784</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>40.547299621603</c:v>
+                  <c:v>21.6960982408196</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>40.786205710354</c:v>
+                  <c:v>18.1946321178227</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>41.525111799106</c:v>
+                  <c:v>15.3533615400643</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41.264017887857</c:v>
+                  <c:v>12.1051578146867</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>40.502923976608</c:v>
+                  <c:v>8.65348751549973</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>旋转轴与速度!$C$2:$C$19</c:f>
+              <c:f>旋转轴与投影!$I$2:$I$20</c:f>
               <c:numCache>
-                <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="18"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>-36.90350877193</c:v>
+                  <c:v>27.5451356774842</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-36.463880288958</c:v>
+                  <c:v>26.745727778357</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-35.524251805986</c:v>
+                  <c:v>26.7451004812523</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-34.0846233230139</c:v>
+                  <c:v>26.769476112824</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-32.144994840041</c:v>
+                  <c:v>26.9471925942159</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-29.705366357069</c:v>
+                  <c:v>27.1705375759781</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-27.765737874097</c:v>
+                  <c:v>26.7252667800205</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-25.326109391125</c:v>
+                  <c:v>26.3374401962207</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-22.386480908153</c:v>
+                  <c:v>26.5162265042296</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-18.946852425181</c:v>
+                  <c:v>27.2288746500686</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-15.507223942209</c:v>
+                  <c:v>27.3456277404456</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-12.067595459236</c:v>
+                  <c:v>27.6012647904757</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-9.12796697626402</c:v>
+                  <c:v>27.114147761045</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-5.68833849329201</c:v>
+                  <c:v>27.1361592332932</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1.74871001032</c:v>
+                  <c:v>27.5124857914732</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.69091847265202</c:v>
+                  <c:v>26.4257521763015</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.13054695562403</c:v>
+                  <c:v>26.4952993837756</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.57017543859604</c:v>
+                  <c:v>26.8888301505863</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6599,15 +7079,15 @@
           <c:smooth val="1"/>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="2"/>
+          <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>"YUAN"</c:f>
+              <c:f>"未降噪投影"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>YUAN</c:v>
+                  <c:v>未降噪投影</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6615,146 +7095,321 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:dLbls>
             <c:delete val="1"/>
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>旋转轴与速度!$E$2:$E$20</c:f>
+              <c:f>旋转轴与投影!$L$2:$L$19</c:f>
               <c:numCache>
-                <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="19"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>47.44</c:v>
+                  <c:v>35.8845149077707</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.5818885096479</c:v>
+                  <c:v>35.8369608285804</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>36.3519385786961</c:v>
+                  <c:v>35.3072748645608</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23.7418076465493</c:v>
+                  <c:v>33.7598267917936</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.27093753917763</c:v>
+                  <c:v>32.2242672388239</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-8.19652875776856</c:v>
+                  <c:v>29.6828340969042</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-23.6763646574306</c:v>
+                  <c:v>27.6591983992064</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-36.3033468523216</c:v>
+                  <c:v>25.6236741817111</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-44.5560030448154</c:v>
+                  <c:v>22.0942002305375</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-47.4399398331545</c:v>
+                  <c:v>18.5766147991616</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-44.6076608905174</c:v>
+                  <c:v>15.5530497724125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-36.4004380967454</c:v>
+                  <c:v>12.0354643410365</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-23.8071904135063</c:v>
+                  <c:v>9.02973209398376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-8.3453253409821</c:v>
+                  <c:v>5.01812625798092</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.12209918549612</c:v>
+                  <c:v>1.01246468187686</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>23.6108616121494</c:v>
+                  <c:v>-2.49323222970154</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>36.254663040877</c:v>
+                  <c:v>-5.98704062148238</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>44.5300045616798</c:v>
-                </c:pt>
-                <c:pt idx="18" c:formatCode="General">
-                  <c:v>47.4397593327705</c:v>
+                  <c:v>-9.48084901326322</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>旋转轴与速度!$F$2:$F$20</c:f>
+              <c:f>旋转轴与投影!$M$2:$M$19</c:f>
               <c:numCache>
-                <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="19"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>30.5971501314081</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.2175465750319</c:v>
+                  <c:v>29.6397029782784</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30.4809803249618</c:v>
+                  <c:v>29.3495555866634</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41.0716467855168</c:v>
+                  <c:v>29.24349688588</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.7134369557949</c:v>
+                  <c:v>29.1601230450425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.7265504432231</c:v>
+                  <c:v>29.3801203464063</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>41.1094071546692</c:v>
+                  <c:v>29.8079942642832</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30.5388376877712</c:v>
+                  <c:v>28.847313317116</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16.2885294815216</c:v>
+                  <c:v>29.3576299662944</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0755554543581351</c:v>
+                  <c:v>30.4082688974515</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-16.1465225320068</c:v>
+                  <c:v>29.8976424367853</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-30.4230456457766</c:v>
+                  <c:v>29.8204233095988</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-41.0337822362874</c:v>
+                  <c:v>30.4389972634051</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-46.7002049776354</c:v>
+                  <c:v>30.1827343340946</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-46.7395454066571</c:v>
+                  <c:v>29.9912856259764</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-41.1470632479638</c:v>
+                  <c:v>29.1546775279477</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-30.5966175874469</c:v>
+                  <c:v>29.3903860480841</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-16.3594710714245</c:v>
-                </c:pt>
-                <c:pt idx="18" c:formatCode="General">
-                  <c:v>-0.151110717066466</c:v>
+                  <c:v>29.0913317657002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"对比"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>对比</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>旋转轴与投影!$O$2:$O$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>35.9498521970467</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35.9289443984996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.415883854705</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33.8949965470498</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32.3793361890314</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.8610760167891</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>27.8506494387047</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25.8349959109836</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22.3219763489726</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18.8141837365984</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15.8037708191086</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.2959782067344</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.2934057136997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.28823340644118</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.28567457400103</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-2.21689108873639</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-5.71422980183706</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-9.21156851493772</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>旋转轴与投影!$P$2:$P$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>30.5508991459797</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29.5862794402994</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29.2922634575459</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29.1808549636835</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29.0938654047332</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.3105261921941</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29.7371818700338</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28.7731762903532</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29.2830239091722</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30.3350689858281</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>29.8240289178094</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>29.7479084974178</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30.368968485558</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.1151496313741</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>29.9270266115456</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>29.0930381126321</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>29.3333864221325</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>29.0388261600757</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6769,41 +7424,28 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="-92832768"/>
-        <c:axId val="-92843104"/>
+        <c:axId val="50697616"/>
+        <c:axId val="858172422"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="-92832768"/>
+        <c:axId val="50697616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0_ " sourceLinked="0"/>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
+                <a:alpha val="25000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -6811,60 +7453,48 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:cs typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:sym typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-92843104"/>
+        <c:crossAx val="858172422"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-92843104"/>
+        <c:axId val="858172422"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0_ " sourceLinked="0"/>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
+                <a:alpha val="25000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -6872,28 +7502,48 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:cs typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:sym typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-92832768"/>
+        <c:crossAx val="50697616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="50000"/>
+              <a:lumOff val="50000"/>
+              <a:alpha val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -6901,25 +7551,41 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-    </c:plotArea>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1" forceAA="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              <a:cs typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              <a:sym typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
-        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{634241fc-8f45-4b1e-aaae-5c52da3a8e38}"/>
-      </c:ext>
-    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+          <a:alpha val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -6931,13 +7597,26 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr lang="zh-CN"/>
+        <a:defRPr lang="zh-CN">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:latin typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+          <a:ea typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+          <a:cs typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+          <a:sym typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+        </a:defRPr>
       </a:pPr>
     </a:p>
   </c:txPr>
-  <c:externalData r:id="rId1">
-    <c:autoUpdate val="0"/>
-  </c:externalData>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
@@ -11472,7 +12151,7 @@
 </file>
 
 <file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10172">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -11499,8 +12178,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -11541,7 +12220,7 @@
         <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -11566,20 +12245,29 @@
         </a:solidFill>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:noFill/>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -11618,7 +12306,7 @@
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
@@ -11626,6 +12314,7 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
+      <a:effectLst/>
     </cs:spPr>
   </cs:dataPointMarker>
   <cs:dataPointMarkerLayout symbol="circle" size="5"/>
@@ -11758,9 +12447,8 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -11843,6 +12531,17 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -11889,11 +12588,11 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -11961,8 +12660,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -12026,16 +12725,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>14286</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>492760</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>17145</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>143510</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12043,8 +12742,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4334510" y="19050"/>
-        <a:ext cx="3681095" cy="4339590"/>
+        <a:off x="6931660" y="200025"/>
+        <a:ext cx="4588510" cy="4952365"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12267,24 +12966,24 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>14286</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>356870</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>59055</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>554990</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvPr id="2" name="图表 1" descr="7b0a202020202263686172745265734964223a20223139393836313830220a7d0a"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4334510" y="19050"/>
-        <a:ext cx="3681095" cy="4339590"/>
+        <a:off x="6809105" y="3716655"/>
+        <a:ext cx="6553200" cy="5982335"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -12544,6 +13243,250 @@
 </a:theme>
 </file>
 
+<file path=xl/theme/themeOverride1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:themeOverride xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <a:clrScheme name="WPS">
+    <a:dk1>
+      <a:sysClr val="windowText" lastClr="000000"/>
+    </a:dk1>
+    <a:lt1>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:lt1>
+    <a:dk2>
+      <a:srgbClr val="44546A"/>
+    </a:dk2>
+    <a:lt2>
+      <a:srgbClr val="E7E6E6"/>
+    </a:lt2>
+    <a:accent1>
+      <a:srgbClr val="4874CB"/>
+    </a:accent1>
+    <a:accent2>
+      <a:srgbClr val="EE822F"/>
+    </a:accent2>
+    <a:accent3>
+      <a:srgbClr val="F2BA02"/>
+    </a:accent3>
+    <a:accent4>
+      <a:srgbClr val="75BD42"/>
+    </a:accent4>
+    <a:accent5>
+      <a:srgbClr val="30C0B4"/>
+    </a:accent5>
+    <a:accent6>
+      <a:srgbClr val="E54C5E"/>
+    </a:accent6>
+    <a:hlink>
+      <a:srgbClr val="0026E5"/>
+    </a:hlink>
+    <a:folHlink>
+      <a:srgbClr val="7E1FAD"/>
+    </a:folHlink>
+  </a:clrScheme>
+  <a:fontScheme name="WPS">
+    <a:majorFont>
+      <a:latin typeface="Calibri Light"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Times New Roman"/>
+      <a:font script="Hebr" typeface="Times New Roman"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="MoolBoran"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Times New Roman"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:majorFont>
+    <a:minorFont>
+      <a:latin typeface="Calibri"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="宋体"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Arial"/>
+      <a:font script="Hebr" typeface="Arial"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="DaunPenh"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Arial"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+    </a:minorFont>
+  </a:fontScheme>
+  <a:fmtScheme name="WPS">
+    <a:fillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:lumOff val="17500"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="2700000" scaled="0"/>
+      </a:gradFill>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:hueOff val="-2520000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="2700000" scaled="0"/>
+      </a:gradFill>
+    </a:fillStyleLst>
+    <a:lnStyleLst>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:hueOff val="-4200000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="2700000" scaled="1"/>
+        </a:gradFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+    </a:lnStyleLst>
+    <a:effectStyleLst>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:schemeClr val="phClr">
+              <a:alpha val="60000"/>
+            </a:schemeClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+        </a:effectLst>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="63000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+    </a:effectStyleLst>
+    <a:bgFillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:tint val="95000"/>
+          <a:satMod val="170000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="93000"/>
+              <a:satMod val="150000"/>
+              <a:shade val="98000"/>
+              <a:lumMod val="102000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="50000">
+            <a:schemeClr val="phClr">
+              <a:tint val="98000"/>
+              <a:satMod val="130000"/>
+              <a:shade val="90000"/>
+              <a:lumMod val="103000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="63000"/>
+              <a:satMod val="120000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </a:bgFillStyleLst>
+  </a:fmtScheme>
+</a:themeOverride>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -12551,31 +13494,31 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -13115,22 +14058,22 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -13138,23 +14081,23 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <f>(L0!B2+L0!D2)/2</f>
         <v>884.5</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="7">
         <f>(L0!C2+L0!E2)/2</f>
         <v>518</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="7">
         <f>(L0!D2-L0!B2+L0!E2-L0!C2)/4</f>
         <v>48.75</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="7">
         <f>(L0!F2+L0!H2)/2</f>
         <v>894</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="7">
         <f>(L0!G2+L0!I2)/2</f>
         <v>554</v>
       </c>
@@ -13163,23 +14106,23 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <f>(L0!B3+L0!D3)/2</f>
         <v>881</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <f>(L0!C3+L0!E3)/2</f>
         <v>520</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="7">
         <f>(L0!D3-L0!B3+L0!E3-L0!C3)/4</f>
         <v>48</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="7">
         <f>(L0!F3+L0!H3)/2</f>
         <v>894.5</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="7">
         <f>(L0!G3+L0!I3)/2</f>
         <v>556</v>
       </c>
@@ -13188,23 +14131,23 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="7">
         <f>(L0!B4+L0!D4)/2</f>
         <v>877.5</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="7">
         <f>(L0!C4+L0!E4)/2</f>
         <v>522</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="7">
         <f>(L0!D4-L0!B4+L0!E4-L0!C4)/4</f>
         <v>48.25</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="7">
         <f>(L0!F4+L0!H4)/2</f>
         <v>893.5</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="7">
         <f>(L0!G4+L0!I4)/2</f>
         <v>557.5</v>
       </c>
@@ -13213,23 +14156,23 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <f>(L0!B5+L0!D5)/2</f>
         <v>873</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="7">
         <f>(L0!C5+L0!E5)/2</f>
         <v>524.5</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="7">
         <f>(L0!D5-L0!B5+L0!E5-L0!C5)/4</f>
         <v>47.75</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="7">
         <f>(L0!F5+L0!H5)/2</f>
         <v>893</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="7">
         <f>(L0!G5+L0!I5)/2</f>
         <v>558.5</v>
       </c>
@@ -13238,23 +14181,23 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="7">
         <f>(L0!B6+L0!D6)/2</f>
         <v>869.5</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="7">
         <f>(L0!C6+L0!E6)/2</f>
         <v>526.5</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="7">
         <f>(L0!D6-L0!B6+L0!E6-L0!C6)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="7">
         <f>(L0!F6+L0!H6)/2</f>
         <v>892.5</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="7">
         <f>(L0!G6+L0!I6)/2</f>
         <v>559</v>
       </c>
@@ -13263,23 +14206,23 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="7">
         <f>(L0!B7+L0!D7)/2</f>
         <v>865.5</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="7">
         <f>(L0!C7+L0!E7)/2</f>
         <v>529</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="7">
         <f>(L0!D7-L0!B7+L0!E7-L0!C7)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="7">
         <f>(L0!F7+L0!H7)/2</f>
         <v>892</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="7">
         <f>(L0!G7+L0!I7)/2</f>
         <v>559</v>
       </c>
@@ -13288,23 +14231,23 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <f>(L0!B8+L0!D8)/2</f>
         <v>862.5</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="7">
         <f>(L0!C8+L0!E8)/2</f>
         <v>531.5</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="7">
         <f>(L0!D8-L0!B8+L0!E8-L0!C8)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="7">
         <f>(L0!F8+L0!H8)/2</f>
         <v>891</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="7">
         <f>(L0!G8+L0!I8)/2</f>
         <v>559.5</v>
       </c>
@@ -13313,23 +14256,23 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <f>(L0!B9+L0!D9)/2</f>
         <v>858.5</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="7">
         <f>(L0!C9+L0!E9)/2</f>
         <v>533.5</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="7">
         <f>(L0!D9-L0!B9+L0!E9-L0!C9)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="7">
         <f>(L0!F9+L0!H9)/2</f>
         <v>890</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="7">
         <f>(L0!G9+L0!I9)/2</f>
         <v>559.5</v>
       </c>
@@ -13338,23 +14281,23 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <f>(L0!B10+L0!D10)/2</f>
         <v>854.5</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="7">
         <f>(L0!C10+L0!E10)/2</f>
         <v>536.5</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="7">
         <f>(L0!D10-L0!B10+L0!E10-L0!C10)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="7">
         <f>(L0!F10+L0!H10)/2</f>
         <v>888.5</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="7">
         <f>(L0!G10+L0!I10)/2</f>
         <v>559</v>
       </c>
@@ -13363,23 +14306,23 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <f>(L0!B11+L0!D11)/2</f>
         <v>851</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="7">
         <f>(L0!C11+L0!E11)/2</f>
         <v>539</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="7">
         <f>(L0!D11-L0!B11+L0!E11-L0!C11)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="7">
         <f>(L0!F11+L0!H11)/2</f>
         <v>886.5</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="7">
         <f>(L0!G11+L0!I11)/2</f>
         <v>558</v>
       </c>
@@ -13388,23 +14331,23 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="7">
         <f>(L0!B12+L0!D12)/2</f>
         <v>847</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="7">
         <f>(L0!C12+L0!E12)/2</f>
         <v>541</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="7">
         <f>(L0!D12-L0!B12+L0!E12-L0!C12)/4</f>
         <v>47</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="7">
         <f>(L0!F12+L0!H12)/2</f>
         <v>884.5</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="7">
         <f>(L0!G12+L0!I12)/2</f>
         <v>557</v>
       </c>
@@ -13413,23 +14356,23 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <f>(L0!B13+L0!D13)/2</f>
         <v>843</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="7">
         <f>(L0!C13+L0!E13)/2</f>
         <v>543.5</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="7">
         <f>(L0!D13-L0!B13+L0!E13-L0!C13)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="7">
         <f>(L0!F13+L0!H13)/2</f>
         <v>882</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="7">
         <f>(L0!G13+L0!I13)/2</f>
         <v>556</v>
       </c>
@@ -13438,23 +14381,23 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <f>(L0!B14+L0!D14)/2</f>
         <v>840</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="7">
         <f>(L0!C14+L0!E14)/2</f>
         <v>546</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="7">
         <f>(L0!D14-L0!B14+L0!E14-L0!C14)/4</f>
         <v>47</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="7">
         <f>(L0!F14+L0!H14)/2</f>
         <v>879.5</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="7">
         <f>(L0!G14+L0!I14)/2</f>
         <v>555.5</v>
       </c>
@@ -13463,23 +14406,23 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
         <f>(L0!B15+L0!D15)/2</f>
         <v>836</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="7">
         <f>(L0!C15+L0!E15)/2</f>
         <v>549</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="7">
         <f>(L0!D15-L0!B15+L0!E15-L0!C15)/4</f>
         <v>47</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="7">
         <f>(L0!F15+L0!H15)/2</f>
         <v>876.5</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="7">
         <f>(L0!G15+L0!I15)/2</f>
         <v>554.5</v>
       </c>
@@ -13488,23 +14431,23 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="7">
         <f>(L0!B16+L0!D16)/2</f>
         <v>832</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="7">
         <f>(L0!C16+L0!E16)/2</f>
         <v>551.5</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="7">
         <f>(L0!D16-L0!B16+L0!E16-L0!C16)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="7">
         <f>(L0!F16+L0!H16)/2</f>
         <v>873</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="7">
         <f>(L0!G16+L0!I16)/2</f>
         <v>553</v>
       </c>
@@ -13513,23 +14456,23 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="7">
         <f>(L0!B17+L0!D17)/2</f>
         <v>828.5</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="7">
         <f>(L0!C17+L0!E17)/2</f>
         <v>554</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="7">
         <f>(L0!D17-L0!B17+L0!E17-L0!C17)/4</f>
         <v>46.75</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="7">
         <f>(L0!F17+L0!H17)/2</f>
         <v>870</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="7">
         <f>(L0!G17+L0!I17)/2</f>
         <v>552</v>
       </c>
@@ -13538,23 +14481,23 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="7">
         <f>(L0!B18+L0!D18)/2</f>
         <v>825</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="7">
         <f>(L0!C18+L0!E18)/2</f>
         <v>556.5</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="7">
         <f>(L0!D18-L0!B18+L0!E18-L0!C18)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="7">
         <f>(L0!F18+L0!H18)/2</f>
         <v>866</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="7">
         <f>(L0!G18+L0!I18)/2</f>
         <v>551</v>
       </c>
@@ -13563,29 +14506,29 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="7">
         <f>(L0!B19+L0!D19)/2</f>
         <v>821</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="7">
         <f>(L0!C19+L0!E19)/2</f>
         <v>559</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="7">
         <f>(L0!D19-L0!B19+L0!E19-L0!C19)/4</f>
         <v>47</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="7">
         <f>(L0!F19+L0!H19)/2</f>
         <v>861.5</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="7">
         <f>(L0!G19+L0!I19)/2</f>
         <v>550</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="D20" s="2">
+      <c r="D20" s="7">
         <f>AVERAGE(D2:D19)</f>
         <v>47.4444444444444</v>
       </c>
@@ -13601,480 +14544,708 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="10" max="10" width="12.8888888888889"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="H1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <f>'L1'!E2-'L1'!B2</f>
         <v>9.5</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="7">
         <f>-('L1'!F2-'L1'!C2)</f>
         <v>-36</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="7">
         <f>SQRT(47.44*47.44-B2*B2-C2*C2)</f>
         <v>29.3990408006792</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="7">
         <f>COS(3.14/9*((A2-25)/20))*47.44</f>
         <v>47.44</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="7">
         <f>SIN(3.14/9*((A2-25)/20))*47.44</f>
         <v>0</v>
       </c>
+      <c r="H2" s="7">
+        <f>'L1'!E2-球心降噪!B2</f>
+        <v>9.44152046783597</v>
+      </c>
+      <c r="I2" s="7">
+        <f>-('L1'!F2-球心降噪!C2)</f>
+        <v>-36.90350877193</v>
+      </c>
+      <c r="J2" s="8">
+        <f>SQRT(47.44*47.44-H2*H2-I2*I2)</f>
+        <v>28.2761795788526</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <f>'L1'!E3-'L1'!B3</f>
         <v>13.5</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <f>-('L1'!F3-'L1'!C3)</f>
         <v>-36</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="7">
         <f t="shared" ref="D3:D19" si="0">SQRT(47.44*47.44-B3*B3-C3*C3)</f>
         <v>27.7903508434133</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="7">
         <f t="shared" ref="E3:E20" si="1">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="7">
         <f t="shared" ref="F3:F20" si="2">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
+      <c r="H3" s="7">
+        <f>'L1'!E3-球心降噪!B3</f>
+        <v>13.680426556588</v>
+      </c>
+      <c r="I3" s="7">
+        <f>-('L1'!F3-球心降噪!C3)</f>
+        <v>-36.463880288958</v>
+      </c>
+      <c r="J3" s="8">
+        <f t="shared" ref="J3:J19" si="3">SQRT(47.44*47.44-H3*H3-I3*I3)</f>
+        <v>27.0884655066016</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="7">
         <f>'L1'!E4-'L1'!B4</f>
         <v>16</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="7">
         <f>-('L1'!F4-'L1'!C4)</f>
         <v>-35.5</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="7">
         <f t="shared" si="0"/>
         <v>27.0980368292613</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="7">
         <f t="shared" si="1"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="7">
         <f t="shared" si="2"/>
         <v>30.4809803249618</v>
       </c>
+      <c r="H4" s="7">
+        <f>'L1'!E4-球心降噪!B4</f>
+        <v>16.419332645339</v>
+      </c>
+      <c r="I4" s="7">
+        <f>-('L1'!F4-球心降噪!C4)</f>
+        <v>-35.524251805986</v>
+      </c>
+      <c r="J4" s="8">
+        <f t="shared" si="3"/>
+        <v>26.8139264022748</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <f>'L1'!E5-'L1'!B5</f>
         <v>20</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="7">
         <f>-('L1'!F5-'L1'!C5)</f>
         <v>-34</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="7">
         <f t="shared" si="0"/>
         <v>26.3543848344066</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="7">
         <f t="shared" si="1"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="7">
         <f t="shared" si="2"/>
         <v>41.0716467855168</v>
       </c>
+      <c r="H5" s="7">
+        <f>'L1'!E5-球心降噪!B5</f>
+        <v>19.65823873409</v>
+      </c>
+      <c r="I5" s="7">
+        <f>-('L1'!F5-球心降噪!C5)</f>
+        <v>-34.0846233230139</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="3"/>
+        <v>26.5018056517245</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="7">
         <f>'L1'!E6-'L1'!B6</f>
         <v>23</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="7">
         <f>-('L1'!F6-'L1'!C6)</f>
         <v>-32.5</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="7">
         <f t="shared" si="0"/>
         <v>25.7934797962586</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="7">
         <f t="shared" si="1"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="7">
         <f t="shared" si="2"/>
         <v>46.7134369557949</v>
       </c>
+      <c r="H6" s="7">
+        <f>'L1'!E6-球心降噪!B6</f>
+        <v>22.897144822841</v>
+      </c>
+      <c r="I6" s="7">
+        <f>-('L1'!F6-球心降噪!C6)</f>
+        <v>-32.144994840041</v>
+      </c>
+      <c r="J6" s="8">
+        <f t="shared" si="3"/>
+        <v>26.3243929786725</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="7">
         <f>'L1'!E7-'L1'!B7</f>
         <v>26.5</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="7">
         <f>-('L1'!F7-'L1'!C7)</f>
         <v>-30</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="7">
         <f t="shared" si="0"/>
         <v>25.461806691592</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="7">
         <f t="shared" si="1"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="7">
         <f t="shared" si="2"/>
         <v>46.7265504432231</v>
       </c>
+      <c r="H7" s="7">
+        <f>'L1'!E7-球心降噪!B7</f>
+        <v>26.136050911593</v>
+      </c>
+      <c r="I7" s="7">
+        <f>-('L1'!F7-球心降噪!C7)</f>
+        <v>-29.705366357069</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="3"/>
+        <v>26.1734914052163</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <f>'L1'!E8-'L1'!B8</f>
         <v>28.5</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="7">
         <f>-('L1'!F8-'L1'!C8)</f>
         <v>-28</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="7">
         <f t="shared" si="0"/>
         <v>25.5793588660858</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="7">
         <f t="shared" si="1"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="7">
         <f t="shared" si="2"/>
         <v>41.1094071546692</v>
       </c>
+      <c r="H8" s="7">
+        <f>'L1'!E8-球心降噪!B8</f>
+        <v>28.874957000344</v>
+      </c>
+      <c r="I8" s="7">
+        <f>-('L1'!F8-球心降噪!C8)</f>
+        <v>-27.765737874097</v>
+      </c>
+      <c r="J8" s="8">
+        <f t="shared" si="3"/>
+        <v>25.4136628319339</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <f>'L1'!E9-'L1'!B9</f>
         <v>31.5</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="7">
         <f>-('L1'!F9-'L1'!C9)</f>
         <v>-26</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="7">
         <f t="shared" si="0"/>
         <v>24.1309676556909</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="7">
         <f t="shared" si="1"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="7">
         <f t="shared" si="2"/>
         <v>30.5388376877712</v>
       </c>
+      <c r="H9" s="7">
+        <f>'L1'!E9-球心降噪!B9</f>
+        <v>31.613863089095</v>
+      </c>
+      <c r="I9" s="7">
+        <f>-('L1'!F9-球心降噪!C9)</f>
+        <v>-25.326109391125</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="3"/>
+        <v>24.6922142322782</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <f>'L1'!E10-'L1'!B10</f>
         <v>34</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="7">
         <f>-('L1'!F10-'L1'!C10)</f>
         <v>-22.5</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="7">
         <f t="shared" si="0"/>
         <v>24.2549706245957</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="7">
         <f t="shared" si="1"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="7">
         <f t="shared" si="2"/>
         <v>16.2885294815216</v>
       </c>
+      <c r="H10" s="7">
+        <f>'L1'!E10-球心降噪!B10</f>
+        <v>33.852769177847</v>
+      </c>
+      <c r="I10" s="7">
+        <f>-('L1'!F10-球心降噪!C10)</f>
+        <v>-22.386480908153</v>
+      </c>
+      <c r="J10" s="8">
+        <f t="shared" si="3"/>
+        <v>24.5639795542236</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <f>'L1'!E11-'L1'!B11</f>
         <v>35.5</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="7">
         <f>-('L1'!F11-'L1'!C11)</f>
         <v>-19</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="7">
         <f t="shared" si="0"/>
         <v>25.0859243401554</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="7">
         <f t="shared" si="1"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="7">
         <f t="shared" si="2"/>
         <v>0.0755554543581351</v>
       </c>
+      <c r="H11" s="7">
+        <f>'L1'!E11-球心降噪!B11</f>
+        <v>35.591675266598</v>
+      </c>
+      <c r="I11" s="7">
+        <f>-('L1'!F11-球心降噪!C11)</f>
+        <v>-18.946852425181</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="3"/>
+        <v>24.996060387498</v>
+      </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="7">
         <f>'L1'!E12-'L1'!B12</f>
         <v>37.5</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="7">
         <f>-('L1'!F12-'L1'!C12)</f>
         <v>-16</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="7">
         <f t="shared" si="0"/>
         <v>24.2549706245957</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="7">
         <f t="shared" si="1"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="7">
         <f t="shared" si="2"/>
         <v>-16.1465225320068</v>
       </c>
+      <c r="H12" s="7">
+        <f>'L1'!E12-球心降噪!B12</f>
+        <v>37.330581355349</v>
+      </c>
+      <c r="I12" s="7">
+        <f>-('L1'!F12-球心降噪!C12)</f>
+        <v>-15.507223942209</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="3"/>
+        <v>24.8295650642103</v>
+      </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <f>'L1'!E13-'L1'!B13</f>
         <v>39</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="7">
         <f>-('L1'!F13-'L1'!C13)</f>
         <v>-12.5</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="7">
         <f t="shared" si="0"/>
         <v>23.9437591033655</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="7">
         <f t="shared" si="1"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="7">
         <f t="shared" si="2"/>
         <v>-30.4230456457766</v>
       </c>
+      <c r="H13" s="7">
+        <f>'L1'!E13-球心降噪!B13</f>
+        <v>38.569487444101</v>
+      </c>
+      <c r="I13" s="7">
+        <f>-('L1'!F13-球心降噪!C13)</f>
+        <v>-12.067595459236</v>
+      </c>
+      <c r="J13" s="8">
+        <f t="shared" si="3"/>
+        <v>24.845952952776</v>
+      </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <f>'L1'!E14-'L1'!B14</f>
         <v>39.5</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="7">
         <f>-('L1'!F14-'L1'!C14)</f>
         <v>-9.5</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="7">
         <f t="shared" si="0"/>
         <v>24.4959915088163</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="7">
         <f t="shared" si="1"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="7">
         <f t="shared" si="2"/>
         <v>-41.0337822362874</v>
       </c>
+      <c r="H14" s="7">
+        <f>'L1'!E14-球心降噪!B14</f>
+        <v>39.8083935328521</v>
+      </c>
+      <c r="I14" s="7">
+        <f>-('L1'!F14-球心降噪!C14)</f>
+        <v>-9.12796697626402</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="3"/>
+        <v>24.1355675966781</v>
+      </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
         <f>'L1'!E15-'L1'!B15</f>
         <v>40.5</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="7">
         <f>-('L1'!F15-'L1'!C15)</f>
         <v>-5.5</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="7">
         <f t="shared" si="0"/>
         <v>24.0843019413061</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="7">
         <f t="shared" si="1"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="7">
         <f t="shared" si="2"/>
         <v>-46.7002049776354</v>
       </c>
+      <c r="H15" s="7">
+        <f>'L1'!E15-球心降噪!B15</f>
+        <v>40.547299621603</v>
+      </c>
+      <c r="I15" s="7">
+        <f>-('L1'!F15-球心降噪!C15)</f>
+        <v>-5.68833849329201</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="3"/>
+        <v>23.9606531334538</v>
+      </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="7">
         <f>'L1'!E16-'L1'!B16</f>
         <v>41</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="7">
         <f>-('L1'!F16-'L1'!C16)</f>
         <v>-1.5</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="7">
         <f t="shared" si="0"/>
         <v>23.8181359472147</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="7">
         <f t="shared" si="1"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="7">
         <f t="shared" si="2"/>
         <v>-46.7395454066571</v>
       </c>
+      <c r="H16" s="7">
+        <f>'L1'!E16-球心降噪!B16</f>
+        <v>40.786205710354</v>
+      </c>
+      <c r="I16" s="7">
+        <f>-('L1'!F16-球心降噪!C16)</f>
+        <v>-1.74871001032</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="3"/>
+        <v>24.1656995978286</v>
+      </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="7">
         <f>'L1'!E17-'L1'!B17</f>
         <v>41.5</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="7">
         <f>-('L1'!F17-'L1'!C17)</f>
         <v>2</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="7">
         <f t="shared" si="0"/>
         <v>22.8976767380448</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="7">
         <f t="shared" si="1"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="7">
         <f t="shared" si="2"/>
         <v>-41.1470632479638</v>
       </c>
+      <c r="H17" s="7">
+        <f>'L1'!E17-球心降噪!B17</f>
+        <v>41.525111799106</v>
+      </c>
+      <c r="I17" s="7">
+        <f>-('L1'!F17-球心降噪!C17)</f>
+        <v>1.69091847265202</v>
+      </c>
+      <c r="J17" s="8">
+        <f t="shared" si="3"/>
+        <v>22.877051488131</v>
+      </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="7">
         <f>'L1'!E18-'L1'!B18</f>
         <v>41</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="7">
         <f>-('L1'!F18-'L1'!C18)</f>
         <v>5.5</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="7">
         <f t="shared" si="0"/>
         <v>23.2229111008934</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="7">
         <f t="shared" si="1"/>
         <v>36.254663040877</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="7">
         <f t="shared" si="2"/>
         <v>-30.5966175874469</v>
       </c>
+      <c r="H18" s="7">
+        <f>'L1'!E18-球心降噪!B18</f>
+        <v>41.264017887857</v>
+      </c>
+      <c r="I18" s="7">
+        <f>-('L1'!F18-球心降噪!C18)</f>
+        <v>5.13054695562403</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="3"/>
+        <v>22.8366353845472</v>
+      </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="7">
         <f>'L1'!E19-'L1'!B19</f>
         <v>40.5</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="7">
         <f>-('L1'!F19-'L1'!C19)</f>
         <v>9</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="7">
         <f t="shared" si="0"/>
         <v>23.0065990533151</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="7">
         <f t="shared" si="1"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="7">
         <f t="shared" si="2"/>
         <v>-16.3594710714245</v>
       </c>
+      <c r="H19" s="7">
+        <f>'L1'!E19-球心降噪!B19</f>
+        <v>40.502923976608</v>
+      </c>
+      <c r="I19" s="7">
+        <f>-('L1'!F19-球心降噪!C19)</f>
+        <v>8.57017543859604</v>
+      </c>
+      <c r="J19" s="8">
+        <f t="shared" si="3"/>
+        <v>23.1650349081713</v>
+      </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>385</v>
       </c>
@@ -14087,9 +15258,9 @@
         <v>-0.151110717066466</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
+    <row r="21" spans="1:10">
+      <c r="A21" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -14112,34 +15283,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -14147,38 +15318,38 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <f>COS(A2*3.1416/9)*47.44</f>
         <v>47.44</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="7">
         <f>SIN(A2*3.1416/9)*47.44</f>
         <v>0</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="7">
         <f>COS(A2*3.1416/18+3.1416/30)*47.44</f>
         <v>47.1801175019494</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="7">
         <f>SIN(A2*3.1416/18+3.1416/30)*47.44</f>
         <v>4.95884185090085</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="7">
         <f>D2*COS(-3.1416/30)-E2*SIN(-3.1416/30)</f>
         <v>47.44</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="7">
         <f>(D2*SIN(-3.1416/30)+E2*COS(-3.1416/30))*0.8</f>
         <v>0</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="7">
         <f>G2*COS(3.1416/30)-H2*SIN(3.1416/30)</f>
         <v>47.1801175019494</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="7">
         <f>G2*SIN(3.1416/30)+H2*COS(3.1416/30)</f>
         <v>4.95884185090085</v>
       </c>
@@ -14187,35 +15358,35 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <f t="shared" ref="B3:B20" si="0">COS(A3*3.1416/9)*47.44</f>
         <v>44.579004685768</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <f t="shared" ref="C3:C20" si="1">SIN(A3*3.1416/9)*47.44</f>
         <v>16.2254719877812</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="7">
         <f t="shared" ref="D3:D20" si="2">COS(A3*3.1416/18+3.1416/30)*47.44</f>
         <v>45.6022463163357</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="7">
         <f t="shared" ref="E3:E20" si="3">SIN(A3*3.1416/18+3.1416/30)*47.44</f>
         <v>13.0762659388775</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="7">
         <f t="shared" ref="G3:G20" si="4">D3*COS(-3.1416/30)-E3*SIN(-3.1416/30)</f>
         <v>46.7192764407414</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="7">
         <f t="shared" ref="H3:H20" si="5">(D3*SIN(-3.1416/30)+E3*COS(-3.1416/30))*0.8</f>
         <v>6.5903108929923</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="7">
         <f t="shared" ref="I3:I20" si="6">G3*COS(3.1416/30)-H3*SIN(3.1416/30)</f>
         <v>45.77446548511</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="7">
         <f t="shared" ref="J3:J20" si="7">G3*SIN(3.1416/30)+H3*COS(3.1416/30)</f>
         <v>11.4377138609593</v>
       </c>
@@ -14224,35 +15395,35 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="7">
         <f t="shared" si="0"/>
         <v>36.3410985992296</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="7">
         <f t="shared" si="1"/>
         <v>30.4939035317073</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="7">
         <f t="shared" si="2"/>
         <v>42.6387674884245</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="7">
         <f t="shared" si="3"/>
         <v>20.7963724497344</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="7">
         <f t="shared" si="4"/>
         <v>44.579004685768</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="7">
         <f t="shared" si="5"/>
         <v>12.980377590225</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="7">
         <f t="shared" si="6"/>
         <v>42.9779730092661</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="7">
         <f t="shared" si="7"/>
         <v>17.5690551018925</v>
       </c>
@@ -14261,35 +15432,35 @@
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <f t="shared" si="0"/>
         <v>23.7198993926896</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="7">
         <f t="shared" si="1"/>
         <v>41.0843032410273</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="7">
         <f t="shared" si="2"/>
         <v>38.3797252428634</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="7">
         <f t="shared" si="3"/>
         <v>27.8845887594261</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="7">
         <f t="shared" si="4"/>
         <v>41.0842161126946</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="7">
         <f t="shared" si="5"/>
         <v>18.9760402428815</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="7">
         <f t="shared" si="6"/>
         <v>38.8756104795876</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="7">
         <f t="shared" si="7"/>
         <v>23.1665670036247</v>
       </c>
@@ -14298,35 +15469,35 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="7">
         <f t="shared" si="0"/>
         <v>8.23771700670016</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="7">
         <f t="shared" si="1"/>
         <v>46.7193066998808</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="7">
         <f t="shared" si="2"/>
         <v>32.9545290267963</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="7">
         <f t="shared" si="3"/>
         <v>34.1255419974839</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="7">
         <f t="shared" si="4"/>
         <v>36.3410985992296</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="7">
         <f t="shared" si="5"/>
         <v>24.3951228253659</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="7">
         <f t="shared" si="6"/>
         <v>33.5920266871267</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="7">
         <f t="shared" si="7"/>
         <v>28.0601712060882</v>
       </c>
@@ -14335,35 +15506,35 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="7">
         <f t="shared" si="0"/>
         <v>-8.23806022566945</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="7">
         <f t="shared" si="1"/>
         <v>46.7192461809717</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="7">
         <f t="shared" si="2"/>
         <v>26.5280214509534</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="7">
         <f t="shared" si="3"/>
         <v>39.3296030732291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="7">
         <f t="shared" si="4"/>
         <v>30.4937700431928</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="7">
         <f t="shared" si="5"/>
         <v>29.0729684874772</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="7">
         <f t="shared" si="6"/>
         <v>27.287761400709</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="7">
         <f t="shared" si="7"/>
         <v>32.1011773282373</v>
       </c>
@@ -14372,35 +15543,35 @@
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <f t="shared" si="0"/>
         <v>-23.7202012141941</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="7">
         <f t="shared" si="1"/>
         <v>41.0841289838076</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="7">
         <f t="shared" si="2"/>
         <v>19.2954696069731</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="7">
         <f t="shared" si="3"/>
         <v>43.338648486615</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="7">
         <f t="shared" si="4"/>
         <v>23.7198993926896</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="7">
         <f t="shared" si="5"/>
         <v>32.8674425928218</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="7">
         <f t="shared" si="6"/>
         <v>20.1543674245393</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="7">
         <f t="shared" si="7"/>
         <v>35.1668008711117</v>
       </c>
@@ -14409,35 +15580,35 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <f t="shared" si="0"/>
         <v>-36.3413226189731</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="7">
         <f t="shared" si="1"/>
         <v>30.4936365542668</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="7">
         <f t="shared" si="2"/>
         <v>11.4766319479547</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="7">
         <f t="shared" si="3"/>
         <v>46.0308648531742</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="7">
         <f t="shared" si="4"/>
         <v>16.2253082398443</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="7">
         <f t="shared" si="5"/>
         <v>35.663251427963</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="7">
         <f t="shared" si="6"/>
         <v>12.4085903360248</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="7">
         <f t="shared" si="7"/>
         <v>37.1638939801089</v>
       </c>
@@ -14446,35 +15617,35 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <f t="shared" si="0"/>
         <v>-44.5791238835381</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="7">
         <f t="shared" si="1"/>
         <v>16.2251444916884</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="7">
         <f t="shared" si="2"/>
         <v>3.30908100791483</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="7">
         <f t="shared" si="3"/>
         <v>47.3244501593316</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="7">
         <f t="shared" si="4"/>
         <v>8.23771700670016</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="7">
         <f t="shared" si="5"/>
         <v>37.3754453599046</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="7">
         <f t="shared" si="6"/>
         <v>4.28578275036188</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="7">
         <f t="shared" si="7"/>
         <v>38.0317757086149</v>
       </c>
@@ -14483,35 +15654,35 @@
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <f t="shared" si="0"/>
         <v>-47.4399999987198</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="7">
         <f t="shared" si="1"/>
         <v>-0.000348513700203172</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="7">
         <f t="shared" si="2"/>
         <v>-4.95901515311578</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="7">
         <f t="shared" si="3"/>
         <v>47.1800992867879</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="7">
         <f t="shared" si="4"/>
         <v>-0.000174256850099752</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="7">
         <f t="shared" si="5"/>
         <v>37.951999999744</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="7">
         <f t="shared" si="6"/>
         <v>-3.9672467829423</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="7">
         <f t="shared" si="7"/>
         <v>37.7440757864617</v>
       </c>
@@ -14520,35 +15691,35 @@
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="7">
         <f t="shared" si="0"/>
         <v>-44.578885485592</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="7">
         <f t="shared" si="1"/>
         <v>-16.2257994829984</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="7">
         <f t="shared" si="2"/>
         <v>-13.0764334451932</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="7">
         <f t="shared" si="3"/>
         <v>45.6021982842213</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="7">
         <f t="shared" si="4"/>
         <v>-8.23806022566945</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="7">
         <f t="shared" si="5"/>
         <v>37.3753969447774</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="7">
         <f t="shared" si="6"/>
         <v>-12.0997329679388</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="7">
         <f t="shared" si="7"/>
         <v>36.3095358709803</v>
       </c>
@@ -14557,35 +15728,35 @@
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <f t="shared" si="0"/>
         <v>-36.3408745775248</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="7">
         <f t="shared" si="1"/>
         <v>-30.4941705075021</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="7">
         <f t="shared" si="2"/>
         <v>-20.7965290705324</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="7">
         <f t="shared" si="3"/>
         <v>42.6386910987955</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="7">
         <f t="shared" si="4"/>
         <v>-16.2256357354993</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="7">
         <f t="shared" si="5"/>
         <v>35.6631560687846</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="7">
         <f t="shared" si="6"/>
         <v>-19.8645731744052</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="7">
         <f t="shared" si="7"/>
         <v>33.7717439349273</v>
       </c>
@@ -14594,35 +15765,35 @@
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <f t="shared" si="0"/>
         <v>-23.7195975699048</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="7">
         <f t="shared" si="1"/>
         <v>-41.0844774960296</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="7">
         <f t="shared" si="2"/>
         <v>-27.8847297358406</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="7">
         <f t="shared" si="3"/>
         <v>38.3796228167908</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="7">
         <f t="shared" si="4"/>
         <v>-23.7202012141941</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="7">
         <f t="shared" si="5"/>
         <v>32.8673031870461</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="7">
         <f t="shared" si="6"/>
         <v>-27.0258355612507</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="7">
         <f t="shared" si="7"/>
         <v>30.2078098618107</v>
       </c>
@@ -14631,35 +15802,35 @@
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
         <f t="shared" si="0"/>
         <v>-8.23737378728626</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="7">
         <f t="shared" si="1"/>
         <v>-46.7193672162683</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="7">
         <f t="shared" si="2"/>
         <v>-34.1256630459979</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="7">
         <f t="shared" si="3"/>
         <v>32.954403676459</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="7">
         <f t="shared" si="4"/>
         <v>-30.4940370198104</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="7">
         <f t="shared" si="5"/>
         <v>29.0727892708979</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="7">
         <f t="shared" si="6"/>
         <v>-33.3659277795616</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="7">
         <f t="shared" si="7"/>
         <v>25.7260224901691</v>
       </c>
@@ -14668,35 +15839,35 @@
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="7">
         <f t="shared" si="0"/>
         <v>8.23840344419414</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="7">
         <f t="shared" si="1"/>
         <v>-46.7191856595413</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="7">
         <f t="shared" si="2"/>
         <v>-39.3297005158276</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="7">
         <f t="shared" si="3"/>
         <v>26.5278769850757</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="7">
         <f t="shared" si="4"/>
         <v>-36.3413226189731</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="7">
         <f t="shared" si="5"/>
         <v>24.3949092434134</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="7">
         <f t="shared" si="6"/>
         <v>-38.6922084368585</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="7">
         <f t="shared" si="7"/>
         <v>20.4625592966607</v>
       </c>
@@ -14705,35 +15876,35 @@
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="7">
         <f t="shared" si="0"/>
         <v>23.7205030344186</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="7">
         <f t="shared" si="1"/>
         <v>-41.0839547243707</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="7">
         <f t="shared" si="2"/>
         <v>-43.3387193625401</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="7">
         <f t="shared" si="3"/>
         <v>19.2953104150981</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="7">
         <f t="shared" si="4"/>
         <v>-41.0843903688056</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="7">
         <f t="shared" si="5"/>
         <v>18.9757987851658</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="7">
         <f t="shared" si="6"/>
         <v>-42.8428404356316</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="7">
         <f t="shared" si="7"/>
         <v>14.5773486930415</v>
       </c>
@@ -14742,35 +15913,35 @@
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="7">
         <f t="shared" si="0"/>
         <v>36.3415466367552</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="7">
         <f t="shared" si="1"/>
         <v>-30.4933695751805</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="7">
         <f t="shared" si="2"/>
         <v>-46.0309070088867</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="7">
         <f t="shared" si="3"/>
         <v>11.4764628670696</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="7">
         <f t="shared" si="4"/>
         <v>-44.5791238835381</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="7">
         <f t="shared" si="5"/>
         <v>12.9801155933507</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="7">
         <f t="shared" si="6"/>
         <v>-45.6917083345937</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="7">
         <f t="shared" si="7"/>
         <v>8.24921065963301</v>
       </c>
@@ -14779,35 +15950,35 @@
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="7">
         <f t="shared" si="0"/>
         <v>44.5792430789022</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="7">
         <f t="shared" si="1"/>
         <v>-16.2248169947199</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="7">
         <f t="shared" si="2"/>
         <v>-47.3244623139455</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="7">
         <f t="shared" si="3"/>
         <v>3.30890717548068</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="7">
         <f t="shared" si="4"/>
         <v>-46.7193369583897</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="7">
         <f t="shared" si="5"/>
         <v>6.59003631763904</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="7">
         <f t="shared" si="6"/>
         <v>-47.1522503204229</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="7">
         <f t="shared" si="7"/>
         <v>1.67042336536092</v>
       </c>
@@ -14816,35 +15987,35 @@
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="7">
         <f t="shared" si="0"/>
         <v>47.4399999948794</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="7">
         <f t="shared" si="1"/>
         <v>0.000697027400387534</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="7">
         <f t="shared" si="2"/>
         <v>-47.1800810709899</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="7">
         <f t="shared" si="3"/>
         <v>-4.9591884552638</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="7">
         <f t="shared" si="4"/>
         <v>-47.4399999987198</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="7">
         <f t="shared" si="5"/>
         <v>-0.000278810960160314</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="7">
         <f t="shared" si="6"/>
         <v>-47.1800883569272</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="7">
         <f t="shared" si="7"/>
         <v>-4.95911913436445</v>
       </c>
@@ -14898,34 +16069,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="F1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>18</v>
       </c>
     </row>
@@ -14933,31 +16104,31 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <f>'L2'!C2*'L2'!D3-'L2'!D2*'L2'!C3</f>
         <v>57.9128384615722</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="7">
         <f>'L2'!D2*'L2'!B3-'L2'!B2*'L2'!D3</f>
         <v>132.878717796743</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="7">
         <f>'L2'!B2*'L2'!C3-'L2'!C2*'L2'!B3</f>
         <v>144</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="7">
         <f>SQRT(B2*B2+C2*C2+D2*D2)</f>
         <v>204.319970883863</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="7">
         <f>B2/E2*47.44</f>
         <v>13.4464832034389</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="7">
         <f>C2/E2*47.44</f>
         <v>30.8524239946206</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="7">
         <f>-D2/E2*47.44</f>
         <v>-33.4346171372695</v>
       </c>
@@ -14974,31 +16145,31 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <f>'L2'!C3*'L2'!D4-'L2'!D3*'L2'!C4</f>
         <v>11.0281290877654</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <f>'L2'!D3*'L2'!B4-'L2'!B3*'L2'!D4</f>
         <v>78.8221162995853</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="7">
         <f>'L2'!B3*'L2'!C4-'L2'!C3*'L2'!B4</f>
         <v>96.75</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="7">
         <f t="shared" ref="E3:E19" si="0">SQRT(B3*B3+C3*C3+D3*D3)</f>
         <v>125.280118730474</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="7">
         <f t="shared" ref="F3:F19" si="1">B3/E3*47.44</f>
         <v>4.17603726134023</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="7">
         <f t="shared" ref="G3:G19" si="2">C3/E3*47.44</f>
         <v>29.8476824187646</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="7">
         <f t="shared" ref="H3:H19" si="3">-D3/E3*47.44</f>
         <v>-36.6364595317351</v>
       </c>
@@ -15015,31 +16186,31 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="7">
         <f>'L2'!C4*'L2'!D5-'L2'!D4*'L2'!C5</f>
         <v>-14.2474094265501</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="7">
         <f>'L2'!D4*'L2'!B5-'L2'!B4*'L2'!D5</f>
         <v>120.29057923472</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="7">
         <f>'L2'!B4*'L2'!C5-'L2'!C4*'L2'!B5</f>
         <v>166</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="7">
         <f t="shared" si="0"/>
         <v>205.496501498182</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="7">
         <f t="shared" si="1"/>
         <v>-3.28909299315501</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="7">
         <f t="shared" si="2"/>
         <v>27.7697432184539</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="7">
         <f t="shared" si="3"/>
         <v>-38.3220149374157</v>
       </c>
@@ -15056,31 +16227,31 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <f>'L2'!C5*'L2'!D6-'L2'!D5*'L2'!C6</f>
         <v>-20.4608059545781</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="7">
         <f>'L2'!D5*'L2'!B6-'L2'!B5*'L2'!D6</f>
         <v>90.2812552661798</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="7">
         <f>'L2'!B5*'L2'!C6-'L2'!C5*'L2'!B6</f>
         <v>132</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="7">
         <f t="shared" si="0"/>
         <v>161.224531733691</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="7">
         <f t="shared" si="1"/>
         <v>-6.02055173643493</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="7">
         <f t="shared" si="2"/>
         <v>26.5650810318499</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="7">
         <f t="shared" si="3"/>
         <v>-38.8407392638214</v>
       </c>
@@ -15097,31 +16268,31 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="7">
         <f>'L2'!C6*'L2'!D7-'L2'!D6*'L2'!C7</f>
         <v>-53.704323588982</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="7">
         <f>'L2'!D6*'L2'!B7-'L2'!B6*'L2'!D7</f>
         <v>97.905660694237</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="7">
         <f>'L2'!B6*'L2'!C7-'L2'!C6*'L2'!B7</f>
         <v>171.25</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="7">
         <f t="shared" si="0"/>
         <v>204.441275842539</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="7">
         <f t="shared" si="1"/>
         <v>-12.4619311856749</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="7">
         <f t="shared" si="2"/>
         <v>22.7187221572219</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="7">
         <f t="shared" si="3"/>
         <v>-39.7380615363465</v>
       </c>
@@ -15138,31 +16309,31 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="7">
         <f>'L2'!C7*'L2'!D8-'L2'!D7*'L2'!C8</f>
         <v>-54.4501786179981</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="7">
         <f>'L2'!D7*'L2'!B8-'L2'!B7*'L2'!D8</f>
         <v>47.8084807590982</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="7">
         <f>'L2'!B7*'L2'!C8-'L2'!C7*'L2'!B8</f>
         <v>113</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="7">
         <f t="shared" si="0"/>
         <v>134.23662981476</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="7">
         <f t="shared" si="1"/>
         <v>-19.243007495066</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="7">
         <f t="shared" si="2"/>
         <v>16.8957931254784</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="7">
         <f t="shared" si="3"/>
         <v>-39.9348524124714</v>
       </c>
@@ -15179,31 +16350,31 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <f>'L2'!C8*'L2'!D9-'L2'!D8*'L2'!C9</f>
         <v>-10.6037638411143</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="7">
         <f>'L2'!D8*'L2'!B9-'L2'!B8*'L2'!D9</f>
         <v>118.017226094512</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="7">
         <f>'L2'!B8*'L2'!C9-'L2'!C8*'L2'!B9</f>
         <v>141</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="7">
         <f t="shared" si="0"/>
         <v>184.177917956093</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="7">
         <f t="shared" si="1"/>
         <v>-2.73128593375882</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="7">
         <f t="shared" si="2"/>
         <v>30.3985258822307</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="7">
         <f t="shared" si="3"/>
         <v>-36.3183603888639</v>
       </c>
@@ -15220,31 +16391,31 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <f>'L2'!C9*'L2'!D10-'L2'!D9*'L2'!C10</f>
         <v>-87.6824639864429</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="7">
         <f>'L2'!D9*'L2'!B10-'L2'!B9*'L2'!D10</f>
         <v>56.421325618726</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="7">
         <f>'L2'!B9*'L2'!C10-'L2'!C9*'L2'!B10</f>
         <v>175.25</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="7">
         <f t="shared" si="0"/>
         <v>203.921904108676</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="7">
         <f t="shared" si="1"/>
         <v>-20.3982799675117</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="7">
         <f t="shared" si="2"/>
         <v>13.1257487960975</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="7">
         <f t="shared" si="3"/>
         <v>-40.7698233122092</v>
       </c>
@@ -15261,31 +16432,31 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <f>'L2'!C10*'L2'!D11-'L2'!D10*'L2'!C11</f>
         <v>-103.588855786178</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="7">
         <f>'L2'!D10*'L2'!B11-'L2'!B10*'L2'!D11</f>
         <v>8.13002960786366</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="7">
         <f>'L2'!B10*'L2'!C11-'L2'!C10*'L2'!B11</f>
         <v>152.75</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="7">
         <f t="shared" si="0"/>
         <v>184.741199856757</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="7">
         <f t="shared" si="1"/>
         <v>-26.6007545815804</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="7">
         <f t="shared" si="2"/>
         <v>2.08772382606643</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="7">
         <f t="shared" si="3"/>
         <v>-39.2249265763061</v>
       </c>
@@ -15302,31 +16473,31 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <f>'L2'!C11*'L2'!D12-'L2'!D11*'L2'!C12</f>
         <v>-59.4696524248319</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="7">
         <f>'L2'!D11*'L2'!B12-'L2'!B11*'L2'!D12</f>
         <v>79.6707055826802</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="7">
         <f>'L2'!B11*'L2'!C12-'L2'!C11*'L2'!B12</f>
         <v>144.5</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="7">
         <f t="shared" si="0"/>
         <v>175.397579480369</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="7">
         <f t="shared" si="1"/>
         <v>-16.0848303573641</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="7">
         <f t="shared" si="2"/>
         <v>21.5486341604011</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="7">
         <f t="shared" si="3"/>
         <v>-39.0830935085238</v>
       </c>
@@ -15343,31 +16514,31 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="7">
         <f>'L2'!C12*'L2'!D13-'L2'!D12*'L2'!C13</f>
         <v>-79.9130128464018</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="7">
         <f>'L2'!D12*'L2'!B13-'L2'!B12*'L2'!D13</f>
         <v>48.052887983026</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="7">
         <f>'L2'!B12*'L2'!C13-'L2'!C12*'L2'!B13</f>
         <v>155.25</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="7">
         <f t="shared" si="0"/>
         <v>181.101441644451</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="7">
         <f t="shared" si="1"/>
         <v>-20.9334243560367</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="7">
         <f t="shared" si="2"/>
         <v>12.5875806686854</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="7">
         <f t="shared" si="3"/>
         <v>-40.6681467199998</v>
       </c>
@@ -15384,31 +16555,31 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <f>'L2'!C13*'L2'!D14-'L2'!D13*'L2'!C14</f>
         <v>-78.7341823782315</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="7">
         <f>'L2'!D13*'L2'!B14-'L2'!B13*'L2'!D14</f>
         <v>-9.56518426089838</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="7">
         <f>'L2'!B13*'L2'!C14-'L2'!C13*'L2'!B14</f>
         <v>123.25</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="7">
         <f t="shared" si="0"/>
         <v>146.564411521739</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="7">
         <f t="shared" si="1"/>
         <v>-25.4846969550265</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="7">
         <f t="shared" si="2"/>
         <v>-3.09606088289526</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="7">
         <f t="shared" si="3"/>
         <v>-39.8935863030622</v>
       </c>
@@ -15425,31 +16596,31 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <f>'L2'!C14*'L2'!D15-'L2'!D14*'L2'!C15</f>
         <v>-94.0729151439183</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="7">
         <f>'L2'!D14*'L2'!B15-'L2'!B14*'L2'!D15</f>
         <v>40.7577294254691</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="7">
         <f>'L2'!B14*'L2'!C15-'L2'!C14*'L2'!B15</f>
         <v>167.5</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="7">
         <f t="shared" si="0"/>
         <v>196.385223149795</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="7">
         <f t="shared" si="1"/>
         <v>-22.7248212612383</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="7">
         <f t="shared" si="2"/>
         <v>9.84568315748187</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="7">
         <f t="shared" si="3"/>
         <v>-40.4623111278539</v>
       </c>
@@ -15466,31 +16637,31 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
         <f>'L2'!C15*'L2'!D16-'L2'!D15*'L2'!C16</f>
         <v>-94.8732947977217</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="7">
         <f>'L2'!D15*'L2'!B16-'L2'!B15*'L2'!D16</f>
         <v>22.8218737313549</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="7">
         <f>'L2'!B15*'L2'!C16-'L2'!C15*'L2'!B16</f>
         <v>164.75</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="7">
         <f t="shared" si="0"/>
         <v>191.479352637263</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="7">
         <f t="shared" si="1"/>
         <v>-23.50534949703</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="7">
         <f t="shared" si="2"/>
         <v>5.65423725797986</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="7">
         <f t="shared" si="3"/>
         <v>-40.8176646325209</v>
       </c>
@@ -15507,31 +16678,31 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="7">
         <f>'L2'!C16*'L2'!D17-'L2'!D16*'L2'!C17</f>
         <v>-81.9827870014967</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="7">
         <f>'L2'!D16*'L2'!B17-'L2'!B16*'L2'!D17</f>
         <v>49.6478955495716</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="7">
         <f>'L2'!B16*'L2'!C17-'L2'!C16*'L2'!B17</f>
         <v>144.25</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="7">
         <f t="shared" si="0"/>
         <v>173.188202245517</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="7">
         <f t="shared" si="1"/>
         <v>-22.4568611771688</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="7">
         <f t="shared" si="2"/>
         <v>13.5996340070136</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="7">
         <f t="shared" si="3"/>
         <v>-39.5131995786806</v>
       </c>
@@ -15548,31 +16719,31 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="7">
         <f>'L2'!C17*'L2'!D18-'L2'!D17*'L2'!C18</f>
         <v>-79.4913998574598</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="7">
         <f>'L2'!D17*'L2'!B18-'L2'!B17*'L2'!D18</f>
         <v>-24.9460644272376</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="7">
         <f>'L2'!B17*'L2'!C18-'L2'!C17*'L2'!B18</f>
         <v>146.25</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="7">
         <f t="shared" si="0"/>
         <v>168.315926999516</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="7">
         <f t="shared" si="1"/>
         <v>-22.404724713002</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="7">
         <f t="shared" si="2"/>
         <v>-7.03107137586305</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="7">
         <f t="shared" si="3"/>
         <v>-41.2206980271091</v>
       </c>
@@ -15589,31 +16760,31 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="7">
         <f>'L2'!C18*'L2'!D19-'L2'!D18*'L2'!C19</f>
         <v>-82.4699051148075</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="7">
         <f>'L2'!D18*'L2'!B19-'L2'!B18*'L2'!D19</f>
         <v>-2.74266159973683</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="7">
         <f>'L2'!B18*'L2'!C19-'L2'!C18*'L2'!B19</f>
         <v>146.25</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="7">
         <f t="shared" si="0"/>
         <v>167.92221396318</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="7">
         <f t="shared" si="1"/>
         <v>-23.2987179379634</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="7">
         <f t="shared" si="2"/>
         <v>-0.774834152198856</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="7">
         <f t="shared" si="3"/>
         <v>-41.3173447172469</v>
       </c>
@@ -15630,31 +16801,31 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="7">
         <f>-('L2'!C19*'L2'!D2-'L2'!D19*'L2'!C2)</f>
         <v>-1092.82893312546</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="7">
         <f>-('L2'!D19*'L2'!B2-'L2'!B19*'L2'!D2)</f>
         <v>972.098461421014</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="7">
         <f>-('L2'!B19*'L2'!C2-'L2'!C19*'L2'!B2)</f>
         <v>1543.5</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="7">
         <f t="shared" si="0"/>
         <v>2126.41546875798</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="7">
         <f t="shared" si="1"/>
         <v>-24.3808443595236</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="7">
         <f t="shared" si="2"/>
         <v>21.687366221404</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="7">
         <f t="shared" si="3"/>
         <v>-34.435246110568</v>
       </c>
@@ -15681,8 +16852,8 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
+      <c r="A21" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -15723,34 +16894,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="F1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>18</v>
       </c>
     </row>
@@ -15758,31 +16929,31 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <f>'L2'!C2*'L2'!D4-'L2'!D2*'L2'!C4</f>
         <v>68.1366225707045</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="7">
         <f>'L2'!D2*'L2'!B4-'L2'!B2*'L2'!D4</f>
         <v>212.953302932885</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="7">
         <f>'L2'!B2*'L2'!C4-'L2'!C2*'L2'!B4</f>
         <v>238.75</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="7">
         <f>SQRT(B2*B2+C2*C2+D2*D2)</f>
         <v>327.098259037506</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="7">
         <f>B2/E2*47.44</f>
         <v>9.88205007347221</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="7">
         <f>C2/E2*47.44</f>
         <v>30.8852291689442</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="7">
         <f>-D2/E2*47.44</f>
         <v>-34.6265982378747</v>
       </c>
@@ -15799,39 +16970,39 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <f>'L2'!C3*'L2'!D5-'L2'!D3*'L2'!C5</f>
         <v>-3.88592536258534</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <f>'L2'!D3*'L2'!B5-'L2'!B3*'L2'!D5</f>
         <v>200.022821603777</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="7">
         <f>'L2'!B3*'L2'!C5-'L2'!C3*'L2'!B5</f>
         <v>261</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="7">
         <f t="shared" ref="E3:E19" si="0">SQRT(B3*B3+C3*C3+D3*D3)</f>
         <v>328.85442003759</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="7">
         <f t="shared" ref="F3:F19" si="1">B3/E3*47.44</f>
         <v>-0.560577228002519</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="7">
         <f t="shared" ref="G3:G19" si="2">C3/E3*47.44</f>
         <v>28.8549646247677</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="7">
         <f t="shared" ref="H3:H19" si="3">-D3/E3*47.44</f>
         <v>-37.6514325049506</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="7">
         <f t="shared" ref="I3:I19" si="4">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="7">
         <f t="shared" ref="J3:J19" si="5">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
@@ -15840,39 +17011,39 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="7">
         <f>'L2'!C4*'L2'!D6-'L2'!D4*'L2'!C6</f>
         <v>-34.9823358161882</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="7">
         <f>'L2'!D4*'L2'!B6-'L2'!B4*'L2'!D6</f>
         <v>210.559170332872</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="7">
         <f>'L2'!B4*'L2'!C6-'L2'!C4*'L2'!B6</f>
         <v>296.5</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="7">
         <f t="shared" si="0"/>
         <v>365.337074535865</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="7">
         <f t="shared" si="1"/>
         <v>-4.54255022769952</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="7">
         <f t="shared" si="2"/>
         <v>27.3416735853641</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="7">
         <f t="shared" si="3"/>
         <v>-38.5013210550005</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="7">
         <f t="shared" si="4"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="7">
         <f t="shared" si="5"/>
         <v>30.4809803249618</v>
       </c>
@@ -15881,39 +17052,39 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <f>'L2'!C5*'L2'!D7-'L2'!D5*'L2'!C7</f>
         <v>-75.06988248193</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="7">
         <f>'L2'!D5*'L2'!B7-'L2'!B5*'L2'!D7</f>
         <v>189.155064279935</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="7">
         <f>'L2'!B5*'L2'!C7-'L2'!C5*'L2'!B7</f>
         <v>301</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="7">
         <f t="shared" si="0"/>
         <v>363.340233938656</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="7">
         <f t="shared" si="1"/>
         <v>-9.801598865993</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="7">
         <f t="shared" si="2"/>
         <v>24.6972820823227</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="7">
         <f t="shared" si="3"/>
         <v>-39.3004645954262</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="7">
         <f t="shared" si="4"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="7">
         <f t="shared" si="5"/>
         <v>41.0716467855168</v>
       </c>
@@ -15922,39 +17093,39 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="7">
         <f>'L2'!C6*'L2'!D8-'L2'!D6*'L2'!C8</f>
         <v>-109.111728852548</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="7">
         <f>'L2'!D6*'L2'!B8-'L2'!B6*'L2'!D8</f>
         <v>146.788920273397</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="7">
         <f>'L2'!B6*'L2'!C8-'L2'!C6*'L2'!B8</f>
         <v>282.25</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="7">
         <f t="shared" si="0"/>
         <v>336.329331144671</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="7">
         <f t="shared" si="1"/>
         <v>-15.3904519690503</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="7">
         <f t="shared" si="2"/>
         <v>20.7049035957395</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="7">
         <f t="shared" si="3"/>
         <v>-39.8119900944363</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="7">
         <f t="shared" si="4"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="7">
         <f t="shared" si="5"/>
         <v>46.7134369557949</v>
       </c>
@@ -15963,39 +17134,39 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="7">
         <f>'L2'!C7*'L2'!D9-'L2'!D7*'L2'!C9</f>
         <v>-61.922055689335</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="7">
         <f>'L2'!D7*'L2'!B9-'L2'!B7*'L2'!D9</f>
         <v>162.576267909339</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="7">
         <f>'L2'!B7*'L2'!C9-'L2'!C7*'L2'!B9</f>
         <v>256</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="7">
         <f t="shared" si="0"/>
         <v>309.517986340249</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="7">
         <f t="shared" si="1"/>
         <v>-9.49082913285954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="7">
         <f t="shared" si="2"/>
         <v>24.918158200799</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="7">
         <f t="shared" si="3"/>
         <v>-39.2372674156958</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="7">
         <f t="shared" si="4"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="7">
         <f t="shared" si="5"/>
         <v>46.7265504432231</v>
       </c>
@@ -16004,39 +17175,39 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <f>'L2'!C8*'L2'!D10-'L2'!D8*'L2'!C10</f>
         <v>-103.603603001749</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="7">
         <f>'L2'!D8*'L2'!B10-'L2'!B8*'L2'!D10</f>
         <v>178.43153864594</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="7">
         <f>'L2'!B8*'L2'!C10-'L2'!C8*'L2'!B10</f>
         <v>310.75</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="7">
         <f t="shared" si="0"/>
         <v>373.010835014885</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="7">
         <f t="shared" si="1"/>
         <v>-13.17644010584</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="7">
         <f t="shared" si="2"/>
         <v>22.6931536533667</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="7">
         <f t="shared" si="3"/>
         <v>-39.5215865496554</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="7">
         <f t="shared" si="4"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="7">
         <f t="shared" si="5"/>
         <v>41.1094071546692</v>
       </c>
@@ -16045,39 +17216,39 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <f>'L2'!C9*'L2'!D11-'L2'!D9*'L2'!C11</f>
         <v>-193.745647385913</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="7">
         <f>'L2'!D9*'L2'!B11-'L2'!B9*'L2'!D11</f>
         <v>66.4427350621318</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="7">
         <f>'L2'!B9*'L2'!C11-'L2'!C9*'L2'!B11</f>
         <v>324.5</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="7">
         <f t="shared" si="0"/>
         <v>383.734625651013</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="7">
         <f t="shared" si="1"/>
         <v>-23.9522130597272</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="7">
         <f t="shared" si="2"/>
         <v>8.21412283554039</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="7">
         <f t="shared" si="3"/>
         <v>-40.1169948473722</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="7">
         <f t="shared" si="4"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="7">
         <f t="shared" si="5"/>
         <v>30.5388376877712</v>
       </c>
@@ -16086,39 +17257,39 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <f>'L2'!C10*'L2'!D12-'L2'!D10*'L2'!C12</f>
         <v>-157.657309059872</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="7">
         <f>'L2'!D10*'L2'!B12-'L2'!B10*'L2'!D12</f>
         <v>84.892397186085</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="7">
         <f>'L2'!B10*'L2'!C12-'L2'!C10*'L2'!B12</f>
         <v>299.75</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="7">
         <f t="shared" si="0"/>
         <v>349.159861238373</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="7">
         <f t="shared" si="1"/>
         <v>-21.4207403888679</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="7">
         <f t="shared" si="2"/>
         <v>11.534244824775</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="7">
         <f t="shared" si="3"/>
         <v>-40.7267317313196</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="7">
         <f t="shared" si="4"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="7">
         <f t="shared" si="5"/>
         <v>16.2885294815216</v>
       </c>
@@ -16127,39 +17298,39 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <f>'L2'!C11*'L2'!D13-'L2'!D11*'L2'!C13</f>
         <v>-141.357368712002</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="7">
         <f>'L2'!D11*'L2'!B13-'L2'!B11*'L2'!D13</f>
         <v>128.347601096585</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="7">
         <f>'L2'!B11*'L2'!C13-'L2'!C11*'L2'!B13</f>
         <v>297.25</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="7">
         <f t="shared" si="0"/>
         <v>353.288232037849</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="7">
         <f t="shared" si="1"/>
         <v>-18.9816500057634</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="7">
         <f t="shared" si="2"/>
         <v>17.2346816108205</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="7">
         <f t="shared" si="3"/>
         <v>-39.9151138396516</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="7">
         <f t="shared" si="4"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="7">
         <f t="shared" si="5"/>
         <v>0.0755554543581351</v>
       </c>
@@ -16168,39 +17339,39 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="7">
         <f>'L2'!C12*'L2'!D14-'L2'!D12*'L2'!C14</f>
         <v>-161.513643207402</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="7">
         <f>'L2'!D12*'L2'!B14-'L2'!B12*'L2'!D14</f>
         <v>39.4716580909189</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="7">
         <f>'L2'!B12*'L2'!C14-'L2'!C12*'L2'!B14</f>
         <v>275.75</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="7">
         <f t="shared" si="0"/>
         <v>321.998029861324</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="7">
         <f t="shared" si="1"/>
         <v>-23.7958202323754</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="7">
         <f t="shared" si="2"/>
         <v>5.81536309597809</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="7">
         <f t="shared" si="3"/>
         <v>-40.6262734142624</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="7">
         <f t="shared" si="4"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="7">
         <f t="shared" si="5"/>
         <v>-16.1465225320068</v>
       </c>
@@ -16209,39 +17380,39 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <f>'L2'!C13*'L2'!D15-'L2'!D13*'L2'!C15</f>
         <v>-169.363099197816</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="7">
         <f>'L2'!D13*'L2'!B15-'L2'!B13*'L2'!D15</f>
         <v>30.4344679753649</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="7">
         <f>'L2'!B13*'L2'!C15-'L2'!C13*'L2'!B15</f>
         <v>291.75</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="7">
         <f t="shared" si="0"/>
         <v>338.715483423526</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="7">
         <f t="shared" si="1"/>
         <v>-23.7207503617366</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="7">
         <f t="shared" si="2"/>
         <v>4.26260750219672</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="7">
         <f t="shared" si="3"/>
         <v>-40.862082418281</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="7">
         <f t="shared" si="4"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="7">
         <f t="shared" si="5"/>
         <v>-30.4230456457766</v>
       </c>
@@ -16250,39 +17421,39 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <f>'L2'!C14*'L2'!D16-'L2'!D14*'L2'!C16</f>
         <v>-189.528304235315</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="7">
         <f>'L2'!D14*'L2'!B16-'L2'!B14*'L2'!D16</f>
         <v>63.5192819464876</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="7">
         <f>'L2'!B14*'L2'!C16-'L2'!C14*'L2'!B16</f>
         <v>330.25</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="7">
         <f t="shared" si="0"/>
         <v>386.03204502387</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="7">
         <f t="shared" si="1"/>
         <v>-23.2913895849433</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="7">
         <f t="shared" si="2"/>
         <v>7.80597044826949</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="7">
         <f t="shared" si="3"/>
         <v>-40.5848690593322</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="7">
         <f t="shared" si="4"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="7">
         <f t="shared" si="5"/>
         <v>-41.0337822362874</v>
       </c>
@@ -16291,39 +17462,39 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
         <f>'L2'!C15*'L2'!D17-'L2'!D15*'L2'!C17</f>
         <v>-174.105825941859</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="7">
         <f>'L2'!D15*'L2'!B17-'L2'!B15*'L2'!D17</f>
         <v>72.1426226733871</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="7">
         <f>'L2'!B15*'L2'!C17-'L2'!C15*'L2'!B17</f>
         <v>309.25</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="7">
         <f t="shared" si="0"/>
         <v>362.150464769951</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="7">
         <f t="shared" si="1"/>
         <v>-22.8070406810841</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="7">
         <f t="shared" si="2"/>
         <v>9.45034275131892</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="7">
         <f t="shared" si="3"/>
         <v>-40.5102890295042</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="7">
         <f t="shared" si="4"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="7">
         <f t="shared" si="5"/>
         <v>-46.7002049776354</v>
       </c>
@@ -16332,39 +17503,39 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="7">
         <f>'L2'!C16*'L2'!D18-'L2'!D16*'L2'!C18</f>
         <v>-165.834114361021</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="7">
         <f>'L2'!D16*'L2'!B18-'L2'!B16*'L2'!D18</f>
         <v>24.4042186991734</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="7">
         <f>'L2'!B16*'L2'!C18-'L2'!C16*'L2'!B18</f>
         <v>287</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="7">
         <f t="shared" si="0"/>
         <v>332.363534967694</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="7">
         <f t="shared" si="1"/>
         <v>-23.6703776364984</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="7">
         <f t="shared" si="2"/>
         <v>3.48334282580464</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="7">
         <f t="shared" si="3"/>
         <v>-40.9650234383367</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="7">
         <f t="shared" si="4"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="7">
         <f t="shared" si="5"/>
         <v>-46.7395454066571</v>
       </c>
@@ -16373,39 +17544,39 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="7">
         <f>'L2'!C17*'L2'!D19-'L2'!D17*'L2'!C19</f>
         <v>-160.065892535773</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="7">
         <f>'L2'!D17*'L2'!B19-'L2'!B17*'L2'!D19</f>
         <v>-27.417952821761</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="7">
         <f>'L2'!B17*'L2'!C19-'L2'!C17*'L2'!B19</f>
         <v>292.5</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="7">
         <f t="shared" si="0"/>
         <v>334.558042931582</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="7">
         <f t="shared" si="1"/>
         <v>-22.6971854430951</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="7">
         <f t="shared" si="2"/>
         <v>-3.88783862574884</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="7">
         <f t="shared" si="3"/>
         <v>-41.4762110586525</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="7">
         <f t="shared" si="4"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="7">
         <f t="shared" si="5"/>
         <v>-41.1470632479638</v>
       </c>
@@ -16414,39 +17585,39 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="7">
         <f>-('L2'!C18*'L2'!D2-'L2'!D18*'L2'!C2)</f>
         <v>-997.719524035898</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="7">
         <f>-('L2'!D18*'L2'!B2-'L2'!B18*'L2'!D2)</f>
         <v>984.74301736936</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="7">
         <f>-('L2'!B18*'L2'!C2-'L2'!C18*'L2'!B2)</f>
         <v>1528.25</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="7">
         <f t="shared" si="0"/>
         <v>2073.81559483965</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="7">
         <f t="shared" si="1"/>
         <v>-22.8235405009204</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="7">
         <f t="shared" si="2"/>
         <v>22.5266937235153</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="7">
         <f t="shared" si="3"/>
         <v>-34.9598007558651</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="7">
         <f t="shared" si="4"/>
         <v>36.254663040877</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="7">
         <f t="shared" si="5"/>
         <v>-30.5966175874469</v>
       </c>
@@ -16455,46 +17626,46 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="7">
         <f>-('L2'!C19*'L2'!D3-'L2'!D19*'L2'!C3)</f>
         <v>-1078.35072351006</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="7">
         <f>-('L2'!D19*'L2'!B3-'L2'!B19*'L2'!D3)</f>
         <v>814.920121938485</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="7">
         <f>-('L2'!B19*'L2'!C3-'L2'!C19*'L2'!B3)</f>
         <v>1579.5</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="7">
         <f t="shared" si="0"/>
         <v>2078.88319489935</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="7">
         <f t="shared" si="1"/>
         <v>-24.6079041135326</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="7">
         <f t="shared" si="2"/>
         <v>18.596432295771</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="7">
         <f t="shared" si="3"/>
         <v>-36.0441029990759</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="7">
         <f t="shared" si="4"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="7">
         <f t="shared" si="5"/>
         <v>-16.3594710714245</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
+      <c r="A21" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -16519,78 +17690,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="F1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="K1" s="6" t="s">
         <v>35</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <f>'L2'!C2*'L2'!D4-'L2'!D2*'L2'!C4</f>
         <v>68.1366225707045</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="7">
         <f>'L2'!D2*'L2'!B4-'L2'!B2*'L2'!D4</f>
         <v>212.953302932885</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="7">
         <f>'L2'!B2*'L2'!C4-'L2'!C2*'L2'!B4</f>
         <v>238.75</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="7">
         <f>SQRT(B2*B2+C2*C2+D2*D2)</f>
         <v>327.098259037506</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="7">
         <f>B2/E2*47.44</f>
         <v>9.88205007347221</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="7">
         <f>C2/E2*47.44</f>
         <v>30.8852291689442</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="7">
         <f>-D2/E2*47.44</f>
         <v>-34.6265982378747</v>
       </c>
@@ -16623,39 +17794,39 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <f>'L2'!C3*'L2'!D5-'L2'!D3*'L2'!C5</f>
         <v>-3.88592536258534</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <f>'L2'!D3*'L2'!B5-'L2'!B3*'L2'!D5</f>
         <v>200.022821603777</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="7">
         <f>'L2'!B3*'L2'!C5-'L2'!C3*'L2'!B5</f>
         <v>261</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="7">
         <f t="shared" ref="E3:E19" si="0">SQRT(B3*B3+C3*C3+D3*D3)</f>
         <v>328.85442003759</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="7">
         <f t="shared" ref="F3:F19" si="1">B3/E3*47.44</f>
         <v>-0.560577228002519</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="7">
         <f t="shared" ref="G3:G19" si="2">C3/E3*47.44</f>
         <v>28.8549646247677</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="7">
         <f t="shared" ref="H3:H19" si="3">-D3/E3*47.44</f>
         <v>-37.6514325049506</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="7">
         <f t="shared" ref="I3:I19" si="4">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="7">
         <f t="shared" ref="J3:J19" si="5">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
@@ -16668,39 +17839,39 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="7">
         <f>'L2'!C4*'L2'!D6-'L2'!D4*'L2'!C6</f>
         <v>-34.9823358161882</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="7">
         <f>'L2'!D4*'L2'!B6-'L2'!B4*'L2'!D6</f>
         <v>210.559170332872</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="7">
         <f>'L2'!B4*'L2'!C6-'L2'!C4*'L2'!B6</f>
         <v>296.5</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="7">
         <f t="shared" si="0"/>
         <v>365.337074535865</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="7">
         <f t="shared" si="1"/>
         <v>-4.54255022769952</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="7">
         <f t="shared" si="2"/>
         <v>27.3416735853641</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="7">
         <f t="shared" si="3"/>
         <v>-38.5013210550005</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="7">
         <f t="shared" si="4"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="7">
         <f t="shared" si="5"/>
         <v>30.4809803249618</v>
       </c>
@@ -16713,39 +17884,39 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="7">
         <f>'L2'!C5*'L2'!D7-'L2'!D5*'L2'!C7</f>
         <v>-75.06988248193</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="7">
         <f>'L2'!D5*'L2'!B7-'L2'!B5*'L2'!D7</f>
         <v>189.155064279935</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="7">
         <f>'L2'!B5*'L2'!C7-'L2'!C5*'L2'!B7</f>
         <v>301</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="7">
         <f t="shared" si="0"/>
         <v>363.340233938656</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="7">
         <f t="shared" si="1"/>
         <v>-9.801598865993</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="7">
         <f t="shared" si="2"/>
         <v>24.6972820823227</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="7">
         <f t="shared" si="3"/>
         <v>-39.3004645954262</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="7">
         <f t="shared" si="4"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="7">
         <f t="shared" si="5"/>
         <v>41.0716467855168</v>
       </c>
@@ -16758,39 +17929,39 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="7">
         <f>'L2'!C6*'L2'!D8-'L2'!D6*'L2'!C8</f>
         <v>-109.111728852548</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="7">
         <f>'L2'!D6*'L2'!B8-'L2'!B6*'L2'!D8</f>
         <v>146.788920273397</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="7">
         <f>'L2'!B6*'L2'!C8-'L2'!C6*'L2'!B8</f>
         <v>282.25</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="7">
         <f t="shared" si="0"/>
         <v>336.329331144671</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="7">
         <f t="shared" si="1"/>
         <v>-15.3904519690503</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="7">
         <f t="shared" si="2"/>
         <v>20.7049035957395</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="7">
         <f t="shared" si="3"/>
         <v>-39.8119900944363</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="7">
         <f t="shared" si="4"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="7">
         <f t="shared" si="5"/>
         <v>46.7134369557949</v>
       </c>
@@ -16803,39 +17974,39 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="7">
         <f>'L2'!C7*'L2'!D9-'L2'!D7*'L2'!C9</f>
         <v>-61.922055689335</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="7">
         <f>'L2'!D7*'L2'!B9-'L2'!B7*'L2'!D9</f>
         <v>162.576267909339</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="7">
         <f>'L2'!B7*'L2'!C9-'L2'!C7*'L2'!B9</f>
         <v>256</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="7">
         <f t="shared" si="0"/>
         <v>309.517986340249</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="7">
         <f t="shared" si="1"/>
         <v>-9.49082913285954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="7">
         <f t="shared" si="2"/>
         <v>24.918158200799</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="7">
         <f t="shared" si="3"/>
         <v>-39.2372674156958</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="7">
         <f t="shared" si="4"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="7">
         <f t="shared" si="5"/>
         <v>46.7265504432231</v>
       </c>
@@ -16848,39 +18019,39 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="7">
         <f>'L2'!C8*'L2'!D10-'L2'!D8*'L2'!C10</f>
         <v>-103.603603001749</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="7">
         <f>'L2'!D8*'L2'!B10-'L2'!B8*'L2'!D10</f>
         <v>178.43153864594</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="7">
         <f>'L2'!B8*'L2'!C10-'L2'!C8*'L2'!B10</f>
         <v>310.75</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="7">
         <f t="shared" si="0"/>
         <v>373.010835014885</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="7">
         <f t="shared" si="1"/>
         <v>-13.17644010584</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="7">
         <f t="shared" si="2"/>
         <v>22.6931536533667</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="7">
         <f t="shared" si="3"/>
         <v>-39.5215865496554</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="7">
         <f t="shared" si="4"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="7">
         <f t="shared" si="5"/>
         <v>41.1094071546692</v>
       </c>
@@ -16893,39 +18064,39 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="7">
         <f>'L2'!C9*'L2'!D11-'L2'!D9*'L2'!C11</f>
         <v>-193.745647385913</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="7">
         <f>'L2'!D9*'L2'!B11-'L2'!B9*'L2'!D11</f>
         <v>66.4427350621318</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="7">
         <f>'L2'!B9*'L2'!C11-'L2'!C9*'L2'!B11</f>
         <v>324.5</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="7">
         <f t="shared" si="0"/>
         <v>383.734625651013</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="7">
         <f t="shared" si="1"/>
         <v>-23.9522130597272</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="7">
         <f t="shared" si="2"/>
         <v>8.21412283554039</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="7">
         <f t="shared" si="3"/>
         <v>-40.1169948473722</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="7">
         <f t="shared" si="4"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="7">
         <f t="shared" si="5"/>
         <v>30.5388376877712</v>
       </c>
@@ -16938,39 +18109,39 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="7">
         <f>'L2'!C10*'L2'!D12-'L2'!D10*'L2'!C12</f>
         <v>-157.657309059872</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="7">
         <f>'L2'!D10*'L2'!B12-'L2'!B10*'L2'!D12</f>
         <v>84.892397186085</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="7">
         <f>'L2'!B10*'L2'!C12-'L2'!C10*'L2'!B12</f>
         <v>299.75</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="7">
         <f t="shared" si="0"/>
         <v>349.159861238373</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="7">
         <f t="shared" si="1"/>
         <v>-21.4207403888679</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="7">
         <f t="shared" si="2"/>
         <v>11.534244824775</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="7">
         <f t="shared" si="3"/>
         <v>-40.7267317313196</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="7">
         <f t="shared" si="4"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="7">
         <f t="shared" si="5"/>
         <v>16.2885294815216</v>
       </c>
@@ -16983,39 +18154,39 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <f>'L2'!C11*'L2'!D13-'L2'!D11*'L2'!C13</f>
         <v>-141.357368712002</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="7">
         <f>'L2'!D11*'L2'!B13-'L2'!B11*'L2'!D13</f>
         <v>128.347601096585</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="7">
         <f>'L2'!B11*'L2'!C13-'L2'!C11*'L2'!B13</f>
         <v>297.25</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="7">
         <f t="shared" si="0"/>
         <v>353.288232037849</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="7">
         <f t="shared" si="1"/>
         <v>-18.9816500057634</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="7">
         <f t="shared" si="2"/>
         <v>17.2346816108205</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="7">
         <f t="shared" si="3"/>
         <v>-39.9151138396516</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="7">
         <f t="shared" si="4"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="7">
         <f t="shared" si="5"/>
         <v>0.0755554543581351</v>
       </c>
@@ -17028,39 +18199,39 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="7">
         <f>'L2'!C12*'L2'!D14-'L2'!D12*'L2'!C14</f>
         <v>-161.513643207402</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="7">
         <f>'L2'!D12*'L2'!B14-'L2'!B12*'L2'!D14</f>
         <v>39.4716580909189</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="7">
         <f>'L2'!B12*'L2'!C14-'L2'!C12*'L2'!B14</f>
         <v>275.75</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="7">
         <f t="shared" si="0"/>
         <v>321.998029861324</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="7">
         <f t="shared" si="1"/>
         <v>-23.7958202323754</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="7">
         <f t="shared" si="2"/>
         <v>5.81536309597809</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="7">
         <f t="shared" si="3"/>
         <v>-40.6262734142624</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="7">
         <f t="shared" si="4"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="7">
         <f t="shared" si="5"/>
         <v>-16.1465225320068</v>
       </c>
@@ -17073,39 +18244,39 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <f>'L2'!C13*'L2'!D15-'L2'!D13*'L2'!C15</f>
         <v>-169.363099197816</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="7">
         <f>'L2'!D13*'L2'!B15-'L2'!B13*'L2'!D15</f>
         <v>30.4344679753649</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="7">
         <f>'L2'!B13*'L2'!C15-'L2'!C13*'L2'!B15</f>
         <v>291.75</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="7">
         <f t="shared" si="0"/>
         <v>338.715483423526</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="7">
         <f t="shared" si="1"/>
         <v>-23.7207503617366</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="7">
         <f t="shared" si="2"/>
         <v>4.26260750219672</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="7">
         <f t="shared" si="3"/>
         <v>-40.862082418281</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="7">
         <f t="shared" si="4"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="7">
         <f t="shared" si="5"/>
         <v>-30.4230456457766</v>
       </c>
@@ -17118,39 +18289,39 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <f>'L2'!C14*'L2'!D16-'L2'!D14*'L2'!C16</f>
         <v>-189.528304235315</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="7">
         <f>'L2'!D14*'L2'!B16-'L2'!B14*'L2'!D16</f>
         <v>63.5192819464876</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="7">
         <f>'L2'!B14*'L2'!C16-'L2'!C14*'L2'!B16</f>
         <v>330.25</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="7">
         <f t="shared" si="0"/>
         <v>386.03204502387</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="7">
         <f t="shared" si="1"/>
         <v>-23.2913895849433</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="7">
         <f t="shared" si="2"/>
         <v>7.80597044826949</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="7">
         <f t="shared" si="3"/>
         <v>-40.5848690593322</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="7">
         <f t="shared" si="4"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="7">
         <f t="shared" si="5"/>
         <v>-41.0337822362874</v>
       </c>
@@ -17163,39 +18334,39 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
         <f>'L2'!C15*'L2'!D17-'L2'!D15*'L2'!C17</f>
         <v>-174.105825941859</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="7">
         <f>'L2'!D15*'L2'!B17-'L2'!B15*'L2'!D17</f>
         <v>72.1426226733871</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="7">
         <f>'L2'!B15*'L2'!C17-'L2'!C15*'L2'!B17</f>
         <v>309.25</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="7">
         <f t="shared" si="0"/>
         <v>362.150464769951</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="7">
         <f t="shared" si="1"/>
         <v>-22.8070406810841</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="7">
         <f t="shared" si="2"/>
         <v>9.45034275131892</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="7">
         <f t="shared" si="3"/>
         <v>-40.5102890295042</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="7">
         <f t="shared" si="4"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="7">
         <f t="shared" si="5"/>
         <v>-46.7002049776354</v>
       </c>
@@ -17208,39 +18379,39 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="7">
         <f>'L2'!C16*'L2'!D18-'L2'!D16*'L2'!C18</f>
         <v>-165.834114361021</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="7">
         <f>'L2'!D16*'L2'!B18-'L2'!B16*'L2'!D18</f>
         <v>24.4042186991734</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="7">
         <f>'L2'!B16*'L2'!C18-'L2'!C16*'L2'!B18</f>
         <v>287</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="7">
         <f t="shared" si="0"/>
         <v>332.363534967694</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="7">
         <f t="shared" si="1"/>
         <v>-23.6703776364984</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="7">
         <f t="shared" si="2"/>
         <v>3.48334282580464</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="7">
         <f t="shared" si="3"/>
         <v>-40.9650234383367</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="7">
         <f t="shared" si="4"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="7">
         <f t="shared" si="5"/>
         <v>-46.7395454066571</v>
       </c>
@@ -17253,39 +18424,39 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="7">
         <f>'L2'!C17*'L2'!D19-'L2'!D17*'L2'!C19</f>
         <v>-160.065892535773</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="7">
         <f>'L2'!D17*'L2'!B19-'L2'!B17*'L2'!D19</f>
         <v>-27.417952821761</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="7">
         <f>'L2'!B17*'L2'!C19-'L2'!C17*'L2'!B19</f>
         <v>292.5</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="7">
         <f t="shared" si="0"/>
         <v>334.558042931582</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="7">
         <f t="shared" si="1"/>
         <v>-22.6971854430951</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="7">
         <f t="shared" si="2"/>
         <v>-3.88783862574884</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="7">
         <f t="shared" si="3"/>
         <v>-41.4762110586525</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="7">
         <f t="shared" si="4"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="7">
         <f t="shared" si="5"/>
         <v>-41.1470632479638</v>
       </c>
@@ -17298,39 +18469,39 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="7">
         <f>-('L2'!C18*'L2'!D2-'L2'!D18*'L2'!C2)</f>
         <v>-997.719524035898</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="7">
         <f>-('L2'!D18*'L2'!B2-'L2'!B18*'L2'!D2)</f>
         <v>984.74301736936</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="7">
         <f>-('L2'!B18*'L2'!C2-'L2'!C18*'L2'!B2)</f>
         <v>1528.25</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="7">
         <f t="shared" si="0"/>
         <v>2073.81559483965</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="7">
         <f t="shared" si="1"/>
         <v>-22.8235405009204</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="7">
         <f t="shared" si="2"/>
         <v>22.5266937235153</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="7">
         <f t="shared" si="3"/>
         <v>-34.9598007558651</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="7">
         <f t="shared" si="4"/>
         <v>36.254663040877</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="7">
         <f t="shared" si="5"/>
         <v>-30.5966175874469</v>
       </c>
@@ -17343,39 +18514,39 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="7">
         <f>-('L2'!C19*'L2'!D3-'L2'!D19*'L2'!C3)</f>
         <v>-1078.35072351006</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="7">
         <f>-('L2'!D19*'L2'!B3-'L2'!B19*'L2'!D3)</f>
         <v>814.920121938485</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="7">
         <f>-('L2'!B19*'L2'!C3-'L2'!C19*'L2'!B3)</f>
         <v>1579.5</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="7">
         <f t="shared" si="0"/>
         <v>2078.88319489935</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="7">
         <f t="shared" si="1"/>
         <v>-24.6079041135326</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="7">
         <f t="shared" si="2"/>
         <v>18.596432295771</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="7">
         <f t="shared" si="3"/>
         <v>-36.0441029990759</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="7">
         <f t="shared" si="4"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="7">
         <f t="shared" si="5"/>
         <v>-16.3594710714245</v>
       </c>
@@ -17385,18 +18556,18 @@
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
+      <c r="A21" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="J24" s="1" t="s">
-        <v>36</v>
+      <c r="J24" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="J25" s="1" t="s">
-        <v>37</v>
+      <c r="J25" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -17413,483 +18584,483 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="10" style="3"/>
-    <col min="2" max="2" width="12.8888888888889" style="4"/>
-    <col min="3" max="3" width="10" style="4"/>
-    <col min="4" max="4" width="23.8055555555556" style="4" customWidth="1"/>
-    <col min="5" max="6" width="10" style="4"/>
-    <col min="7" max="7" width="22.4814814814815" style="4" customWidth="1"/>
+    <col min="1" max="1" width="10" style="1"/>
+    <col min="2" max="2" width="12.8888888888889" style="5"/>
+    <col min="3" max="3" width="10" style="5"/>
+    <col min="4" max="4" width="23.8055555555556" style="5" customWidth="1"/>
+    <col min="5" max="6" width="10" style="5"/>
+    <col min="7" max="7" width="22.4814814814815" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>43</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>25</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="5">
         <v>884.558479532164</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>517.09649122807</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="5">
         <f>SQRT((B2-'L1'!B2)^2+(C2-'L1'!C2)^2)</f>
         <v>0.905399335451789</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="5">
         <v>884.556923951664</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="5">
         <v>517.094107579775</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <f>SQRT((E2-'L1'!B2)^2+(F2-'L1'!C2)^2)</f>
         <v>0.907679135649873</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>45</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="5">
         <v>880.819573443412</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>519.536119711042</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <f>SQRT((B3-'L1'!B3)^2+(C3-'L1'!C3)^2)</f>
         <v>0.497733527910207</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="5">
         <v>880.818200872383</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="5">
         <v>519.534016491958</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="5">
         <f>SQRT((E3-'L1'!B3)^2+(F3-'L1'!C3)^2)</f>
         <v>0.500191515891052</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>65</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <v>877.080667354661</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>521.975748194014</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <f>SQRT((B4-'L1'!B4)^2+(C4-'L1'!C4)^2)</f>
         <v>0.420033352890632</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>877.079477793103</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>521.973925404142</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <f>SQRT((E4-'L1'!B4)^2+(F4-'L1'!C4)^2)</f>
         <v>0.42132981266777</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>85</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>873.34176126591</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>524.415376676986</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <f>SQRT((B5-'L1'!B5)^2+(C5-'L1'!C5)^2)</f>
         <v>0.352082191646118</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>873.340754713822</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>524.413834316325</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <f>SQRT((E5-'L1'!B5)^2+(F5-'L1'!C5)^2)</f>
         <v>0.351480155961998</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>105</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>869.602855177159</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>526.855005159959</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <f>SQRT((B6-'L1'!B6)^2+(C6-'L1'!C6)^2)</f>
         <v>0.369604993291355</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>869.602031634541</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>526.853743228508</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <f>SQRT((E6-'L1'!B6)^2+(F6-'L1'!C6)^2)</f>
         <v>0.368163993571367</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>125</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <v>865.863949088407</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>529.294633642931</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <f>SQRT((B7-'L1'!B7)^2+(C7-'L1'!C7)^2)</f>
         <v>0.468260528444466</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>865.86330855526</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>529.293652140692</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <f>SQRT((E7-'L1'!B7)^2+(F7-'L1'!C7)^2)</f>
         <v>0.467145251563241</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>145</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>862.125042999656</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>531.734262125903</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <f>SQRT((B8-'L1'!B8)^2+(C8-'L1'!C8)^2)</f>
         <v>0.442121584792659</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>862.12458547598</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>531.733561052875</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <f>SQRT((E8-'L1'!B8)^2+(F8-'L1'!C8)^2)</f>
         <v>0.442138926430636</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>165</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>858.386136910905</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>534.173890608875</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <f>SQRT((B9-'L1'!B9)^2+(C9-'L1'!C9)^2)</f>
         <v>0.683442284167582</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>858.385862396699</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>534.173469965058</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <f>SQRT((E9-'L1'!B9)^2+(F9-'L1'!C9)^2)</f>
         <v>0.68307333890473</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>185</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>854.647230822153</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>536.613519091847</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <f>SQRT((B10-'L1'!B10)^2+(C10-'L1'!C10)^2)</f>
         <v>0.185912611744398</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>854.647139317418</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>536.613378877242</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="5">
         <f>SQRT((E10-'L1'!B10)^2+(F10-'L1'!C10)^2)</f>
         <v>0.185754538396484</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>205</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>850.908324733402</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>539.053147574819</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <f>SQRT((B11-'L1'!B11)^2+(C11-'L1'!C11)^2)</f>
         <v>0.10596706665264</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>850.908416238137</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>539.053287789425</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <f>SQRT((E11-'L1'!B11)^2+(F11-'L1'!C11)^2)</f>
         <v>0.105958359456848</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>225</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <v>847.169418644651</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>541.492776057791</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <f>SQRT((B12-'L1'!B12)^2+(C12-'L1'!C12)^2)</f>
         <v>0.521086288715682</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>847.169693158857</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>541.493196701608</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <f>SQRT((E12-'L1'!B12)^2+(F12-'L1'!C12)^2)</f>
         <v>0.521573345407762</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>245</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <v>843.430512555899</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>543.932404540764</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <f>SQRT((B13-'L1'!B13)^2+(C13-'L1'!C13)^2)</f>
         <v>0.610175997282732</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>843.430970079576</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>543.933105613792</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <f>SQRT((E13-'L1'!B13)^2+(F13-'L1'!C13)^2)</f>
         <v>0.610995648256113</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>265</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>839.691606467148</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>546.372033023736</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <f>SQRT((B14-'L1'!B14)^2+(C14-'L1'!C14)^2)</f>
         <v>0.483234044594445</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>839.692247000295</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>546.373014525975</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <f>SQRT((E14-'L1'!B14)^2+(F14-'L1'!C14)^2)</f>
         <v>0.483582201301707</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>285</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>835.952700378397</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>548.811661506708</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <f>SQRT((B15-'L1'!B15)^2+(C15-'L1'!C15)^2)</f>
         <v>0.194187132064121</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>835.953523921014</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <v>548.812923438158</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <f>SQRT((E15-'L1'!B15)^2+(F15-'L1'!C15)^2)</f>
         <v>0.192763237959237</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>305</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <v>832.213794289646</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>551.25128998968</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <f>SQRT((B16-'L1'!B16)^2+(C16-'L1'!C16)^2)</f>
         <v>0.327970528429927</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>832.214800841734</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>551.252832350341</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <f>SQRT((E16-'L1'!B16)^2+(F16-'L1'!C16)^2)</f>
         <v>0.327461827771715</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>325</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="5">
         <v>828.474888200894</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>553.690918472652</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <f>SQRT((B17-'L1'!B17)^2+(C17-'L1'!C17)^2)</f>
         <v>0.310099972592874</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <v>828.476077762453</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="5">
         <v>553.692741262525</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="5">
         <f>SQRT((E17-'L1'!B17)^2+(F17-'L1'!C17)^2)</f>
         <v>0.308188587076107</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>345</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="5">
         <v>824.735982112143</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>556.130546955624</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <f>SQRT((B18-'L1'!B18)^2+(C18-'L1'!C18)^2)</f>
         <v>0.454093599500305</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <v>824.737354683172</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="5">
         <v>556.132650174708</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="5">
         <f>SQRT((E18-'L1'!B18)^2+(F18-'L1'!C18)^2)</f>
         <v>0.451584384798342</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>365</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="5">
         <v>820.997076023392</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>558.570175438596</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <f>SQRT((B19-'L1'!B19)^2+(C19-'L1'!C19)^2)</f>
         <v>0.429834506787568</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>820.998631603891</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="5">
         <v>558.572559086891</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="5">
         <f>SQRT((E19-'L1'!B19)^2+(F19-'L1'!C19)^2)</f>
         <v>0.427443103473829</v>
       </c>
@@ -17904,496 +19075,736 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="15.5277777777778" style="1" customWidth="1"/>
+    <col min="2" max="6" width="12.8888888888889" style="1"/>
+    <col min="7" max="10" width="14.1111111111111" style="1"/>
+    <col min="11" max="11" width="9" style="1"/>
+    <col min="12" max="13" width="14.1111111111111" style="1"/>
+    <col min="14" max="14" width="13.1111111111111" style="1" customWidth="1"/>
+    <col min="15" max="16" width="14.1111111111111" style="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
+      <c r="H1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
+    <row r="2" spans="1:16">
+      <c r="A2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.0863602</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.0384723</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.995521</v>
+      </c>
+      <c r="E2" s="4">
+        <v>-26.9584</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="1">
         <v>25</v>
       </c>
-      <c r="B2" s="2">
-        <f>'L1'!E2-球心降噪!B2</f>
-        <v>9.44152046783597</v>
-      </c>
-      <c r="C2" s="2">
-        <f>-('L1'!F2-球心降噪!C2)</f>
-        <v>-36.90350877193</v>
-      </c>
-      <c r="D2" s="2">
-        <f t="shared" ref="D2:D19" si="0">SQRT(47.44*47.44-B2*B2-C2*C2)</f>
-        <v>28.2761795788526</v>
-      </c>
-      <c r="E2" s="2">
-        <f t="shared" ref="E2:E20" si="1">COS(3.14/9*((A2-25)/20))*47.44</f>
-        <v>47.44</v>
-      </c>
-      <c r="F2" s="2">
-        <f t="shared" ref="F2:F20" si="2">SIN(3.14/9*((A2-25)/20))*47.44</f>
-        <v>0</v>
+      <c r="H2" s="1">
+        <f>'L2'!H2*COS(ATAN2($C$2,$B$2))-'L2'!I2*SIN(ATAN2($C$2,$B$2))</f>
+        <v>37.5518708493067</v>
+      </c>
+      <c r="I2" s="1">
+        <f>('L2'!H2*SIN(ATAN2($C$2,$B$2))+'L2'!I2*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J2*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>27.5451356774842</v>
+      </c>
+      <c r="J2" s="1">
+        <f>('L2'!H2*SIN(ATAN2($C$2,$B$2))+'L2'!I2*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J2*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>9.03748284789415</v>
+      </c>
+      <c r="L2" s="1">
+        <f>'L2'!B2*COS(ATAN2($C$3,$B$3))-'L2'!C2*SIN(ATAN2($C$3,$B$3))</f>
+        <v>35.8845149077707</v>
+      </c>
+      <c r="M2" s="1">
+        <f>('L2'!B2*SIN(ATAN2($C$3,$B$3))+'L2'!C2*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D2*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>30.5971501314081</v>
+      </c>
+      <c r="O2" s="1">
+        <f>'L2'!B2*COS(ATAN2($C$4,$B$4))-'L2'!C2*SIN(ATAN2($C$4,$B$4))</f>
+        <v>35.9498521970467</v>
+      </c>
+      <c r="P2" s="1">
+        <f>('L2'!B2*SIN(ATAN2($C$4,$B$4))+'L2'!C2*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D2*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>30.5508991459797</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
+    <row r="3" spans="1:16">
+      <c r="A3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.157773</v>
+      </c>
+      <c r="C3" s="4">
+        <v>-0.00187582</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.987474</v>
+      </c>
+      <c r="E3" s="4">
+        <v>-29.6533</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="1">
         <v>45</v>
       </c>
-      <c r="B3" s="2">
-        <f>'L1'!E3-球心降噪!B3</f>
-        <v>13.680426556588</v>
-      </c>
-      <c r="C3" s="2">
-        <f>-('L1'!F3-球心降噪!C3)</f>
-        <v>-36.463880288958</v>
-      </c>
-      <c r="D3" s="2">
-        <f t="shared" si="0"/>
-        <v>27.0884655066016</v>
-      </c>
-      <c r="E3" s="2">
-        <f t="shared" si="1"/>
-        <v>44.5818885096479</v>
-      </c>
-      <c r="F3" s="2">
-        <f t="shared" si="2"/>
-        <v>16.2175465750319</v>
+      <c r="H3" s="1">
+        <f>'L2'!H3*COS(ATAN2($C$2,$B$2))-'L2'!I3*SIN(ATAN2($C$2,$B$2))</f>
+        <v>38.8752401167859</v>
+      </c>
+      <c r="I3" s="1">
+        <f>('L2'!H3*SIN(ATAN2($C$2,$B$2))+'L2'!I3*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J3*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.745727778357</v>
+      </c>
+      <c r="J3" s="1">
+        <f>('L2'!H3*SIN(ATAN2($C$2,$B$2))+'L2'!I3*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J3*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>4.89237687308159</v>
+      </c>
+      <c r="L3" s="1">
+        <f>'L2'!B3*COS(ATAN2($C$3,$B$3))-'L2'!C3*SIN(ATAN2($C$3,$B$3))</f>
+        <v>35.8369608285804</v>
+      </c>
+      <c r="M3" s="1">
+        <f>('L2'!B3*SIN(ATAN2($C$3,$B$3))+'L2'!C3*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D3*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.6397029782784</v>
+      </c>
+      <c r="O3" s="1">
+        <f>'L2'!B3*COS(ATAN2($C$4,$B$4))-'L2'!C3*SIN(ATAN2($C$4,$B$4))</f>
+        <v>35.9289443984996</v>
+      </c>
+      <c r="P3" s="1">
+        <f>('L2'!B3*SIN(ATAN2($C$4,$B$4))+'L2'!C3*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D3*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.5862794402994</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
+    <row r="4" spans="1:16">
+      <c r="B4" s="1">
+        <v>0.158025</v>
+      </c>
+      <c r="C4" s="1">
+        <v>-0.000826</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>-29.955569</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="1">
         <v>65</v>
       </c>
-      <c r="B4" s="2">
-        <f>'L1'!E4-球心降噪!B4</f>
-        <v>16.419332645339</v>
-      </c>
-      <c r="C4" s="2">
-        <f>-('L1'!F4-球心降噪!C4)</f>
-        <v>-35.524251805986</v>
-      </c>
-      <c r="D4" s="2">
-        <f t="shared" si="0"/>
-        <v>26.8139264022748</v>
-      </c>
-      <c r="E4" s="2">
-        <f t="shared" si="1"/>
-        <v>36.3519385786961</v>
-      </c>
-      <c r="F4" s="2">
-        <f t="shared" si="2"/>
-        <v>30.4809803249618</v>
+      <c r="H4" s="1">
+        <f>'L2'!H4*COS(ATAN2($C$2,$B$2))-'L2'!I4*SIN(ATAN2($C$2,$B$2))</f>
+        <v>39.1314806914079</v>
+      </c>
+      <c r="I4" s="1">
+        <f>('L2'!H4*SIN(ATAN2($C$2,$B$2))+'L2'!I4*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J4*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.7451004812523</v>
+      </c>
+      <c r="J4" s="1">
+        <f>('L2'!H4*SIN(ATAN2($C$2,$B$2))+'L2'!I4*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J4*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>1.99509878093546</v>
+      </c>
+      <c r="L4" s="1">
+        <f>'L2'!B4*COS(ATAN2($C$3,$B$3))-'L2'!C4*SIN(ATAN2($C$3,$B$3))</f>
+        <v>35.3072748645608</v>
+      </c>
+      <c r="M4" s="1">
+        <f>('L2'!B4*SIN(ATAN2($C$3,$B$3))+'L2'!C4*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D4*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.3495555866634</v>
+      </c>
+      <c r="O4" s="1">
+        <f>'L2'!B4*COS(ATAN2($C$4,$B$4))-'L2'!C4*SIN(ATAN2($C$4,$B$4))</f>
+        <v>35.415883854705</v>
+      </c>
+      <c r="P4" s="1">
+        <f>('L2'!B4*SIN(ATAN2($C$4,$B$4))+'L2'!C4*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D4*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.2922634575459</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
+    <row r="5" spans="1:16">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="1">
         <v>85</v>
       </c>
-      <c r="B5" s="2">
-        <f>'L1'!E5-球心降噪!B5</f>
-        <v>19.65823873409</v>
-      </c>
-      <c r="C5" s="2">
-        <f>-('L1'!F5-球心降噪!C5)</f>
-        <v>-34.0846233230139</v>
-      </c>
-      <c r="D5" s="2">
-        <f t="shared" si="0"/>
-        <v>26.5018056517245</v>
-      </c>
-      <c r="E5" s="2">
-        <f t="shared" si="1"/>
-        <v>23.7418076465493</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" si="2"/>
-        <v>41.0716467855168</v>
+      <c r="H5" s="1">
+        <f>'L2'!H5*COS(ATAN2($C$2,$B$2))-'L2'!I5*SIN(ATAN2($C$2,$B$2))</f>
+        <v>39.1344588684106</v>
+      </c>
+      <c r="I5" s="1">
+        <f>('L2'!H5*SIN(ATAN2($C$2,$B$2))+'L2'!I5*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J5*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.769476112824</v>
+      </c>
+      <c r="J5" s="1">
+        <f>('L2'!H5*SIN(ATAN2($C$2,$B$2))+'L2'!I5*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J5*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-1.56297079998958</v>
+      </c>
+      <c r="L5" s="1">
+        <f>'L2'!B5*COS(ATAN2($C$3,$B$3))-'L2'!C5*SIN(ATAN2($C$3,$B$3))</f>
+        <v>33.7598267917936</v>
+      </c>
+      <c r="M5" s="1">
+        <f>('L2'!B5*SIN(ATAN2($C$3,$B$3))+'L2'!C5*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D5*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.24349688588</v>
+      </c>
+      <c r="O5" s="1">
+        <f>'L2'!B5*COS(ATAN2($C$4,$B$4))-'L2'!C5*SIN(ATAN2($C$4,$B$4))</f>
+        <v>33.8949965470498</v>
+      </c>
+      <c r="P5" s="1">
+        <f>('L2'!B5*SIN(ATAN2($C$4,$B$4))+'L2'!C5*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D5*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.1808549636835</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
+    <row r="6" spans="1:16">
+      <c r="G6" s="1">
         <v>105</v>
       </c>
-      <c r="B6" s="2">
-        <f>'L1'!E6-球心降噪!B6</f>
-        <v>22.897144822841</v>
-      </c>
-      <c r="C6" s="2">
-        <f>-('L1'!F6-球心降噪!C6)</f>
-        <v>-32.144994840041</v>
-      </c>
-      <c r="D6" s="2">
-        <f t="shared" si="0"/>
-        <v>26.3243929786725</v>
-      </c>
-      <c r="E6" s="2">
-        <f t="shared" si="1"/>
-        <v>8.27093753917763</v>
-      </c>
-      <c r="F6" s="2">
-        <f t="shared" si="2"/>
-        <v>46.7134369557949</v>
+      <c r="H6" s="1">
+        <f>'L2'!H6*COS(ATAN2($C$2,$B$2))-'L2'!I6*SIN(ATAN2($C$2,$B$2))</f>
+        <v>38.6807080739839</v>
+      </c>
+      <c r="I6" s="1">
+        <f>('L2'!H6*SIN(ATAN2($C$2,$B$2))+'L2'!I6*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J6*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.9471925942159</v>
+      </c>
+      <c r="J6" s="1">
+        <f>('L2'!H6*SIN(ATAN2($C$2,$B$2))+'L2'!I6*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J6*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-5.31086002314791</v>
+      </c>
+      <c r="L6" s="1">
+        <f>'L2'!B6*COS(ATAN2($C$3,$B$3))-'L2'!C6*SIN(ATAN2($C$3,$B$3))</f>
+        <v>32.2242672388239</v>
+      </c>
+      <c r="M6" s="1">
+        <f>('L2'!B6*SIN(ATAN2($C$3,$B$3))+'L2'!C6*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D6*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.1601230450425</v>
+      </c>
+      <c r="O6" s="1">
+        <f>'L2'!B6*COS(ATAN2($C$4,$B$4))-'L2'!C6*SIN(ATAN2($C$4,$B$4))</f>
+        <v>32.3793361890314</v>
+      </c>
+      <c r="P6" s="1">
+        <f>('L2'!B6*SIN(ATAN2($C$4,$B$4))+'L2'!C6*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D6*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.0938654047332</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
+    <row r="7" spans="1:16">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1">
         <v>125</v>
       </c>
-      <c r="B7" s="2">
-        <f>'L1'!E7-球心降噪!B7</f>
-        <v>26.136050911593</v>
-      </c>
-      <c r="C7" s="2">
-        <f>-('L1'!F7-球心降噪!C7)</f>
-        <v>-29.705366357069</v>
-      </c>
-      <c r="D7" s="2">
-        <f t="shared" si="0"/>
-        <v>26.1734914052163</v>
-      </c>
-      <c r="E7" s="2">
-        <f t="shared" si="1"/>
-        <v>-8.19652875776856</v>
-      </c>
-      <c r="F7" s="2">
-        <f t="shared" si="2"/>
-        <v>46.7265504432231</v>
+      <c r="H7" s="1">
+        <f>'L2'!H7*COS(ATAN2($C$2,$B$2))-'L2'!I7*SIN(ATAN2($C$2,$B$2))</f>
+        <v>37.7702283081298</v>
+      </c>
+      <c r="I7" s="1">
+        <f>('L2'!H7*SIN(ATAN2($C$2,$B$2))+'L2'!I7*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J7*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>27.1705375759781</v>
+      </c>
+      <c r="J7" s="1">
+        <f>('L2'!H7*SIN(ATAN2($C$2,$B$2))+'L2'!I7*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J7*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-9.25879805288526</v>
+      </c>
+      <c r="L7" s="1">
+        <f>'L2'!B7*COS(ATAN2($C$3,$B$3))-'L2'!C7*SIN(ATAN2($C$3,$B$3))</f>
+        <v>29.6828340969042</v>
+      </c>
+      <c r="M7" s="1">
+        <f>('L2'!B7*SIN(ATAN2($C$3,$B$3))+'L2'!C7*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D7*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.3801203464063</v>
+      </c>
+      <c r="O7" s="1">
+        <f>'L2'!B7*COS(ATAN2($C$4,$B$4))-'L2'!C7*SIN(ATAN2($C$4,$B$4))</f>
+        <v>29.8610760167891</v>
+      </c>
+      <c r="P7" s="1">
+        <f>('L2'!B7*SIN(ATAN2($C$4,$B$4))+'L2'!C7*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D7*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.3105261921941</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
+    <row r="8" spans="1:16">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="1">
         <v>145</v>
       </c>
-      <c r="B8" s="2">
-        <f>'L1'!E8-球心降噪!B8</f>
-        <v>28.874957000344</v>
-      </c>
-      <c r="C8" s="2">
-        <f>-('L1'!F8-球心降噪!C8)</f>
-        <v>-27.765737874097</v>
-      </c>
-      <c r="D8" s="2">
-        <f t="shared" si="0"/>
-        <v>25.4136628319339</v>
-      </c>
-      <c r="E8" s="2">
-        <f t="shared" si="1"/>
-        <v>-23.6763646574306</v>
-      </c>
-      <c r="F8" s="2">
-        <f t="shared" si="2"/>
-        <v>41.1094071546692</v>
+      <c r="H8" s="1">
+        <f>'L2'!H8*COS(ATAN2($C$2,$B$2))-'L2'!I8*SIN(ATAN2($C$2,$B$2))</f>
+        <v>37.1130109398945</v>
+      </c>
+      <c r="I8" s="1">
+        <f>('L2'!H8*SIN(ATAN2($C$2,$B$2))+'L2'!I8*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J8*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.7252667800205</v>
+      </c>
+      <c r="J8" s="1">
+        <f>('L2'!H8*SIN(ATAN2($C$2,$B$2))+'L2'!I8*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J8*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-12.6070668480818</v>
+      </c>
+      <c r="L8" s="1">
+        <f>'L2'!B8*COS(ATAN2($C$3,$B$3))-'L2'!C8*SIN(ATAN2($C$3,$B$3))</f>
+        <v>27.6591983992064</v>
+      </c>
+      <c r="M8" s="1">
+        <f>('L2'!B8*SIN(ATAN2($C$3,$B$3))+'L2'!C8*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D8*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.8079942642832</v>
+      </c>
+      <c r="O8" s="1">
+        <f>'L2'!B8*COS(ATAN2($C$4,$B$4))-'L2'!C8*SIN(ATAN2($C$4,$B$4))</f>
+        <v>27.8506494387047</v>
+      </c>
+      <c r="P8" s="1">
+        <f>('L2'!B8*SIN(ATAN2($C$4,$B$4))+'L2'!C8*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D8*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.7371818700338</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
+    <row r="9" spans="1:16">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="1">
         <v>165</v>
       </c>
-      <c r="B9" s="2">
-        <f>'L1'!E9-球心降噪!B9</f>
-        <v>31.613863089095</v>
-      </c>
-      <c r="C9" s="2">
-        <f>-('L1'!F9-球心降噪!C9)</f>
-        <v>-25.326109391125</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" si="0"/>
-        <v>24.6922142322782</v>
-      </c>
-      <c r="E9" s="2">
-        <f t="shared" si="1"/>
-        <v>-36.3033468523216</v>
-      </c>
-      <c r="F9" s="2">
-        <f t="shared" si="2"/>
-        <v>30.5388376877712</v>
+      <c r="H9" s="1">
+        <f>'L2'!H9*COS(ATAN2($C$2,$B$2))-'L2'!I9*SIN(ATAN2($C$2,$B$2))</f>
+        <v>35.9990646002306</v>
+      </c>
+      <c r="I9" s="1">
+        <f>('L2'!H9*SIN(ATAN2($C$2,$B$2))+'L2'!I9*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J9*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.3374401962207</v>
+      </c>
+      <c r="J9" s="1">
+        <f>('L2'!H9*SIN(ATAN2($C$2,$B$2))+'L2'!I9*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J9*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-16.1542623421473</v>
+      </c>
+      <c r="L9" s="1">
+        <f>'L2'!B9*COS(ATAN2($C$3,$B$3))-'L2'!C9*SIN(ATAN2($C$3,$B$3))</f>
+        <v>25.6236741817111</v>
+      </c>
+      <c r="M9" s="1">
+        <f>('L2'!B9*SIN(ATAN2($C$3,$B$3))+'L2'!C9*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D9*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>28.847313317116</v>
+      </c>
+      <c r="O9" s="1">
+        <f>'L2'!B9*COS(ATAN2($C$4,$B$4))-'L2'!C9*SIN(ATAN2($C$4,$B$4))</f>
+        <v>25.8349959109836</v>
+      </c>
+      <c r="P9" s="1">
+        <f>('L2'!B9*SIN(ATAN2($C$4,$B$4))+'L2'!C9*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D9*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>28.7731762903532</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
+    <row r="10" spans="1:16">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="1">
         <v>185</v>
       </c>
-      <c r="B10" s="2">
-        <f>'L1'!E10-球心降噪!B10</f>
-        <v>33.852769177847</v>
-      </c>
-      <c r="C10" s="2">
-        <f>-('L1'!F10-球心降噪!C10)</f>
-        <v>-22.386480908153</v>
-      </c>
-      <c r="D10" s="2">
-        <f t="shared" si="0"/>
-        <v>24.5639795542236</v>
-      </c>
-      <c r="E10" s="2">
-        <f t="shared" si="1"/>
-        <v>-44.5560030448154</v>
-      </c>
-      <c r="F10" s="2">
-        <f t="shared" si="2"/>
-        <v>16.2885294815216</v>
+      <c r="H10" s="1">
+        <f>'L2'!H10*COS(ATAN2($C$2,$B$2))-'L2'!I10*SIN(ATAN2($C$2,$B$2))</f>
+        <v>34.224922715329</v>
+      </c>
+      <c r="I10" s="1">
+        <f>('L2'!H10*SIN(ATAN2($C$2,$B$2))+'L2'!I10*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J10*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.5162265042296</v>
+      </c>
+      <c r="J10" s="1">
+        <f>('L2'!H10*SIN(ATAN2($C$2,$B$2))+'L2'!I10*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J10*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-19.3932461724733</v>
+      </c>
+      <c r="L10" s="1">
+        <f>'L2'!B10*COS(ATAN2($C$3,$B$3))-'L2'!C10*SIN(ATAN2($C$3,$B$3))</f>
+        <v>22.0942002305375</v>
+      </c>
+      <c r="M10" s="1">
+        <f>('L2'!B10*SIN(ATAN2($C$3,$B$3))+'L2'!C10*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D10*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.3576299662944</v>
+      </c>
+      <c r="O10" s="1">
+        <f>'L2'!B10*COS(ATAN2($C$4,$B$4))-'L2'!C10*SIN(ATAN2($C$4,$B$4))</f>
+        <v>22.3219763489726</v>
+      </c>
+      <c r="P10" s="1">
+        <f>('L2'!B10*SIN(ATAN2($C$4,$B$4))+'L2'!C10*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D10*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.2830239091722</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
+    <row r="11" spans="1:16">
+      <c r="G11" s="1">
         <v>205</v>
       </c>
-      <c r="B11" s="2">
-        <f>'L1'!E11-球心降噪!B11</f>
-        <v>35.591675266598</v>
-      </c>
-      <c r="C11" s="2">
-        <f>-('L1'!F11-球心降噪!C11)</f>
-        <v>-18.946852425181</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>24.996060387498</v>
-      </c>
-      <c r="E11" s="2">
-        <f t="shared" si="1"/>
-        <v>-47.4399398331545</v>
-      </c>
-      <c r="F11" s="2">
-        <f t="shared" si="2"/>
-        <v>0.0755554543581351</v>
+      <c r="H11" s="1">
+        <f>'L2'!H11*COS(ATAN2($C$2,$B$2))-'L2'!I11*SIN(ATAN2($C$2,$B$2))</f>
+        <v>31.790585285189</v>
+      </c>
+      <c r="I11" s="1">
+        <f>('L2'!H11*SIN(ATAN2($C$2,$B$2))+'L2'!I11*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J11*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>27.2288746500686</v>
+      </c>
+      <c r="J11" s="1">
+        <f>('L2'!H11*SIN(ATAN2($C$2,$B$2))+'L2'!I11*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J11*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-22.3271286222832</v>
+      </c>
+      <c r="L11" s="1">
+        <f>'L2'!B11*COS(ATAN2($C$3,$B$3))-'L2'!C11*SIN(ATAN2($C$3,$B$3))</f>
+        <v>18.5766147991616</v>
+      </c>
+      <c r="M11" s="1">
+        <f>('L2'!B11*SIN(ATAN2($C$3,$B$3))+'L2'!C11*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D11*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>30.4082688974515</v>
+      </c>
+      <c r="O11" s="1">
+        <f>'L2'!B11*COS(ATAN2($C$4,$B$4))-'L2'!C11*SIN(ATAN2($C$4,$B$4))</f>
+        <v>18.8141837365984</v>
+      </c>
+      <c r="P11" s="1">
+        <f>('L2'!B11*SIN(ATAN2($C$4,$B$4))+'L2'!C11*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D11*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>30.3350689858281</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
+    <row r="12" spans="1:16">
+      <c r="G12" s="1">
         <v>225</v>
       </c>
-      <c r="B12" s="2">
-        <f>'L1'!E12-球心降噪!B12</f>
-        <v>37.330581355349</v>
-      </c>
-      <c r="C12" s="2">
-        <f>-('L1'!F12-球心降噪!C12)</f>
-        <v>-15.507223942209</v>
-      </c>
-      <c r="D12" s="2">
-        <f t="shared" si="0"/>
-        <v>24.8295650642103</v>
-      </c>
-      <c r="E12" s="2">
-        <f t="shared" si="1"/>
-        <v>-44.6076608905174</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="2"/>
-        <v>-16.1465225320068</v>
+      <c r="H12" s="1">
+        <f>'L2'!H12*COS(ATAN2($C$2,$B$2))-'L2'!I12*SIN(ATAN2($C$2,$B$2))</f>
+        <v>29.356247855049</v>
+      </c>
+      <c r="I12" s="1">
+        <f>('L2'!H12*SIN(ATAN2($C$2,$B$2))+'L2'!I12*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J12*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>27.3456277404456</v>
+      </c>
+      <c r="J12" s="1">
+        <f>('L2'!H12*SIN(ATAN2($C$2,$B$2))+'L2'!I12*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J12*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-25.3176016904031</v>
+      </c>
+      <c r="L12" s="1">
+        <f>'L2'!B12*COS(ATAN2($C$3,$B$3))-'L2'!C12*SIN(ATAN2($C$3,$B$3))</f>
+        <v>15.5530497724125</v>
+      </c>
+      <c r="M12" s="1">
+        <f>('L2'!B12*SIN(ATAN2($C$3,$B$3))+'L2'!C12*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D12*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.8976424367853</v>
+      </c>
+      <c r="O12" s="1">
+        <f>'L2'!B12*COS(ATAN2($C$4,$B$4))-'L2'!C12*SIN(ATAN2($C$4,$B$4))</f>
+        <v>15.8037708191086</v>
+      </c>
+      <c r="P12" s="1">
+        <f>('L2'!B12*SIN(ATAN2($C$4,$B$4))+'L2'!C12*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D12*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.8240289178094</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
+    <row r="13" spans="1:16">
+      <c r="G13" s="1">
         <v>245</v>
       </c>
-      <c r="B13" s="2">
-        <f>'L1'!E13-球心降噪!B13</f>
-        <v>38.569487444101</v>
-      </c>
-      <c r="C13" s="2">
-        <f>-('L1'!F13-球心降噪!C13)</f>
-        <v>-12.067595459236</v>
-      </c>
-      <c r="D13" s="2">
-        <f t="shared" si="0"/>
-        <v>24.845952952776</v>
-      </c>
-      <c r="E13" s="2">
-        <f t="shared" si="1"/>
-        <v>-36.4004380967454</v>
-      </c>
-      <c r="F13" s="2">
-        <f t="shared" si="2"/>
-        <v>-30.4230456457766</v>
+      <c r="H13" s="1">
+        <f>'L2'!H13*COS(ATAN2($C$2,$B$2))-'L2'!I13*SIN(ATAN2($C$2,$B$2))</f>
+        <v>26.7184438510991</v>
+      </c>
+      <c r="I13" s="1">
+        <f>('L2'!H13*SIN(ATAN2($C$2,$B$2))+'L2'!I13*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J13*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>27.6012647904757</v>
+      </c>
+      <c r="J13" s="1">
+        <f>('L2'!H13*SIN(ATAN2($C$2,$B$2))+'L2'!I13*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J13*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-27.8361013818693</v>
+      </c>
+      <c r="L13" s="1">
+        <f>'L2'!B13*COS(ATAN2($C$3,$B$3))-'L2'!C13*SIN(ATAN2($C$3,$B$3))</f>
+        <v>12.0354643410365</v>
+      </c>
+      <c r="M13" s="1">
+        <f>('L2'!B13*SIN(ATAN2($C$3,$B$3))+'L2'!C13*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D13*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.8204233095988</v>
+      </c>
+      <c r="O13" s="1">
+        <f>'L2'!B13*COS(ATAN2($C$4,$B$4))-'L2'!C13*SIN(ATAN2($C$4,$B$4))</f>
+        <v>12.2959782067344</v>
+      </c>
+      <c r="P13" s="1">
+        <f>('L2'!B13*SIN(ATAN2($C$4,$B$4))+'L2'!C13*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D13*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.7479084974178</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
+    <row r="14" spans="1:16">
+      <c r="G14" s="1">
         <v>265</v>
       </c>
-      <c r="B14" s="2">
-        <f>'L1'!E14-球心降噪!B14</f>
-        <v>39.8083935328521</v>
-      </c>
-      <c r="C14" s="2">
-        <f>-('L1'!F14-球心降噪!C14)</f>
-        <v>-9.12796697626402</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="0"/>
-        <v>24.1355675966781</v>
-      </c>
-      <c r="E14" s="2">
-        <f t="shared" si="1"/>
-        <v>-23.8071904135063</v>
-      </c>
-      <c r="F14" s="2">
-        <f t="shared" si="2"/>
-        <v>-41.0337822362874</v>
+      <c r="H14" s="1">
+        <f>'L2'!H14*COS(ATAN2($C$2,$B$2))-'L2'!I14*SIN(ATAN2($C$2,$B$2))</f>
+        <v>24.5373688185784</v>
+      </c>
+      <c r="I14" s="1">
+        <f>('L2'!H14*SIN(ATAN2($C$2,$B$2))+'L2'!I14*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J14*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>27.114147761045</v>
+      </c>
+      <c r="J14" s="1">
+        <f>('L2'!H14*SIN(ATAN2($C$2,$B$2))+'L2'!I14*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J14*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-30.2207564871113</v>
+      </c>
+      <c r="L14" s="1">
+        <f>'L2'!B14*COS(ATAN2($C$3,$B$3))-'L2'!C14*SIN(ATAN2($C$3,$B$3))</f>
+        <v>9.02973209398376</v>
+      </c>
+      <c r="M14" s="1">
+        <f>('L2'!B14*SIN(ATAN2($C$3,$B$3))+'L2'!C14*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D14*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>30.4389972634051</v>
+      </c>
+      <c r="O14" s="1">
+        <f>'L2'!B14*COS(ATAN2($C$4,$B$4))-'L2'!C14*SIN(ATAN2($C$4,$B$4))</f>
+        <v>9.2934057136997</v>
+      </c>
+      <c r="P14" s="1">
+        <f>('L2'!B14*SIN(ATAN2($C$4,$B$4))+'L2'!C14*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D14*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>30.368968485558</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
+    <row r="15" spans="1:16">
+      <c r="G15" s="1">
         <v>285</v>
       </c>
-      <c r="B15" s="2">
-        <f>'L1'!E15-球心降噪!B15</f>
-        <v>40.547299621603</v>
-      </c>
-      <c r="C15" s="2">
-        <f>-('L1'!F15-球心降噪!C15)</f>
-        <v>-5.68833849329201</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="0"/>
-        <v>23.9606531334538</v>
-      </c>
-      <c r="E15" s="2">
-        <f t="shared" si="1"/>
-        <v>-8.3453253409821</v>
-      </c>
-      <c r="F15" s="2">
-        <f t="shared" si="2"/>
-        <v>-46.7002049776354</v>
+      <c r="H15" s="1">
+        <f>'L2'!H15*COS(ATAN2($C$2,$B$2))-'L2'!I15*SIN(ATAN2($C$2,$B$2))</f>
+        <v>21.6960982408196</v>
+      </c>
+      <c r="I15" s="1">
+        <f>('L2'!H15*SIN(ATAN2($C$2,$B$2))+'L2'!I15*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J15*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>27.1361592332932</v>
+      </c>
+      <c r="J15" s="1">
+        <f>('L2'!H15*SIN(ATAN2($C$2,$B$2))+'L2'!I15*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J15*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-32.3026590730557</v>
+      </c>
+      <c r="L15" s="1">
+        <f>'L2'!B15*COS(ATAN2($C$3,$B$3))-'L2'!C15*SIN(ATAN2($C$3,$B$3))</f>
+        <v>5.01812625798092</v>
+      </c>
+      <c r="M15" s="1">
+        <f>('L2'!B15*SIN(ATAN2($C$3,$B$3))+'L2'!C15*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D15*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>30.1827343340946</v>
+      </c>
+      <c r="O15" s="1">
+        <f>'L2'!B15*COS(ATAN2($C$4,$B$4))-'L2'!C15*SIN(ATAN2($C$4,$B$4))</f>
+        <v>5.28823340644118</v>
+      </c>
+      <c r="P15" s="1">
+        <f>('L2'!B15*SIN(ATAN2($C$4,$B$4))+'L2'!C15*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D15*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>30.1151496313741</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
+    <row r="16" spans="1:16">
+      <c r="G16" s="1">
         <v>305</v>
       </c>
-      <c r="B16" s="2">
-        <f>'L1'!E16-球心降噪!B16</f>
-        <v>40.786205710354</v>
-      </c>
-      <c r="C16" s="2">
-        <f>-('L1'!F16-球心降噪!C16)</f>
-        <v>-1.74871001032</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="0"/>
-        <v>24.1656995978286</v>
-      </c>
-      <c r="E16" s="2">
-        <f t="shared" si="1"/>
-        <v>8.12209918549612</v>
-      </c>
-      <c r="F16" s="2">
-        <f t="shared" si="2"/>
-        <v>-46.7395454066571</v>
+      <c r="H16" s="1">
+        <f>'L2'!H16*COS(ATAN2($C$2,$B$2))-'L2'!I16*SIN(ATAN2($C$2,$B$2))</f>
+        <v>18.1946321178227</v>
+      </c>
+      <c r="I16" s="1">
+        <f>('L2'!H16*SIN(ATAN2($C$2,$B$2))+'L2'!I16*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J16*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>27.5124857914732</v>
+      </c>
+      <c r="J16" s="1">
+        <f>('L2'!H16*SIN(ATAN2($C$2,$B$2))+'L2'!I16*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J16*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-34.0965113709758</v>
+      </c>
+      <c r="L16" s="1">
+        <f>'L2'!B16*COS(ATAN2($C$3,$B$3))-'L2'!C16*SIN(ATAN2($C$3,$B$3))</f>
+        <v>1.01246468187686</v>
+      </c>
+      <c r="M16" s="1">
+        <f>('L2'!B16*SIN(ATAN2($C$3,$B$3))+'L2'!C16*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D16*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.9912856259764</v>
+      </c>
+      <c r="O16" s="1">
+        <f>'L2'!B16*COS(ATAN2($C$4,$B$4))-'L2'!C16*SIN(ATAN2($C$4,$B$4))</f>
+        <v>1.28567457400103</v>
+      </c>
+      <c r="P16" s="1">
+        <f>('L2'!B16*SIN(ATAN2($C$4,$B$4))+'L2'!C16*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D16*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.9270266115456</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
+    <row r="17" spans="2:16">
+      <c r="G17" s="1">
         <v>325</v>
       </c>
-      <c r="B17" s="2">
-        <f>'L1'!E17-球心降噪!B17</f>
-        <v>41.525111799106</v>
-      </c>
-      <c r="C17" s="2">
-        <f>-('L1'!F17-球心降噪!C17)</f>
-        <v>1.69091847265202</v>
-      </c>
-      <c r="D17" s="2">
-        <f t="shared" si="0"/>
-        <v>22.877051488131</v>
-      </c>
-      <c r="E17" s="2">
-        <f t="shared" si="1"/>
-        <v>23.6108616121494</v>
-      </c>
-      <c r="F17" s="2">
-        <f t="shared" si="2"/>
-        <v>-41.1470632479638</v>
+      <c r="H17" s="1">
+        <f>'L2'!H17*COS(ATAN2($C$2,$B$2))-'L2'!I17*SIN(ATAN2($C$2,$B$2))</f>
+        <v>15.3533615400643</v>
+      </c>
+      <c r="I17" s="1">
+        <f>('L2'!H17*SIN(ATAN2($C$2,$B$2))+'L2'!I17*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J17*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.4257521763015</v>
+      </c>
+      <c r="J17" s="1">
+        <f>('L2'!H17*SIN(ATAN2($C$2,$B$2))+'L2'!I17*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J17*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-36.2837086215946</v>
+      </c>
+      <c r="L17" s="1">
+        <f>'L2'!B17*COS(ATAN2($C$3,$B$3))-'L2'!C17*SIN(ATAN2($C$3,$B$3))</f>
+        <v>-2.49323222970154</v>
+      </c>
+      <c r="M17" s="1">
+        <f>('L2'!B17*SIN(ATAN2($C$3,$B$3))+'L2'!C17*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D17*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.1546775279477</v>
+      </c>
+      <c r="O17" s="1">
+        <f>'L2'!B17*COS(ATAN2($C$4,$B$4))-'L2'!C17*SIN(ATAN2($C$4,$B$4))</f>
+        <v>-2.21689108873639</v>
+      </c>
+      <c r="P17" s="1">
+        <f>('L2'!B17*SIN(ATAN2($C$4,$B$4))+'L2'!C17*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D17*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.0930381126321</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
+    <row r="18" spans="2:16">
+      <c r="G18" s="1">
         <v>345</v>
       </c>
-      <c r="B18" s="2">
-        <f>'L1'!E18-球心降噪!B18</f>
-        <v>41.264017887857</v>
-      </c>
-      <c r="C18" s="2">
-        <f>-('L1'!F18-球心降噪!C18)</f>
-        <v>5.13054695562403</v>
-      </c>
-      <c r="D18" s="2">
-        <f t="shared" si="0"/>
-        <v>22.8366353845472</v>
-      </c>
-      <c r="E18" s="2">
-        <f t="shared" si="1"/>
-        <v>36.254663040877</v>
-      </c>
-      <c r="F18" s="2">
-        <f t="shared" si="2"/>
-        <v>-30.5966175874469</v>
+      <c r="H18" s="1">
+        <f>'L2'!H18*COS(ATAN2($C$2,$B$2))-'L2'!I18*SIN(ATAN2($C$2,$B$2))</f>
+        <v>12.1051578146867</v>
+      </c>
+      <c r="I18" s="1">
+        <f>('L2'!H18*SIN(ATAN2($C$2,$B$2))+'L2'!I18*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J18*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.4952993837756</v>
+      </c>
+      <c r="J18" s="1">
+        <f>('L2'!H18*SIN(ATAN2($C$2,$B$2))+'L2'!I18*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J18*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-37.4435290116413</v>
+      </c>
+      <c r="L18" s="1">
+        <f>'L2'!B18*COS(ATAN2($C$3,$B$3))-'L2'!C18*SIN(ATAN2($C$3,$B$3))</f>
+        <v>-5.98704062148238</v>
+      </c>
+      <c r="M18" s="1">
+        <f>('L2'!B18*SIN(ATAN2($C$3,$B$3))+'L2'!C18*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D18*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.3903860480841</v>
+      </c>
+      <c r="O18" s="1">
+        <f>'L2'!B18*COS(ATAN2($C$4,$B$4))-'L2'!C18*SIN(ATAN2($C$4,$B$4))</f>
+        <v>-5.71422980183706</v>
+      </c>
+      <c r="P18" s="1">
+        <f>('L2'!B18*SIN(ATAN2($C$4,$B$4))+'L2'!C18*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D18*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.3333864221325</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
+    <row r="19" spans="2:16">
+      <c r="G19" s="1">
         <v>365</v>
       </c>
-      <c r="B19" s="2">
-        <f>'L1'!E19-球心降噪!B19</f>
-        <v>40.502923976608</v>
-      </c>
-      <c r="C19" s="2">
-        <f>-('L1'!F19-球心降噪!C19)</f>
-        <v>8.57017543859604</v>
-      </c>
-      <c r="D19" s="2">
-        <f t="shared" si="0"/>
-        <v>23.1650349081713</v>
-      </c>
-      <c r="E19" s="2">
-        <f t="shared" si="1"/>
-        <v>44.5300045616798</v>
-      </c>
-      <c r="F19" s="2">
-        <f t="shared" si="2"/>
-        <v>-16.3594710714245</v>
+      <c r="H19" s="1">
+        <f>'L2'!H19*COS(ATAN2($C$2,$B$2))-'L2'!I19*SIN(ATAN2($C$2,$B$2))</f>
+        <v>8.65348751549973</v>
+      </c>
+      <c r="I19" s="1">
+        <f>('L2'!H19*SIN(ATAN2($C$2,$B$2))+'L2'!I19*COS(ATAN2($C$2,$B$2)))*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))-'L2'!J19*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>26.8888301505863</v>
+      </c>
+      <c r="J19" s="1">
+        <f>('L2'!H19*SIN(ATAN2($C$2,$B$2))+'L2'!I19*COS(ATAN2($C$2,$B$2)))*SIN(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))+'L2'!J19*COS(ATAN2(SQRT($B$2^2+$C$2^2),-$D$2))</f>
+        <v>-38.1137975928929</v>
+      </c>
+      <c r="L19" s="1">
+        <f>'L2'!B19*COS(ATAN2($C$3,$B$3))-'L2'!C19*SIN(ATAN2($C$3,$B$3))</f>
+        <v>-9.48084901326322</v>
+      </c>
+      <c r="M19" s="1">
+        <f>('L2'!B19*SIN(ATAN2($C$3,$B$3))+'L2'!C19*COS(ATAN2($C$3,$B$3)))*COS(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))-'L2'!D19*SIN(ATAN2(SQRT($B$3^2+$C$3^2),-$D$3))</f>
+        <v>29.0913317657002</v>
+      </c>
+      <c r="O19" s="1">
+        <f>'L2'!B19*COS(ATAN2($C$4,$B$4))-'L2'!C19*SIN(ATAN2($C$4,$B$4))</f>
+        <v>-9.21156851493772</v>
+      </c>
+      <c r="P19" s="1">
+        <f>('L2'!B19*SIN(ATAN2($C$4,$B$4))+'L2'!C19*COS(ATAN2($C$4,$B$4)))*COS(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))-'L2'!D19*SIN(ATAN2(SQRT($B$4^2+$C$4^2),-$D$4))</f>
+        <v>29.0388261600757</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
+    <row r="20" spans="2:16">
+      <c r="G20" s="1">
         <v>385</v>
       </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>47.4397593327705</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="2"/>
-        <v>-0.151110717066466</v>
-      </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
-      </c>
+    <row r="21" spans="2:16">
+      <c r="G21" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/label.xlsx
+++ b/label.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="8"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="L0" sheetId="1" r:id="rId1"/>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="58">
   <si>
     <t>序号</t>
   </si>
@@ -499,13 +499,13 @@
     </r>
   </si>
   <si>
-    <t>X6去噪</t>
+    <t>X6(降噪)</t>
   </si>
   <si>
-    <t>Y6去噪</t>
+    <t>Y6(降噪)</t>
   </si>
   <si>
-    <t>Z6去噪</t>
+    <t>Z6(降噪)</t>
   </si>
   <si>
     <r>
@@ -843,15 +843,6 @@
   </si>
   <si>
     <t>D</t>
-  </si>
-  <si>
-    <t>X6(降噪)</t>
-  </si>
-  <si>
-    <t>Y6(降噪)</t>
-  </si>
-  <si>
-    <t>Z6(降噪)</t>
   </si>
   <si>
     <t>X6(未降噪)</t>
@@ -1524,7 +1515,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -12742,7 +12733,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6931660" y="200025"/>
+        <a:off x="7548880" y="200025"/>
         <a:ext cx="4588510" cy="4952365"/>
       </xdr:xfrm>
       <a:graphic>
@@ -14547,67 +14538,72 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="10" max="10" width="12.8888888888889"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="12.8888888888889" style="1"/>
+    <col min="6" max="6" width="14.1111111111111" style="1"/>
+    <col min="7" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="12.8888888888889" style="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>25</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="5">
         <f>'L1'!E2-'L1'!B2</f>
         <v>9.5</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <f>-('L1'!F2-'L1'!C2)</f>
         <v>-36</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <f>SQRT(47.44*47.44-B2*B2-C2*C2)</f>
         <v>29.3990408006792</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <f>COS(3.14/9*((A2-25)/20))*47.44</f>
         <v>47.44</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="5">
         <f>SIN(3.14/9*((A2-25)/20))*47.44</f>
         <v>0</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="5">
         <f>'L1'!E2-球心降噪!B2</f>
         <v>9.44152046783597</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <f>-('L1'!F2-球心降噪!C2)</f>
         <v>-36.90350877193</v>
       </c>
@@ -14617,34 +14613,34 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>45</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <f>'L1'!E3-'L1'!B3</f>
         <v>13.5</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <f>-('L1'!F3-'L1'!C3)</f>
         <v>-36</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <f t="shared" ref="D3:D19" si="0">SQRT(47.44*47.44-B3*B3-C3*C3)</f>
         <v>27.7903508434133</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <f t="shared" ref="E3:E20" si="1">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <f t="shared" ref="F3:F20" si="2">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <f>'L1'!E3-球心降噪!B3</f>
         <v>13.680426556588</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="5">
         <f>-('L1'!F3-球心降噪!C3)</f>
         <v>-36.463880288958</v>
       </c>
@@ -14654,34 +14650,34 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>65</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <f>'L1'!E4-'L1'!B4</f>
         <v>16</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <f>-('L1'!F4-'L1'!C4)</f>
         <v>-35.5</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <f t="shared" si="0"/>
         <v>27.0980368292613</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <f t="shared" si="1"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <f t="shared" si="2"/>
         <v>30.4809803249618</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <f>'L1'!E4-球心降噪!B4</f>
         <v>16.419332645339</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <f>-('L1'!F4-球心降噪!C4)</f>
         <v>-35.524251805986</v>
       </c>
@@ -14691,34 +14687,34 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>85</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <f>'L1'!E5-'L1'!B5</f>
         <v>20</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <f>-('L1'!F5-'L1'!C5)</f>
         <v>-34</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <f t="shared" si="0"/>
         <v>26.3543848344066</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <f t="shared" si="1"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <f t="shared" si="2"/>
         <v>41.0716467855168</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <f>'L1'!E5-球心降噪!B5</f>
         <v>19.65823873409</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <f>-('L1'!F5-球心降噪!C5)</f>
         <v>-34.0846233230139</v>
       </c>
@@ -14728,34 +14724,34 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>105</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <f>'L1'!E6-'L1'!B6</f>
         <v>23</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <f>-('L1'!F6-'L1'!C6)</f>
         <v>-32.5</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <f t="shared" si="0"/>
         <v>25.7934797962586</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <f t="shared" si="1"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <f t="shared" si="2"/>
         <v>46.7134369557949</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="5">
         <f>'L1'!E6-球心降噪!B6</f>
         <v>22.897144822841</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <f>-('L1'!F6-球心降噪!C6)</f>
         <v>-32.144994840041</v>
       </c>
@@ -14765,34 +14761,34 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>125</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <f>'L1'!E7-'L1'!B7</f>
         <v>26.5</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <f>-('L1'!F7-'L1'!C7)</f>
         <v>-30</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <f t="shared" si="0"/>
         <v>25.461806691592</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <f t="shared" si="1"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <f t="shared" si="2"/>
         <v>46.7265504432231</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="5">
         <f>'L1'!E7-球心降噪!B7</f>
         <v>26.136050911593</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="5">
         <f>-('L1'!F7-球心降噪!C7)</f>
         <v>-29.705366357069</v>
       </c>
@@ -14802,34 +14798,34 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>145</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <f>'L1'!E8-'L1'!B8</f>
         <v>28.5</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <f>-('L1'!F8-'L1'!C8)</f>
         <v>-28</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <f t="shared" si="0"/>
         <v>25.5793588660858</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <f t="shared" si="1"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <f t="shared" si="2"/>
         <v>41.1094071546692</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="5">
         <f>'L1'!E8-球心降噪!B8</f>
         <v>28.874957000344</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="5">
         <f>-('L1'!F8-球心降噪!C8)</f>
         <v>-27.765737874097</v>
       </c>
@@ -14839,34 +14835,34 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>165</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <f>'L1'!E9-'L1'!B9</f>
         <v>31.5</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <f>-('L1'!F9-'L1'!C9)</f>
         <v>-26</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <f t="shared" si="0"/>
         <v>24.1309676556909</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <f t="shared" si="1"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <f t="shared" si="2"/>
         <v>30.5388376877712</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="5">
         <f>'L1'!E9-球心降噪!B9</f>
         <v>31.613863089095</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="5">
         <f>-('L1'!F9-球心降噪!C9)</f>
         <v>-25.326109391125</v>
       </c>
@@ -14876,34 +14872,34 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>185</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <f>'L1'!E10-'L1'!B10</f>
         <v>34</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <f>-('L1'!F10-'L1'!C10)</f>
         <v>-22.5</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <f t="shared" si="0"/>
         <v>24.2549706245957</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <f t="shared" si="1"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <f t="shared" si="2"/>
         <v>16.2885294815216</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="5">
         <f>'L1'!E10-球心降噪!B10</f>
         <v>33.852769177847</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="5">
         <f>-('L1'!F10-球心降噪!C10)</f>
         <v>-22.386480908153</v>
       </c>
@@ -14913,34 +14909,34 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>205</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <f>'L1'!E11-'L1'!B11</f>
         <v>35.5</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <f>-('L1'!F11-'L1'!C11)</f>
         <v>-19</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <f t="shared" si="0"/>
         <v>25.0859243401554</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <f t="shared" si="1"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <f t="shared" si="2"/>
         <v>0.0755554543581351</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="5">
         <f>'L1'!E11-球心降噪!B11</f>
         <v>35.591675266598</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="5">
         <f>-('L1'!F11-球心降噪!C11)</f>
         <v>-18.946852425181</v>
       </c>
@@ -14950,34 +14946,34 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>225</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <f>'L1'!E12-'L1'!B12</f>
         <v>37.5</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <f>-('L1'!F12-'L1'!C12)</f>
         <v>-16</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <f t="shared" si="0"/>
         <v>24.2549706245957</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <f t="shared" si="1"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <f t="shared" si="2"/>
         <v>-16.1465225320068</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="5">
         <f>'L1'!E12-球心降噪!B12</f>
         <v>37.330581355349</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <f>-('L1'!F12-球心降噪!C12)</f>
         <v>-15.507223942209</v>
       </c>
@@ -14987,34 +14983,34 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>245</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <f>'L1'!E13-'L1'!B13</f>
         <v>39</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <f>-('L1'!F13-'L1'!C13)</f>
         <v>-12.5</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <f t="shared" si="0"/>
         <v>23.9437591033655</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <f t="shared" si="1"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <f t="shared" si="2"/>
         <v>-30.4230456457766</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="5">
         <f>'L1'!E13-球心降噪!B13</f>
         <v>38.569487444101</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="5">
         <f>-('L1'!F13-球心降噪!C13)</f>
         <v>-12.067595459236</v>
       </c>
@@ -15024,34 +15020,34 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>265</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <f>'L1'!E14-'L1'!B14</f>
         <v>39.5</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <f>-('L1'!F14-'L1'!C14)</f>
         <v>-9.5</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <f t="shared" si="0"/>
         <v>24.4959915088163</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <f t="shared" si="1"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <f t="shared" si="2"/>
         <v>-41.0337822362874</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <f>'L1'!E14-球心降噪!B14</f>
         <v>39.8083935328521</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="5">
         <f>-('L1'!F14-球心降噪!C14)</f>
         <v>-9.12796697626402</v>
       </c>
@@ -15061,34 +15057,34 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>285</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <f>'L1'!E15-'L1'!B15</f>
         <v>40.5</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <f>-('L1'!F15-'L1'!C15)</f>
         <v>-5.5</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <f t="shared" si="0"/>
         <v>24.0843019413061</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <f t="shared" si="1"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <f t="shared" si="2"/>
         <v>-46.7002049776354</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="5">
         <f>'L1'!E15-球心降噪!B15</f>
         <v>40.547299621603</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <f>-('L1'!F15-球心降噪!C15)</f>
         <v>-5.68833849329201</v>
       </c>
@@ -15098,34 +15094,34 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16">
+      <c r="A16" s="1">
         <v>305</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <f>'L1'!E16-'L1'!B16</f>
         <v>41</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <f>-('L1'!F16-'L1'!C16)</f>
         <v>-1.5</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <f t="shared" si="0"/>
         <v>23.8181359472147</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <f t="shared" si="1"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <f t="shared" si="2"/>
         <v>-46.7395454066571</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="5">
         <f>'L1'!E16-球心降噪!B16</f>
         <v>40.786205710354</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <f>-('L1'!F16-球心降噪!C16)</f>
         <v>-1.74871001032</v>
       </c>
@@ -15135,34 +15131,34 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17">
+      <c r="A17" s="1">
         <v>325</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <f>'L1'!E17-'L1'!B17</f>
         <v>41.5</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <f>-('L1'!F17-'L1'!C17)</f>
         <v>2</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <f t="shared" si="0"/>
         <v>22.8976767380448</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <f t="shared" si="1"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <f t="shared" si="2"/>
         <v>-41.1470632479638</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="5">
         <f>'L1'!E17-球心降噪!B17</f>
         <v>41.525111799106</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="5">
         <f>-('L1'!F17-球心降噪!C17)</f>
         <v>1.69091847265202</v>
       </c>
@@ -15172,34 +15168,34 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18">
+      <c r="A18" s="1">
         <v>345</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <f>'L1'!E18-'L1'!B18</f>
         <v>41</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <f>-('L1'!F18-'L1'!C18)</f>
         <v>5.5</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="5">
         <f t="shared" si="0"/>
         <v>23.2229111008934</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <f t="shared" si="1"/>
         <v>36.254663040877</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="5">
         <f t="shared" si="2"/>
         <v>-30.5966175874469</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="5">
         <f>'L1'!E18-球心降噪!B18</f>
         <v>41.264017887857</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="5">
         <f>-('L1'!F18-球心降噪!C18)</f>
         <v>5.13054695562403</v>
       </c>
@@ -15209,34 +15205,34 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19">
+      <c r="A19" s="1">
         <v>365</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <f>'L1'!E19-'L1'!B19</f>
         <v>40.5</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <f>-('L1'!F19-'L1'!C19)</f>
         <v>9</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <f t="shared" si="0"/>
         <v>23.0065990533151</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <f t="shared" si="1"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="5">
         <f t="shared" si="2"/>
         <v>-16.3594710714245</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="5">
         <f>'L1'!E19-球心降噪!B19</f>
         <v>40.502923976608</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="5">
         <f>-('L1'!F19-球心降噪!C19)</f>
         <v>8.57017543859604</v>
       </c>
@@ -15246,20 +15242,20 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20">
+      <c r="A20" s="1">
         <v>385</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <f t="shared" si="1"/>
         <v>47.4397593327705</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <f t="shared" si="2"/>
         <v>-0.151110717066466</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -19108,31 +19104,31 @@
         <v>0</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3">
         <v>0.0863602</v>
@@ -19181,7 +19177,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B3" s="3">
         <v>0.157773</v>

--- a/label.xlsx
+++ b/label.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="8"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="L0" sheetId="1" r:id="rId1"/>
@@ -1082,7 +1082,7 @@
     <t>球心未降噪</t>
   </si>
   <si>
-    <t>弧度与角速度(角速度=弧度*180/PI)</t>
+    <t>弧度与角速度(角度=弧度*180/PI)</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1740,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1754,9 +1754,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -16855,31 +16852,31 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
     </row>
@@ -17419,22 +17416,22 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -17442,23 +17439,23 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <f>(L0!B2+L0!D2)/2</f>
         <v>884.5</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <f>(L0!C2+L0!E2)/2</f>
         <v>518</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <f>(L0!D2-L0!B2+L0!E2-L0!C2)/4</f>
         <v>48.75</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>(L0!F2+L0!H2)/2</f>
         <v>894</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <f>(L0!G2+L0!I2)/2</f>
         <v>554</v>
       </c>
@@ -17467,23 +17464,23 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <f>(L0!B3+L0!D3)/2</f>
         <v>881</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <f>(L0!C3+L0!E3)/2</f>
         <v>520</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <f>(L0!D3-L0!B3+L0!E3-L0!C3)/4</f>
         <v>48</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <f>(L0!F3+L0!H3)/2</f>
         <v>894.5</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <f>(L0!G3+L0!I3)/2</f>
         <v>556</v>
       </c>
@@ -17492,23 +17489,23 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <f>(L0!B4+L0!D4)/2</f>
         <v>877.5</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <f>(L0!C4+L0!E4)/2</f>
         <v>522</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <f>(L0!D4-L0!B4+L0!E4-L0!C4)/4</f>
         <v>48.25</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <f>(L0!F4+L0!H4)/2</f>
         <v>893.5</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <f>(L0!G4+L0!I4)/2</f>
         <v>557.5</v>
       </c>
@@ -17517,23 +17514,23 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <f>(L0!B5+L0!D5)/2</f>
         <v>873</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f>(L0!C5+L0!E5)/2</f>
         <v>524.5</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f>(L0!D5-L0!B5+L0!E5-L0!C5)/4</f>
         <v>47.75</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <f>(L0!F5+L0!H5)/2</f>
         <v>893</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <f>(L0!G5+L0!I5)/2</f>
         <v>558.5</v>
       </c>
@@ -17542,23 +17539,23 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <f>(L0!B6+L0!D6)/2</f>
         <v>869.5</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f>(L0!C6+L0!E6)/2</f>
         <v>526.5</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f>(L0!D6-L0!B6+L0!E6-L0!C6)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <f>(L0!F6+L0!H6)/2</f>
         <v>892.5</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <f>(L0!G6+L0!I6)/2</f>
         <v>559</v>
       </c>
@@ -17567,23 +17564,23 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <f>(L0!B7+L0!D7)/2</f>
         <v>865.5</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f>(L0!C7+L0!E7)/2</f>
         <v>529</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>(L0!D7-L0!B7+L0!E7-L0!C7)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <f>(L0!F7+L0!H7)/2</f>
         <v>892</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <f>(L0!G7+L0!I7)/2</f>
         <v>559</v>
       </c>
@@ -17592,23 +17589,23 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <f>(L0!B8+L0!D8)/2</f>
         <v>862.5</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f>(L0!C8+L0!E8)/2</f>
         <v>531.5</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f>(L0!D8-L0!B8+L0!E8-L0!C8)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <f>(L0!F8+L0!H8)/2</f>
         <v>891</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <f>(L0!G8+L0!I8)/2</f>
         <v>559.5</v>
       </c>
@@ -17617,23 +17614,23 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <f>(L0!B9+L0!D9)/2</f>
         <v>858.5</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f>(L0!C9+L0!E9)/2</f>
         <v>533.5</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f>(L0!D9-L0!B9+L0!E9-L0!C9)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <f>(L0!F9+L0!H9)/2</f>
         <v>890</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <f>(L0!G9+L0!I9)/2</f>
         <v>559.5</v>
       </c>
@@ -17642,23 +17639,23 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <f>(L0!B10+L0!D10)/2</f>
         <v>854.5</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f>(L0!C10+L0!E10)/2</f>
         <v>536.5</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f>(L0!D10-L0!B10+L0!E10-L0!C10)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <f>(L0!F10+L0!H10)/2</f>
         <v>888.5</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <f>(L0!G10+L0!I10)/2</f>
         <v>559</v>
       </c>
@@ -17667,23 +17664,23 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <f>(L0!B11+L0!D11)/2</f>
         <v>851</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <f>(L0!C11+L0!E11)/2</f>
         <v>539</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <f>(L0!D11-L0!B11+L0!E11-L0!C11)/4</f>
         <v>47.5</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <f>(L0!F11+L0!H11)/2</f>
         <v>886.5</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <f>(L0!G11+L0!I11)/2</f>
         <v>558</v>
       </c>
@@ -17692,23 +17689,23 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <f>(L0!B12+L0!D12)/2</f>
         <v>847</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f>(L0!C12+L0!E12)/2</f>
         <v>541</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <f>(L0!D12-L0!B12+L0!E12-L0!C12)/4</f>
         <v>47</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <f>(L0!F12+L0!H12)/2</f>
         <v>884.5</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <f>(L0!G12+L0!I12)/2</f>
         <v>557</v>
       </c>
@@ -17717,23 +17714,23 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <f>(L0!B13+L0!D13)/2</f>
         <v>843</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f>(L0!C13+L0!E13)/2</f>
         <v>543.5</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <f>(L0!D13-L0!B13+L0!E13-L0!C13)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <f>(L0!F13+L0!H13)/2</f>
         <v>882</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <f>(L0!G13+L0!I13)/2</f>
         <v>556</v>
       </c>
@@ -17742,23 +17739,23 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <f>(L0!B14+L0!D14)/2</f>
         <v>840</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f>(L0!C14+L0!E14)/2</f>
         <v>546</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <f>(L0!D14-L0!B14+L0!E14-L0!C14)/4</f>
         <v>47</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <f>(L0!F14+L0!H14)/2</f>
         <v>879.5</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <f>(L0!G14+L0!I14)/2</f>
         <v>555.5</v>
       </c>
@@ -17767,23 +17764,23 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <f>(L0!B15+L0!D15)/2</f>
         <v>836</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <f>(L0!C15+L0!E15)/2</f>
         <v>549</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <f>(L0!D15-L0!B15+L0!E15-L0!C15)/4</f>
         <v>47</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <f>(L0!F15+L0!H15)/2</f>
         <v>876.5</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <f>(L0!G15+L0!I15)/2</f>
         <v>554.5</v>
       </c>
@@ -17792,23 +17789,23 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <f>(L0!B16+L0!D16)/2</f>
         <v>832</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f>(L0!C16+L0!E16)/2</f>
         <v>551.5</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <f>(L0!D16-L0!B16+L0!E16-L0!C16)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <f>(L0!F16+L0!H16)/2</f>
         <v>873</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <f>(L0!G16+L0!I16)/2</f>
         <v>553</v>
       </c>
@@ -17817,23 +17814,23 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <f>(L0!B17+L0!D17)/2</f>
         <v>828.5</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f>(L0!C17+L0!E17)/2</f>
         <v>554</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <f>(L0!D17-L0!B17+L0!E17-L0!C17)/4</f>
         <v>46.75</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <f>(L0!F17+L0!H17)/2</f>
         <v>870</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <f>(L0!G17+L0!I17)/2</f>
         <v>552</v>
       </c>
@@ -17842,23 +17839,23 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <f>(L0!B18+L0!D18)/2</f>
         <v>825</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f>(L0!C18+L0!E18)/2</f>
         <v>556.5</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <f>(L0!D18-L0!B18+L0!E18-L0!C18)/4</f>
         <v>47.25</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <f>(L0!F18+L0!H18)/2</f>
         <v>866</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <f>(L0!G18+L0!I18)/2</f>
         <v>551</v>
       </c>
@@ -17867,29 +17864,29 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <f>(L0!B19+L0!D19)/2</f>
         <v>821</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f>(L0!C19+L0!E19)/2</f>
         <v>559</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <f>(L0!D19-L0!B19+L0!E19-L0!C19)/4</f>
         <v>47</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <f>(L0!F19+L0!H19)/2</f>
         <v>861.5</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <f>(L0!G19+L0!I19)/2</f>
         <v>550</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <f>AVERAGE(D2:D19)</f>
         <v>47.4444444444444</v>
       </c>
@@ -17949,35 +17946,35 @@
       <c r="A2" s="1">
         <v>25</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <f>'L1'!E2-'L1'!B2</f>
         <v>9.5</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <f>-('L1'!F2-'L1'!C2)</f>
         <v>-36</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <f>SQRT(47.44*47.44-B2*B2-C2*C2)</f>
         <v>29.3990408006792</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <f>COS(3.14/9*((A2-25)/20))*47.44</f>
         <v>47.44</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <f>SIN(3.14/9*((A2-25)/20))*47.44</f>
         <v>0</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="7">
         <f>'L1'!E2-球心降噪!B2</f>
         <v>9.44152046783597</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="7">
         <f>-('L1'!F2-球心降噪!C2)</f>
         <v>-36.90350877193</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="10">
         <f>SQRT(47.44*47.44-H2*H2-I2*I2)</f>
         <v>28.2761795788526</v>
       </c>
@@ -17986,35 +17983,35 @@
       <c r="A3" s="1">
         <v>45</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <f>'L1'!E3-'L1'!B3</f>
         <v>13.5</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <f>-('L1'!F3-'L1'!C3)</f>
         <v>-36</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <f t="shared" ref="D3:D19" si="0">SQRT(47.44*47.44-B3*B3-C3*C3)</f>
         <v>27.7903508434133</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <f t="shared" ref="E3:E20" si="1">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <f t="shared" ref="F3:F20" si="2">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <f>'L1'!E3-球心降噪!B3</f>
         <v>13.680426556588</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="7">
         <f>-('L1'!F3-球心降噪!C3)</f>
         <v>-36.463880288958</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="10">
         <f t="shared" ref="J3:J19" si="3">SQRT(47.44*47.44-H3*H3-I3*I3)</f>
         <v>27.0884655066016</v>
       </c>
@@ -18023,35 +18020,35 @@
       <c r="A4" s="1">
         <v>65</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <f>'L1'!E4-'L1'!B4</f>
         <v>16</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <f>-('L1'!F4-'L1'!C4)</f>
         <v>-35.5</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <f t="shared" si="0"/>
         <v>27.0980368292613</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <f t="shared" si="1"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <f t="shared" si="2"/>
         <v>30.4809803249618</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <f>'L1'!E4-球心降噪!B4</f>
         <v>16.419332645339</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <f>-('L1'!F4-球心降噪!C4)</f>
         <v>-35.524251805986</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="10">
         <f t="shared" si="3"/>
         <v>26.8139264022748</v>
       </c>
@@ -18060,35 +18057,35 @@
       <c r="A5" s="1">
         <v>85</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <f>'L1'!E5-'L1'!B5</f>
         <v>20</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <f>-('L1'!F5-'L1'!C5)</f>
         <v>-34</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <f t="shared" si="0"/>
         <v>26.3543848344066</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <f t="shared" si="1"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <f t="shared" si="2"/>
         <v>41.0716467855168</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <f>'L1'!E5-球心降噪!B5</f>
         <v>19.65823873409</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <f>-('L1'!F5-球心降噪!C5)</f>
         <v>-34.0846233230139</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <f t="shared" si="3"/>
         <v>26.5018056517245</v>
       </c>
@@ -18097,35 +18094,35 @@
       <c r="A6" s="1">
         <v>105</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <f>'L1'!E6-'L1'!B6</f>
         <v>23</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f>-('L1'!F6-'L1'!C6)</f>
         <v>-32.5</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f t="shared" si="0"/>
         <v>25.7934797962586</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f t="shared" si="1"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <f t="shared" si="2"/>
         <v>46.7134369557949</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <f>'L1'!E6-球心降噪!B6</f>
         <v>22.897144822841</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <f>-('L1'!F6-球心降噪!C6)</f>
         <v>-32.144994840041</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10">
         <f t="shared" si="3"/>
         <v>26.3243929786725</v>
       </c>
@@ -18134,35 +18131,35 @@
       <c r="A7" s="1">
         <v>125</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <f>'L1'!E7-'L1'!B7</f>
         <v>26.5</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <f>-('L1'!F7-'L1'!C7)</f>
         <v>-30</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <f t="shared" si="0"/>
         <v>25.461806691592</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <f t="shared" si="1"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <f t="shared" si="2"/>
         <v>46.7265504432231</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <f>'L1'!E7-球心降噪!B7</f>
         <v>26.136050911593</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="7">
         <f>-('L1'!F7-球心降噪!C7)</f>
         <v>-29.705366357069</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <f t="shared" si="3"/>
         <v>26.1734914052163</v>
       </c>
@@ -18171,35 +18168,35 @@
       <c r="A8" s="1">
         <v>145</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <f>'L1'!E8-'L1'!B8</f>
         <v>28.5</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <f>-('L1'!F8-'L1'!C8)</f>
         <v>-28</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <f t="shared" si="0"/>
         <v>25.5793588660858</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <f t="shared" si="1"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <f t="shared" si="2"/>
         <v>41.1094071546692</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <f>'L1'!E8-球心降噪!B8</f>
         <v>28.874957000344</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <f>-('L1'!F8-球心降噪!C8)</f>
         <v>-27.765737874097</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10">
         <f t="shared" si="3"/>
         <v>25.4136628319339</v>
       </c>
@@ -18208,35 +18205,35 @@
       <c r="A9" s="1">
         <v>165</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <f>'L1'!E9-'L1'!B9</f>
         <v>31.5</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <f>-('L1'!F9-'L1'!C9)</f>
         <v>-26</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <f t="shared" si="0"/>
         <v>24.1309676556909</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <f t="shared" si="1"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <f t="shared" si="2"/>
         <v>30.5388376877712</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <f>'L1'!E9-球心降噪!B9</f>
         <v>31.613863089095</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="7">
         <f>-('L1'!F9-球心降噪!C9)</f>
         <v>-25.326109391125</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <f t="shared" si="3"/>
         <v>24.6922142322782</v>
       </c>
@@ -18245,35 +18242,35 @@
       <c r="A10" s="1">
         <v>185</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <f>'L1'!E10-'L1'!B10</f>
         <v>34</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <f>-('L1'!F10-'L1'!C10)</f>
         <v>-22.5</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <f t="shared" si="0"/>
         <v>24.2549706245957</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <f t="shared" si="1"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <f t="shared" si="2"/>
         <v>16.2885294815216</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <f>'L1'!E10-球心降噪!B10</f>
         <v>33.852769177847</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="7">
         <f>-('L1'!F10-球心降噪!C10)</f>
         <v>-22.386480908153</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="10">
         <f t="shared" si="3"/>
         <v>24.5639795542236</v>
       </c>
@@ -18282,35 +18279,35 @@
       <c r="A11" s="1">
         <v>205</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <f>'L1'!E11-'L1'!B11</f>
         <v>35.5</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <f>-('L1'!F11-'L1'!C11)</f>
         <v>-19</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <f t="shared" si="0"/>
         <v>25.0859243401554</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f t="shared" si="1"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <f t="shared" si="2"/>
         <v>0.0755554543581351</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <f>'L1'!E11-球心降噪!B11</f>
         <v>35.591675266598</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <f>-('L1'!F11-球心降噪!C11)</f>
         <v>-18.946852425181</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10">
         <f t="shared" si="3"/>
         <v>24.996060387498</v>
       </c>
@@ -18319,35 +18316,35 @@
       <c r="A12" s="1">
         <v>225</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <f>'L1'!E12-'L1'!B12</f>
         <v>37.5</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <f>-('L1'!F12-'L1'!C12)</f>
         <v>-16</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <f t="shared" si="0"/>
         <v>24.2549706245957</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <f t="shared" si="1"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <f t="shared" si="2"/>
         <v>-16.1465225320068</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <f>'L1'!E12-球心降噪!B12</f>
         <v>37.330581355349</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <f>-('L1'!F12-球心降噪!C12)</f>
         <v>-15.507223942209</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <f t="shared" si="3"/>
         <v>24.8295650642103</v>
       </c>
@@ -18356,35 +18353,35 @@
       <c r="A13" s="1">
         <v>245</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <f>'L1'!E13-'L1'!B13</f>
         <v>39</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <f>-('L1'!F13-'L1'!C13)</f>
         <v>-12.5</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <f t="shared" si="0"/>
         <v>23.9437591033655</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <f t="shared" si="1"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <f t="shared" si="2"/>
         <v>-30.4230456457766</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="7">
         <f>'L1'!E13-球心降噪!B13</f>
         <v>38.569487444101</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <f>-('L1'!F13-球心降噪!C13)</f>
         <v>-12.067595459236</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <f t="shared" si="3"/>
         <v>24.845952952776</v>
       </c>
@@ -18393,35 +18390,35 @@
       <c r="A14" s="1">
         <v>265</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <f>'L1'!E14-'L1'!B14</f>
         <v>39.5</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <f>-('L1'!F14-'L1'!C14)</f>
         <v>-9.5</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <f t="shared" si="0"/>
         <v>24.4959915088163</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <f t="shared" si="1"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <f t="shared" si="2"/>
         <v>-41.0337822362874</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="7">
         <f>'L1'!E14-球心降噪!B14</f>
         <v>39.8083935328521</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <f>-('L1'!F14-球心降噪!C14)</f>
         <v>-9.12796697626402</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <f t="shared" si="3"/>
         <v>24.1355675966781</v>
       </c>
@@ -18430,35 +18427,35 @@
       <c r="A15" s="1">
         <v>285</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <f>'L1'!E15-'L1'!B15</f>
         <v>40.5</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <f>-('L1'!F15-'L1'!C15)</f>
         <v>-5.5</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <f t="shared" si="0"/>
         <v>24.0843019413061</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <f t="shared" si="1"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <f t="shared" si="2"/>
         <v>-46.7002049776354</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="7">
         <f>'L1'!E15-球心降噪!B15</f>
         <v>40.547299621603</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="7">
         <f>-('L1'!F15-球心降噪!C15)</f>
         <v>-5.68833849329201</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="10">
         <f t="shared" si="3"/>
         <v>23.9606531334538</v>
       </c>
@@ -18467,35 +18464,35 @@
       <c r="A16" s="1">
         <v>305</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <f>'L1'!E16-'L1'!B16</f>
         <v>41</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <f>-('L1'!F16-'L1'!C16)</f>
         <v>-1.5</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <f t="shared" si="0"/>
         <v>23.8181359472147</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <f t="shared" si="1"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="7">
         <f t="shared" si="2"/>
         <v>-46.7395454066571</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <f>'L1'!E16-球心降噪!B16</f>
         <v>40.786205710354</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="7">
         <f>-('L1'!F16-球心降噪!C16)</f>
         <v>-1.74871001032</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="10">
         <f t="shared" si="3"/>
         <v>24.1656995978286</v>
       </c>
@@ -18504,35 +18501,35 @@
       <c r="A17" s="1">
         <v>325</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <f>'L1'!E17-'L1'!B17</f>
         <v>41.5</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <f>-('L1'!F17-'L1'!C17)</f>
         <v>2</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <f t="shared" si="0"/>
         <v>22.8976767380448</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <f t="shared" si="1"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="7">
         <f t="shared" si="2"/>
         <v>-41.1470632479638</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <f>'L1'!E17-球心降噪!B17</f>
         <v>41.525111799106</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="7">
         <f>-('L1'!F17-球心降噪!C17)</f>
         <v>1.69091847265202</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10">
         <f t="shared" si="3"/>
         <v>22.877051488131</v>
       </c>
@@ -18541,35 +18538,35 @@
       <c r="A18" s="1">
         <v>345</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <f>'L1'!E18-'L1'!B18</f>
         <v>41</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <f>-('L1'!F18-'L1'!C18)</f>
         <v>5.5</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <f t="shared" si="0"/>
         <v>23.2229111008934</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <f t="shared" si="1"/>
         <v>36.254663040877</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="7">
         <f t="shared" si="2"/>
         <v>-30.5966175874469</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <f>'L1'!E18-球心降噪!B18</f>
         <v>41.264017887857</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="7">
         <f>-('L1'!F18-球心降噪!C18)</f>
         <v>5.13054695562403</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="10">
         <f t="shared" si="3"/>
         <v>22.8366353845472</v>
       </c>
@@ -18578,35 +18575,35 @@
       <c r="A19" s="1">
         <v>365</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <f>'L1'!E19-'L1'!B19</f>
         <v>40.5</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <f>-('L1'!F19-'L1'!C19)</f>
         <v>9</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <f t="shared" si="0"/>
         <v>23.0065990533151</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <f t="shared" si="1"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="7">
         <f t="shared" si="2"/>
         <v>-16.3594710714245</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <f>'L1'!E19-球心降噪!B19</f>
         <v>40.502923976608</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="7">
         <f>-('L1'!F19-球心降噪!C19)</f>
         <v>8.57017543859604</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="10">
         <f t="shared" si="3"/>
         <v>23.1650349081713</v>
       </c>
@@ -18649,34 +18646,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -18684,38 +18681,38 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <f>COS(A2*3.1416/9)*47.44</f>
         <v>47.44</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <f>SIN(A2*3.1416/9)*47.44</f>
         <v>0</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <f>COS(A2*3.1416/18+3.1416/30)*47.44</f>
         <v>47.1801175019494</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>SIN(A2*3.1416/18+3.1416/30)*47.44</f>
         <v>4.95884185090085</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <f>D2*COS(-3.1416/30)-E2*SIN(-3.1416/30)</f>
         <v>47.44</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <f>(D2*SIN(-3.1416/30)+E2*COS(-3.1416/30))*0.8</f>
         <v>0</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <f>G2*COS(3.1416/30)-H2*SIN(3.1416/30)</f>
         <v>47.1801175019494</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="9">
         <f>G2*SIN(3.1416/30)+H2*COS(3.1416/30)</f>
         <v>4.95884185090085</v>
       </c>
@@ -18724,35 +18721,35 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <f t="shared" ref="B3:B20" si="0">COS(A3*3.1416/9)*47.44</f>
         <v>44.579004685768</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <f t="shared" ref="C3:C20" si="1">SIN(A3*3.1416/9)*47.44</f>
         <v>16.2254719877812</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <f t="shared" ref="D3:D20" si="2">COS(A3*3.1416/18+3.1416/30)*47.44</f>
         <v>45.6022463163357</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <f t="shared" ref="E3:E20" si="3">SIN(A3*3.1416/18+3.1416/30)*47.44</f>
         <v>13.0762659388775</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <f t="shared" ref="G3:G20" si="4">D3*COS(-3.1416/30)-E3*SIN(-3.1416/30)</f>
         <v>46.7192764407414</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <f t="shared" ref="H3:H20" si="5">(D3*SIN(-3.1416/30)+E3*COS(-3.1416/30))*0.8</f>
         <v>6.5903108929923</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <f t="shared" ref="I3:I20" si="6">G3*COS(3.1416/30)-H3*SIN(3.1416/30)</f>
         <v>45.77446548511</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <f t="shared" ref="J3:J20" si="7">G3*SIN(3.1416/30)+H3*COS(3.1416/30)</f>
         <v>11.4377138609593</v>
       </c>
@@ -18761,35 +18758,35 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <f t="shared" si="0"/>
         <v>36.3410985992296</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <f t="shared" si="1"/>
         <v>30.4939035317073</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <f t="shared" si="2"/>
         <v>42.6387674884245</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <f t="shared" si="3"/>
         <v>20.7963724497344</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <f t="shared" si="4"/>
         <v>44.579004685768</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <f t="shared" si="5"/>
         <v>12.980377590225</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <f t="shared" si="6"/>
         <v>42.9779730092661</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <f t="shared" si="7"/>
         <v>17.5690551018925</v>
       </c>
@@ -18798,35 +18795,35 @@
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <f t="shared" si="0"/>
         <v>23.7198993926896</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f t="shared" si="1"/>
         <v>41.0843032410273</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f t="shared" si="2"/>
         <v>38.3797252428634</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <f t="shared" si="3"/>
         <v>27.8845887594261</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <f t="shared" si="4"/>
         <v>41.0842161126946</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <f t="shared" si="5"/>
         <v>18.9760402428815</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="9">
         <f t="shared" si="6"/>
         <v>38.8756104795876</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <f t="shared" si="7"/>
         <v>23.1665670036247</v>
       </c>
@@ -18835,35 +18832,35 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <f t="shared" si="0"/>
         <v>8.23771700670016</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f t="shared" si="1"/>
         <v>46.7193066998808</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f t="shared" si="2"/>
         <v>32.9545290267963</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <f t="shared" si="3"/>
         <v>34.1255419974839</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <f t="shared" si="4"/>
         <v>36.3410985992296</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <f t="shared" si="5"/>
         <v>24.3951228253659</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <f t="shared" si="6"/>
         <v>33.5920266871267</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <f t="shared" si="7"/>
         <v>28.0601712060882</v>
       </c>
@@ -18872,35 +18869,35 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <f t="shared" si="0"/>
         <v>-8.23806022566945</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f t="shared" si="1"/>
         <v>46.7192461809717</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f t="shared" si="2"/>
         <v>26.5280214509534</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <f t="shared" si="3"/>
         <v>39.3296030732291</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <f t="shared" si="4"/>
         <v>30.4937700431928</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <f t="shared" si="5"/>
         <v>29.0729684874772</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <f t="shared" si="6"/>
         <v>27.287761400709</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <f t="shared" si="7"/>
         <v>32.1011773282373</v>
       </c>
@@ -18909,35 +18906,35 @@
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <f t="shared" si="0"/>
         <v>-23.7202012141941</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f t="shared" si="1"/>
         <v>41.0841289838076</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f t="shared" si="2"/>
         <v>19.2954696069731</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <f t="shared" si="3"/>
         <v>43.338648486615</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <f t="shared" si="4"/>
         <v>23.7198993926896</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f t="shared" si="5"/>
         <v>32.8674425928218</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <f t="shared" si="6"/>
         <v>20.1543674245393</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <f t="shared" si="7"/>
         <v>35.1668008711117</v>
       </c>
@@ -18946,35 +18943,35 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <f t="shared" si="0"/>
         <v>-36.3413226189731</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f t="shared" si="1"/>
         <v>30.4936365542668</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f t="shared" si="2"/>
         <v>11.4766319479547</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <f t="shared" si="3"/>
         <v>46.0308648531742</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <f t="shared" si="4"/>
         <v>16.2253082398443</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f t="shared" si="5"/>
         <v>35.663251427963</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <f t="shared" si="6"/>
         <v>12.4085903360248</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <f t="shared" si="7"/>
         <v>37.1638939801089</v>
       </c>
@@ -18983,35 +18980,35 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <f t="shared" si="0"/>
         <v>-44.5791238835381</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f t="shared" si="1"/>
         <v>16.2251444916884</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f t="shared" si="2"/>
         <v>3.30908100791483</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <f t="shared" si="3"/>
         <v>47.3244501593316</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <f t="shared" si="4"/>
         <v>8.23771700670016</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <f t="shared" si="5"/>
         <v>37.3754453599046</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <f t="shared" si="6"/>
         <v>4.28578275036188</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <f t="shared" si="7"/>
         <v>38.0317757086149</v>
       </c>
@@ -19020,35 +19017,35 @@
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>-47.4399999987198</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <f t="shared" si="1"/>
         <v>-0.000348513700203172</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <f t="shared" si="2"/>
         <v>-4.95901515311578</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <f t="shared" si="3"/>
         <v>47.1800992867879</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <f t="shared" si="4"/>
         <v>-0.000174256850099752</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <f t="shared" si="5"/>
         <v>37.951999999744</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="9">
         <f t="shared" si="6"/>
         <v>-3.9672467829423</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="9">
         <f t="shared" si="7"/>
         <v>37.7440757864617</v>
       </c>
@@ -19057,35 +19054,35 @@
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <f t="shared" si="0"/>
         <v>-44.578885485592</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f t="shared" si="1"/>
         <v>-16.2257994829984</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <f t="shared" si="2"/>
         <v>-13.0764334451932</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <f t="shared" si="3"/>
         <v>45.6021982842213</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <f t="shared" si="4"/>
         <v>-8.23806022566945</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <f t="shared" si="5"/>
         <v>37.3753969447774</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <f t="shared" si="6"/>
         <v>-12.0997329679388</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="9">
         <f t="shared" si="7"/>
         <v>36.3095358709803</v>
       </c>
@@ -19094,35 +19091,35 @@
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>-36.3408745775248</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f t="shared" si="1"/>
         <v>-30.4941705075021</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <f t="shared" si="2"/>
         <v>-20.7965290705324</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <f t="shared" si="3"/>
         <v>42.6386910987955</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <f t="shared" si="4"/>
         <v>-16.2256357354993</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <f t="shared" si="5"/>
         <v>35.6631560687846</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <f t="shared" si="6"/>
         <v>-19.8645731744052</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="9">
         <f t="shared" si="7"/>
         <v>33.7717439349273</v>
       </c>
@@ -19131,35 +19128,35 @@
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <f t="shared" si="0"/>
         <v>-23.7195975699048</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f t="shared" si="1"/>
         <v>-41.0844774960296</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <f t="shared" si="2"/>
         <v>-27.8847297358406</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <f t="shared" si="3"/>
         <v>38.3796228167908</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <f t="shared" si="4"/>
         <v>-23.7202012141941</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <f t="shared" si="5"/>
         <v>32.8673031870461</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <f t="shared" si="6"/>
         <v>-27.0258355612507</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="9">
         <f t="shared" si="7"/>
         <v>30.2078098618107</v>
       </c>
@@ -19168,35 +19165,35 @@
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <f t="shared" si="0"/>
         <v>-8.23737378728626</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <f t="shared" si="1"/>
         <v>-46.7193672162683</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <f t="shared" si="2"/>
         <v>-34.1256630459979</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <f t="shared" si="3"/>
         <v>32.954403676459</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <f t="shared" si="4"/>
         <v>-30.4940370198104</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="9">
         <f t="shared" si="5"/>
         <v>29.0727892708979</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <f t="shared" si="6"/>
         <v>-33.3659277795616</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="9">
         <f t="shared" si="7"/>
         <v>25.7260224901691</v>
       </c>
@@ -19205,35 +19202,35 @@
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <f t="shared" si="0"/>
         <v>8.23840344419414</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f t="shared" si="1"/>
         <v>-46.7191856595413</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <f t="shared" si="2"/>
         <v>-39.3297005158276</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <f t="shared" si="3"/>
         <v>26.5278769850757</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <f t="shared" si="4"/>
         <v>-36.3413226189731</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="9">
         <f t="shared" si="5"/>
         <v>24.3949092434134</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="9">
         <f t="shared" si="6"/>
         <v>-38.6922084368585</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="9">
         <f t="shared" si="7"/>
         <v>20.4625592966607</v>
       </c>
@@ -19242,35 +19239,35 @@
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <f t="shared" si="0"/>
         <v>23.7205030344186</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f t="shared" si="1"/>
         <v>-41.0839547243707</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <f t="shared" si="2"/>
         <v>-43.3387193625401</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <f t="shared" si="3"/>
         <v>19.2953104150981</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <f t="shared" si="4"/>
         <v>-41.0843903688056</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <f t="shared" si="5"/>
         <v>18.9757987851658</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <f t="shared" si="6"/>
         <v>-42.8428404356316</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <f t="shared" si="7"/>
         <v>14.5773486930415</v>
       </c>
@@ -19279,35 +19276,35 @@
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <f t="shared" si="0"/>
         <v>36.3415466367552</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f t="shared" si="1"/>
         <v>-30.4933695751805</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <f t="shared" si="2"/>
         <v>-46.0309070088867</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <f t="shared" si="3"/>
         <v>11.4764628670696</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <f t="shared" si="4"/>
         <v>-44.5791238835381</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <f t="shared" si="5"/>
         <v>12.9801155933507</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <f t="shared" si="6"/>
         <v>-45.6917083345937</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <f t="shared" si="7"/>
         <v>8.24921065963301</v>
       </c>
@@ -19316,35 +19313,35 @@
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <f t="shared" si="0"/>
         <v>44.5792430789022</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f t="shared" si="1"/>
         <v>-16.2248169947199</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <f t="shared" si="2"/>
         <v>-47.3244623139455</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <f t="shared" si="3"/>
         <v>3.30890717548068</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <f t="shared" si="4"/>
         <v>-46.7193369583897</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <f t="shared" si="5"/>
         <v>6.59003631763904</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <f t="shared" si="6"/>
         <v>-47.1522503204229</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <f t="shared" si="7"/>
         <v>1.67042336536092</v>
       </c>
@@ -19353,35 +19350,35 @@
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <f t="shared" si="0"/>
         <v>47.4399999948794</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <f t="shared" si="1"/>
         <v>0.000697027400387534</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <f t="shared" si="2"/>
         <v>-47.1800810709899</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <f t="shared" si="3"/>
         <v>-4.9591884552638</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <f t="shared" si="4"/>
         <v>-47.4399999987198</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="9">
         <f t="shared" si="5"/>
         <v>-0.000278810960160314</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="9">
         <f t="shared" si="6"/>
         <v>-47.1800883569272</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="9">
         <f t="shared" si="7"/>
         <v>-4.95911913436445</v>
       </c>
@@ -19435,34 +19432,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -19470,31 +19467,31 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <f>'L2'!C2*'L2'!D3-'L2'!D2*'L2'!C3</f>
         <v>57.9128384615722</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <f>'L2'!D2*'L2'!B3-'L2'!B2*'L2'!D3</f>
         <v>132.878717796743</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <f>'L2'!B2*'L2'!C3-'L2'!C2*'L2'!B3</f>
         <v>144</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>SQRT(B2*B2+C2*C2+D2*D2)</f>
         <v>204.319970883863</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <f>B2/E2*47.44</f>
         <v>13.4464832034389</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <f>C2/E2*47.44</f>
         <v>30.8524239946206</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <f>-D2/E2*47.44</f>
         <v>-33.4346171372695</v>
       </c>
@@ -19511,31 +19508,31 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <f>'L2'!C3*'L2'!D4-'L2'!D3*'L2'!C4</f>
         <v>11.0281290877654</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <f>'L2'!D3*'L2'!B4-'L2'!B3*'L2'!D4</f>
         <v>78.8221162995853</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <f>'L2'!B3*'L2'!C4-'L2'!C3*'L2'!B4</f>
         <v>96.75</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <f t="shared" ref="E3:E19" si="0">SQRT(B3*B3+C3*C3+D3*D3)</f>
         <v>125.280118730474</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <f t="shared" ref="F3:F19" si="1">B3/E3*47.44</f>
         <v>4.17603726134023</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <f t="shared" ref="G3:G19" si="2">C3/E3*47.44</f>
         <v>29.8476824187646</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <f t="shared" ref="H3:H19" si="3">-D3/E3*47.44</f>
         <v>-36.6364595317351</v>
       </c>
@@ -19552,31 +19549,31 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <f>'L2'!C4*'L2'!D5-'L2'!D4*'L2'!C5</f>
         <v>-14.2474094265501</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <f>'L2'!D4*'L2'!B5-'L2'!B4*'L2'!D5</f>
         <v>120.29057923472</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <f>'L2'!B4*'L2'!C5-'L2'!C4*'L2'!B5</f>
         <v>166</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <f t="shared" si="0"/>
         <v>205.496501498182</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <f t="shared" si="1"/>
         <v>-3.28909299315501</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <f t="shared" si="2"/>
         <v>27.7697432184539</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <f t="shared" si="3"/>
         <v>-38.3220149374157</v>
       </c>
@@ -19593,31 +19590,31 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <f>'L2'!C5*'L2'!D6-'L2'!D5*'L2'!C6</f>
         <v>-20.4608059545781</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f>'L2'!D5*'L2'!B6-'L2'!B5*'L2'!D6</f>
         <v>90.2812552661798</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f>'L2'!B5*'L2'!C6-'L2'!C5*'L2'!B6</f>
         <v>132</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <f t="shared" si="0"/>
         <v>161.224531733691</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <f t="shared" si="1"/>
         <v>-6.02055173643493</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <f t="shared" si="2"/>
         <v>26.5650810318499</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <f t="shared" si="3"/>
         <v>-38.8407392638214</v>
       </c>
@@ -19634,31 +19631,31 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <f>'L2'!C6*'L2'!D7-'L2'!D6*'L2'!C7</f>
         <v>-53.704323588982</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f>'L2'!D6*'L2'!B7-'L2'!B6*'L2'!D7</f>
         <v>97.905660694237</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f>'L2'!B6*'L2'!C7-'L2'!C6*'L2'!B7</f>
         <v>171.25</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <f t="shared" si="0"/>
         <v>204.441275842539</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <f t="shared" si="1"/>
         <v>-12.4619311856749</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <f t="shared" si="2"/>
         <v>22.7187221572219</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <f t="shared" si="3"/>
         <v>-39.7380615363465</v>
       </c>
@@ -19675,31 +19672,31 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <f>'L2'!C7*'L2'!D8-'L2'!D7*'L2'!C8</f>
         <v>-54.4501786179981</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f>'L2'!D7*'L2'!B8-'L2'!B7*'L2'!D8</f>
         <v>47.8084807590982</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>'L2'!B7*'L2'!C8-'L2'!C7*'L2'!B8</f>
         <v>113</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <f t="shared" si="0"/>
         <v>134.23662981476</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <f t="shared" si="1"/>
         <v>-19.243007495066</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <f t="shared" si="2"/>
         <v>16.8957931254784</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <f t="shared" si="3"/>
         <v>-39.9348524124714</v>
       </c>
@@ -19716,31 +19713,31 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <f>'L2'!C8*'L2'!D9-'L2'!D8*'L2'!C9</f>
         <v>-10.6037638411143</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f>'L2'!D8*'L2'!B9-'L2'!B8*'L2'!D9</f>
         <v>118.017226094512</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f>'L2'!B8*'L2'!C9-'L2'!C8*'L2'!B9</f>
         <v>141</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <f t="shared" si="0"/>
         <v>184.177917956093</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <f t="shared" si="1"/>
         <v>-2.73128593375882</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <f t="shared" si="2"/>
         <v>30.3985258822307</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f t="shared" si="3"/>
         <v>-36.3183603888639</v>
       </c>
@@ -19757,31 +19754,31 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <f>'L2'!C9*'L2'!D10-'L2'!D9*'L2'!C10</f>
         <v>-87.6824639864429</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f>'L2'!D9*'L2'!B10-'L2'!B9*'L2'!D10</f>
         <v>56.421325618726</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f>'L2'!B9*'L2'!C10-'L2'!C9*'L2'!B10</f>
         <v>175.25</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <f t="shared" si="0"/>
         <v>203.921904108676</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <f t="shared" si="1"/>
         <v>-20.3982799675117</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <f t="shared" si="2"/>
         <v>13.1257487960975</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f t="shared" si="3"/>
         <v>-40.7698233122092</v>
       </c>
@@ -19798,31 +19795,31 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <f>'L2'!C10*'L2'!D11-'L2'!D10*'L2'!C11</f>
         <v>-103.588855786178</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f>'L2'!D10*'L2'!B11-'L2'!B10*'L2'!D11</f>
         <v>8.13002960786366</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f>'L2'!B10*'L2'!C11-'L2'!C10*'L2'!B11</f>
         <v>152.75</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <f t="shared" si="0"/>
         <v>184.741199856757</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <f t="shared" si="1"/>
         <v>-26.6007545815804</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <f t="shared" si="2"/>
         <v>2.08772382606643</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <f t="shared" si="3"/>
         <v>-39.2249265763061</v>
       </c>
@@ -19839,31 +19836,31 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <f>'L2'!C11*'L2'!D12-'L2'!D11*'L2'!C12</f>
         <v>-59.4696524248319</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <f>'L2'!D11*'L2'!B12-'L2'!B11*'L2'!D12</f>
         <v>79.6707055826802</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <f>'L2'!B11*'L2'!C12-'L2'!C11*'L2'!B12</f>
         <v>144.5</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <f t="shared" si="0"/>
         <v>175.397579480369</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <f t="shared" si="1"/>
         <v>-16.0848303573641</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <f t="shared" si="2"/>
         <v>21.5486341604011</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <f t="shared" si="3"/>
         <v>-39.0830935085238</v>
       </c>
@@ -19880,31 +19877,31 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <f>'L2'!C12*'L2'!D13-'L2'!D12*'L2'!C13</f>
         <v>-79.9130128464018</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f>'L2'!D12*'L2'!B13-'L2'!B12*'L2'!D13</f>
         <v>48.052887983026</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <f>'L2'!B12*'L2'!C13-'L2'!C12*'L2'!B13</f>
         <v>155.25</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <f t="shared" si="0"/>
         <v>181.101441644451</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <f t="shared" si="1"/>
         <v>-20.9334243560367</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <f t="shared" si="2"/>
         <v>12.5875806686854</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <f t="shared" si="3"/>
         <v>-40.6681467199998</v>
       </c>
@@ -19921,31 +19918,31 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <f>'L2'!C13*'L2'!D14-'L2'!D13*'L2'!C14</f>
         <v>-78.7341823782315</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f>'L2'!D13*'L2'!B14-'L2'!B13*'L2'!D14</f>
         <v>-9.56518426089838</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <f>'L2'!B13*'L2'!C14-'L2'!C13*'L2'!B14</f>
         <v>123.25</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <f t="shared" si="0"/>
         <v>146.564411521739</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <f t="shared" si="1"/>
         <v>-25.4846969550265</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <f t="shared" si="2"/>
         <v>-3.09606088289526</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <f t="shared" si="3"/>
         <v>-39.8935863030622</v>
       </c>
@@ -19962,31 +19959,31 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <f>'L2'!C14*'L2'!D15-'L2'!D14*'L2'!C15</f>
         <v>-94.0729151439183</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f>'L2'!D14*'L2'!B15-'L2'!B14*'L2'!D15</f>
         <v>40.7577294254691</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <f>'L2'!B14*'L2'!C15-'L2'!C14*'L2'!B15</f>
         <v>167.5</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <f t="shared" si="0"/>
         <v>196.385223149795</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <f t="shared" si="1"/>
         <v>-22.7248212612383</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <f t="shared" si="2"/>
         <v>9.84568315748187</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <f t="shared" si="3"/>
         <v>-40.4623111278539</v>
       </c>
@@ -20003,31 +20000,31 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <f>'L2'!C15*'L2'!D16-'L2'!D15*'L2'!C16</f>
         <v>-94.8732947977217</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <f>'L2'!D15*'L2'!B16-'L2'!B15*'L2'!D16</f>
         <v>22.8218737313549</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <f>'L2'!B15*'L2'!C16-'L2'!C15*'L2'!B16</f>
         <v>164.75</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <f t="shared" si="0"/>
         <v>191.479352637263</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <f t="shared" si="1"/>
         <v>-23.50534949703</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <f t="shared" si="2"/>
         <v>5.65423725797986</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="9">
         <f t="shared" si="3"/>
         <v>-40.8176646325209</v>
       </c>
@@ -20044,31 +20041,31 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <f>'L2'!C16*'L2'!D17-'L2'!D16*'L2'!C17</f>
         <v>-81.9827870014967</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f>'L2'!D16*'L2'!B17-'L2'!B16*'L2'!D17</f>
         <v>49.6478955495716</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <f>'L2'!B16*'L2'!C17-'L2'!C16*'L2'!B17</f>
         <v>144.25</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <f t="shared" si="0"/>
         <v>173.188202245517</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <f t="shared" si="1"/>
         <v>-22.4568611771688</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <f t="shared" si="2"/>
         <v>13.5996340070136</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="9">
         <f t="shared" si="3"/>
         <v>-39.5131995786806</v>
       </c>
@@ -20085,31 +20082,31 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <f>'L2'!C17*'L2'!D18-'L2'!D17*'L2'!C18</f>
         <v>-79.4913998574598</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f>'L2'!D17*'L2'!B18-'L2'!B17*'L2'!D18</f>
         <v>-24.9460644272376</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <f>'L2'!B17*'L2'!C18-'L2'!C17*'L2'!B18</f>
         <v>146.25</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <f t="shared" si="0"/>
         <v>168.315926999516</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <f t="shared" si="1"/>
         <v>-22.404724713002</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <f t="shared" si="2"/>
         <v>-7.03107137586305</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <f t="shared" si="3"/>
         <v>-41.2206980271091</v>
       </c>
@@ -20126,31 +20123,31 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <f>'L2'!C18*'L2'!D19-'L2'!D18*'L2'!C19</f>
         <v>-82.4699051148075</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f>'L2'!D18*'L2'!B19-'L2'!B18*'L2'!D19</f>
         <v>-2.74266159973683</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <f>'L2'!B18*'L2'!C19-'L2'!C18*'L2'!B19</f>
         <v>146.25</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <f t="shared" si="0"/>
         <v>167.92221396318</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <f t="shared" si="1"/>
         <v>-23.2987179379634</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <f t="shared" si="2"/>
         <v>-0.774834152198856</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <f t="shared" si="3"/>
         <v>-41.3173447172469</v>
       </c>
@@ -20167,31 +20164,31 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <f>-('L2'!C19*'L2'!D2-'L2'!D19*'L2'!C2)</f>
         <v>-1092.82893312546</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f>-('L2'!D19*'L2'!B2-'L2'!B19*'L2'!D2)</f>
         <v>972.098461421014</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <f>-('L2'!B19*'L2'!C2-'L2'!C19*'L2'!B2)</f>
         <v>1543.5</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <f t="shared" si="0"/>
         <v>2126.41546875798</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <f t="shared" si="1"/>
         <v>-24.3808443595236</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <f t="shared" si="2"/>
         <v>21.687366221404</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <f t="shared" si="3"/>
         <v>-34.435246110568</v>
       </c>
@@ -20218,7 +20215,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>22</v>
       </c>
     </row>
@@ -20260,34 +20257,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -20295,31 +20292,31 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <f>'L2'!C2*'L2'!D4-'L2'!D2*'L2'!C4</f>
         <v>68.1366225707045</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <f>'L2'!D2*'L2'!B4-'L2'!B2*'L2'!D4</f>
         <v>212.953302932885</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <f>'L2'!B2*'L2'!C4-'L2'!C2*'L2'!B4</f>
         <v>238.75</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>SQRT(B2*B2+C2*C2+D2*D2)</f>
         <v>327.098259037506</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <f>B2/E2*47.44</f>
         <v>9.88205007347221</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <f>C2/E2*47.44</f>
         <v>30.8852291689442</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <f>-D2/E2*47.44</f>
         <v>-34.6265982378747</v>
       </c>
@@ -20336,39 +20333,39 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <f>'L2'!C3*'L2'!D5-'L2'!D3*'L2'!C5</f>
         <v>-3.88592536258534</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <f>'L2'!D3*'L2'!B5-'L2'!B3*'L2'!D5</f>
         <v>200.022821603777</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <f>'L2'!B3*'L2'!C5-'L2'!C3*'L2'!B5</f>
         <v>261</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <f t="shared" ref="E3:E19" si="0">SQRT(B3*B3+C3*C3+D3*D3)</f>
         <v>328.85442003759</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <f t="shared" ref="F3:F19" si="1">B3/E3*47.44</f>
         <v>-0.560577228002519</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <f t="shared" ref="G3:G19" si="2">C3/E3*47.44</f>
         <v>28.8549646247677</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <f t="shared" ref="H3:H19" si="3">-D3/E3*47.44</f>
         <v>-37.6514325049506</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <f t="shared" ref="I3:I19" si="4">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <f t="shared" ref="J3:J19" si="5">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
@@ -20377,39 +20374,39 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <f>'L2'!C4*'L2'!D6-'L2'!D4*'L2'!C6</f>
         <v>-34.9823358161882</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <f>'L2'!D4*'L2'!B6-'L2'!B4*'L2'!D6</f>
         <v>210.559170332872</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <f>'L2'!B4*'L2'!C6-'L2'!C4*'L2'!B6</f>
         <v>296.5</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <f t="shared" si="0"/>
         <v>365.337074535865</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <f t="shared" si="1"/>
         <v>-4.54255022769952</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <f t="shared" si="2"/>
         <v>27.3416735853641</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <f t="shared" si="3"/>
         <v>-38.5013210550005</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <f t="shared" si="4"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <f t="shared" si="5"/>
         <v>30.4809803249618</v>
       </c>
@@ -20418,39 +20415,39 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <f>'L2'!C5*'L2'!D7-'L2'!D5*'L2'!C7</f>
         <v>-75.06988248193</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f>'L2'!D5*'L2'!B7-'L2'!B5*'L2'!D7</f>
         <v>189.155064279935</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f>'L2'!B5*'L2'!C7-'L2'!C5*'L2'!B7</f>
         <v>301</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <f t="shared" si="0"/>
         <v>363.340233938656</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <f t="shared" si="1"/>
         <v>-9.801598865993</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <f t="shared" si="2"/>
         <v>24.6972820823227</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <f t="shared" si="3"/>
         <v>-39.3004645954262</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="9">
         <f t="shared" si="4"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <f t="shared" si="5"/>
         <v>41.0716467855168</v>
       </c>
@@ -20459,39 +20456,39 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <f>'L2'!C6*'L2'!D8-'L2'!D6*'L2'!C8</f>
         <v>-109.111728852548</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f>'L2'!D6*'L2'!B8-'L2'!B6*'L2'!D8</f>
         <v>146.788920273397</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f>'L2'!B6*'L2'!C8-'L2'!C6*'L2'!B8</f>
         <v>282.25</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <f t="shared" si="0"/>
         <v>336.329331144671</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <f t="shared" si="1"/>
         <v>-15.3904519690503</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <f t="shared" si="2"/>
         <v>20.7049035957395</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <f t="shared" si="3"/>
         <v>-39.8119900944363</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <f t="shared" si="4"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <f t="shared" si="5"/>
         <v>46.7134369557949</v>
       </c>
@@ -20500,39 +20497,39 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <f>'L2'!C7*'L2'!D9-'L2'!D7*'L2'!C9</f>
         <v>-61.922055689335</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f>'L2'!D7*'L2'!B9-'L2'!B7*'L2'!D9</f>
         <v>162.576267909339</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>'L2'!B7*'L2'!C9-'L2'!C7*'L2'!B9</f>
         <v>256</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <f t="shared" si="0"/>
         <v>309.517986340249</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <f t="shared" si="1"/>
         <v>-9.49082913285954</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <f t="shared" si="2"/>
         <v>24.918158200799</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <f t="shared" si="3"/>
         <v>-39.2372674156958</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <f t="shared" si="4"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <f t="shared" si="5"/>
         <v>46.7265504432231</v>
       </c>
@@ -20541,39 +20538,39 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <f>'L2'!C8*'L2'!D10-'L2'!D8*'L2'!C10</f>
         <v>-103.603603001749</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f>'L2'!D8*'L2'!B10-'L2'!B8*'L2'!D10</f>
         <v>178.43153864594</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f>'L2'!B8*'L2'!C10-'L2'!C8*'L2'!B10</f>
         <v>310.75</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <f t="shared" si="0"/>
         <v>373.010835014885</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <f t="shared" si="1"/>
         <v>-13.17644010584</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <f t="shared" si="2"/>
         <v>22.6931536533667</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f t="shared" si="3"/>
         <v>-39.5215865496554</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <f t="shared" si="4"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <f t="shared" si="5"/>
         <v>41.1094071546692</v>
       </c>
@@ -20582,39 +20579,39 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <f>'L2'!C9*'L2'!D11-'L2'!D9*'L2'!C11</f>
         <v>-193.745647385913</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f>'L2'!D9*'L2'!B11-'L2'!B9*'L2'!D11</f>
         <v>66.4427350621318</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f>'L2'!B9*'L2'!C11-'L2'!C9*'L2'!B11</f>
         <v>324.5</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <f t="shared" si="0"/>
         <v>383.734625651013</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <f t="shared" si="1"/>
         <v>-23.9522130597272</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <f t="shared" si="2"/>
         <v>8.21412283554039</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f t="shared" si="3"/>
         <v>-40.1169948473722</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <f t="shared" si="4"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <f t="shared" si="5"/>
         <v>30.5388376877712</v>
       </c>
@@ -20623,39 +20620,39 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <f>'L2'!C10*'L2'!D12-'L2'!D10*'L2'!C12</f>
         <v>-157.657309059872</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f>'L2'!D10*'L2'!B12-'L2'!B10*'L2'!D12</f>
         <v>84.892397186085</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f>'L2'!B10*'L2'!C12-'L2'!C10*'L2'!B12</f>
         <v>299.75</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <f t="shared" si="0"/>
         <v>349.159861238373</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <f t="shared" si="1"/>
         <v>-21.4207403888679</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <f t="shared" si="2"/>
         <v>11.534244824775</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <f t="shared" si="3"/>
         <v>-40.7267317313196</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <f t="shared" si="4"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <f t="shared" si="5"/>
         <v>16.2885294815216</v>
       </c>
@@ -20664,39 +20661,39 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <f>'L2'!C11*'L2'!D13-'L2'!D11*'L2'!C13</f>
         <v>-141.357368712002</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <f>'L2'!D11*'L2'!B13-'L2'!B11*'L2'!D13</f>
         <v>128.347601096585</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <f>'L2'!B11*'L2'!C13-'L2'!C11*'L2'!B13</f>
         <v>297.25</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <f t="shared" si="0"/>
         <v>353.288232037849</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <f t="shared" si="1"/>
         <v>-18.9816500057634</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <f t="shared" si="2"/>
         <v>17.2346816108205</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <f t="shared" si="3"/>
         <v>-39.9151138396516</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="9">
         <f t="shared" si="4"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="9">
         <f t="shared" si="5"/>
         <v>0.0755554543581351</v>
       </c>
@@ -20705,39 +20702,39 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <f>'L2'!C12*'L2'!D14-'L2'!D12*'L2'!C14</f>
         <v>-161.513643207402</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f>'L2'!D12*'L2'!B14-'L2'!B12*'L2'!D14</f>
         <v>39.4716580909189</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <f>'L2'!B12*'L2'!C14-'L2'!C12*'L2'!B14</f>
         <v>275.75</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <f t="shared" si="0"/>
         <v>321.998029861324</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <f t="shared" si="1"/>
         <v>-23.7958202323754</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <f t="shared" si="2"/>
         <v>5.81536309597809</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <f t="shared" si="3"/>
         <v>-40.6262734142624</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <f t="shared" si="4"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="9">
         <f t="shared" si="5"/>
         <v>-16.1465225320068</v>
       </c>
@@ -20746,39 +20743,39 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <f>'L2'!C13*'L2'!D15-'L2'!D13*'L2'!C15</f>
         <v>-169.363099197816</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f>'L2'!D13*'L2'!B15-'L2'!B13*'L2'!D15</f>
         <v>30.4344679753649</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <f>'L2'!B13*'L2'!C15-'L2'!C13*'L2'!B15</f>
         <v>291.75</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <f t="shared" si="0"/>
         <v>338.715483423526</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <f t="shared" si="1"/>
         <v>-23.7207503617366</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <f t="shared" si="2"/>
         <v>4.26260750219672</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <f t="shared" si="3"/>
         <v>-40.862082418281</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <f t="shared" si="4"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="9">
         <f t="shared" si="5"/>
         <v>-30.4230456457766</v>
       </c>
@@ -20787,39 +20784,39 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <f>'L2'!C14*'L2'!D16-'L2'!D14*'L2'!C16</f>
         <v>-189.528304235315</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f>'L2'!D14*'L2'!B16-'L2'!B14*'L2'!D16</f>
         <v>63.5192819464876</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <f>'L2'!B14*'L2'!C16-'L2'!C14*'L2'!B16</f>
         <v>330.25</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <f t="shared" si="0"/>
         <v>386.03204502387</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <f t="shared" si="1"/>
         <v>-23.2913895849433</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <f t="shared" si="2"/>
         <v>7.80597044826949</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <f t="shared" si="3"/>
         <v>-40.5848690593322</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <f t="shared" si="4"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="9">
         <f t="shared" si="5"/>
         <v>-41.0337822362874</v>
       </c>
@@ -20828,39 +20825,39 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <f>'L2'!C15*'L2'!D17-'L2'!D15*'L2'!C17</f>
         <v>-174.105825941859</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <f>'L2'!D15*'L2'!B17-'L2'!B15*'L2'!D17</f>
         <v>72.1426226733871</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <f>'L2'!B15*'L2'!C17-'L2'!C15*'L2'!B17</f>
         <v>309.25</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <f t="shared" si="0"/>
         <v>362.150464769951</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <f t="shared" si="1"/>
         <v>-22.8070406810841</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <f t="shared" si="2"/>
         <v>9.45034275131892</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="9">
         <f t="shared" si="3"/>
         <v>-40.5102890295042</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <f t="shared" si="4"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="9">
         <f t="shared" si="5"/>
         <v>-46.7002049776354</v>
       </c>
@@ -20869,39 +20866,39 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <f>'L2'!C16*'L2'!D18-'L2'!D16*'L2'!C18</f>
         <v>-165.834114361021</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f>'L2'!D16*'L2'!B18-'L2'!B16*'L2'!D18</f>
         <v>24.4042186991734</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <f>'L2'!B16*'L2'!C18-'L2'!C16*'L2'!B18</f>
         <v>287</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <f t="shared" si="0"/>
         <v>332.363534967694</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <f t="shared" si="1"/>
         <v>-23.6703776364984</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <f t="shared" si="2"/>
         <v>3.48334282580464</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="9">
         <f t="shared" si="3"/>
         <v>-40.9650234383367</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="9">
         <f t="shared" si="4"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="9">
         <f t="shared" si="5"/>
         <v>-46.7395454066571</v>
       </c>
@@ -20910,39 +20907,39 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <f>'L2'!C17*'L2'!D19-'L2'!D17*'L2'!C19</f>
         <v>-160.065892535773</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f>'L2'!D17*'L2'!B19-'L2'!B17*'L2'!D19</f>
         <v>-27.417952821761</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <f>'L2'!B17*'L2'!C19-'L2'!C17*'L2'!B19</f>
         <v>292.5</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <f t="shared" si="0"/>
         <v>334.558042931582</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <f t="shared" si="1"/>
         <v>-22.6971854430951</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <f t="shared" si="2"/>
         <v>-3.88783862574884</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <f t="shared" si="3"/>
         <v>-41.4762110586525</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <f t="shared" si="4"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <f t="shared" si="5"/>
         <v>-41.1470632479638</v>
       </c>
@@ -20951,39 +20948,39 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <f>-('L2'!C18*'L2'!D2-'L2'!D18*'L2'!C2)</f>
         <v>-997.719524035898</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f>-('L2'!D18*'L2'!B2-'L2'!B18*'L2'!D2)</f>
         <v>984.74301736936</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <f>-('L2'!B18*'L2'!C2-'L2'!C18*'L2'!B2)</f>
         <v>1528.25</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <f t="shared" si="0"/>
         <v>2073.81559483965</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <f t="shared" si="1"/>
         <v>-22.8235405009204</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <f t="shared" si="2"/>
         <v>22.5266937235153</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <f t="shared" si="3"/>
         <v>-34.9598007558651</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <f t="shared" si="4"/>
         <v>36.254663040877</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <f t="shared" si="5"/>
         <v>-30.5966175874469</v>
       </c>
@@ -20992,45 +20989,45 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <f>-('L2'!C19*'L2'!D3-'L2'!D19*'L2'!C3)</f>
         <v>-1078.35072351006</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f>-('L2'!D19*'L2'!B3-'L2'!B19*'L2'!D3)</f>
         <v>814.920121938485</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <f>-('L2'!B19*'L2'!C3-'L2'!C19*'L2'!B3)</f>
         <v>1579.5</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <f t="shared" si="0"/>
         <v>2078.88319489935</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <f t="shared" si="1"/>
         <v>-24.6079041135326</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <f t="shared" si="2"/>
         <v>18.596432295771</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <f t="shared" si="3"/>
         <v>-36.0441029990759</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <f t="shared" si="4"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <f t="shared" si="5"/>
         <v>-16.3594710714245</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>22</v>
       </c>
     </row>
@@ -21056,46 +21053,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>38</v>
       </c>
     </row>
@@ -21103,31 +21100,31 @@
       <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <f>'L2'!C2*'L2'!D4-'L2'!D2*'L2'!C4</f>
         <v>68.1366225707045</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <f>'L2'!D2*'L2'!B4-'L2'!B2*'L2'!D4</f>
         <v>212.953302932885</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <f>'L2'!B2*'L2'!C4-'L2'!C2*'L2'!B4</f>
         <v>238.75</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="9">
         <f>SQRT(B2*B2+C2*C2+D2*D2)</f>
         <v>327.098259037506</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <f>B2/E2*47.44</f>
         <v>9.88205007347221</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <f>C2/E2*47.44</f>
         <v>30.8852291689442</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <f>-D2/E2*47.44</f>
         <v>-34.6265982378747</v>
       </c>
@@ -21160,39 +21157,39 @@
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <f>'L2'!C3*'L2'!D5-'L2'!D3*'L2'!C5</f>
         <v>-3.88592536258534</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <f>'L2'!D3*'L2'!B5-'L2'!B3*'L2'!D5</f>
         <v>200.022821603777</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <f>'L2'!B3*'L2'!C5-'L2'!C3*'L2'!B5</f>
         <v>261</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <f t="shared" ref="E3:E19" si="0">SQRT(B3*B3+C3*C3+D3*D3)</f>
         <v>328.85442003759</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <f t="shared" ref="F3:F19" si="1">B3/E3*47.44</f>
         <v>-0.560577228002519</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <f t="shared" ref="G3:G19" si="2">C3/E3*47.44</f>
         <v>28.8549646247677</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <f t="shared" ref="H3:H19" si="3">-D3/E3*47.44</f>
         <v>-37.6514325049506</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <f t="shared" ref="I3:I19" si="4">COS(3.14/9*((A3-25)/20))*47.44</f>
         <v>44.5818885096479</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <f t="shared" ref="J3:J19" si="5">SIN(3.14/9*((A3-25)/20))*47.44</f>
         <v>16.2175465750319</v>
       </c>
@@ -21205,39 +21202,39 @@
       <c r="A4">
         <v>65</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <f>'L2'!C4*'L2'!D6-'L2'!D4*'L2'!C6</f>
         <v>-34.9823358161882</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <f>'L2'!D4*'L2'!B6-'L2'!B4*'L2'!D6</f>
         <v>210.559170332872</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <f>'L2'!B4*'L2'!C6-'L2'!C4*'L2'!B6</f>
         <v>296.5</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <f t="shared" si="0"/>
         <v>365.337074535865</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <f t="shared" si="1"/>
         <v>-4.54255022769952</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <f t="shared" si="2"/>
         <v>27.3416735853641</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <f t="shared" si="3"/>
         <v>-38.5013210550005</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <f t="shared" si="4"/>
         <v>36.3519385786961</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <f t="shared" si="5"/>
         <v>30.4809803249618</v>
       </c>
@@ -21250,39 +21247,39 @@
       <c r="A5">
         <v>85</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <f>'L2'!C5*'L2'!D7-'L2'!D5*'L2'!C7</f>
         <v>-75.06988248193</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f>'L2'!D5*'L2'!B7-'L2'!B5*'L2'!D7</f>
         <v>189.155064279935</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <f>'L2'!B5*'L2'!C7-'L2'!C5*'L2'!B7</f>
         <v>301</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <f t="shared" si="0"/>
         <v>363.340233938656</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <f t="shared" si="1"/>
         <v>-9.801598865993</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <f t="shared" si="2"/>
         <v>24.6972820823227</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <f t="shared" si="3"/>
         <v>-39.3004645954262</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="9">
         <f t="shared" si="4"/>
         <v>23.7418076465493</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="9">
         <f t="shared" si="5"/>
         <v>41.0716467855168</v>
       </c>
@@ -21295,39 +21292,39 @@
       <c r="A6">
         <v>105</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <f>'L2'!C6*'L2'!D8-'L2'!D6*'L2'!C8</f>
         <v>-109.111728852548</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <f>'L2'!D6*'L2'!B8-'L2'!B6*'L2'!D8</f>
         <v>146.788920273397</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <f>'L2'!B6*'L2'!C8-'L2'!C6*'L2'!B8</f>
         <v>282.25</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <f t="shared" si="0"/>
         <v>336.329331144671</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <f t="shared" si="1"/>
         <v>-15.3904519690503</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <f t="shared" si="2"/>
         <v>20.7049035957395</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <f t="shared" si="3"/>
         <v>-39.8119900944363</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <f t="shared" si="4"/>
         <v>8.27093753917763</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <f t="shared" si="5"/>
         <v>46.7134369557949</v>
       </c>
@@ -21340,39 +21337,39 @@
       <c r="A7">
         <v>125</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <f>'L2'!C7*'L2'!D9-'L2'!D7*'L2'!C9</f>
         <v>-61.922055689335</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f>'L2'!D7*'L2'!B9-'L2'!B7*'L2'!D9</f>
         <v>162.576267909339</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <f>'L2'!B7*'L2'!C9-'L2'!C7*'L2'!B9</f>
         <v>256</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <f t="shared" si="0"/>
         <v>309.517986340249</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <f t="shared" si="1"/>
         <v>-9.49082913285954</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <f t="shared" si="2"/>
         <v>24.918158200799</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <f t="shared" si="3"/>
         <v>-39.2372674156958</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <f t="shared" si="4"/>
         <v>-8.19652875776856</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <f t="shared" si="5"/>
         <v>46.7265504432231</v>
       </c>
@@ -21385,39 +21382,39 @@
       <c r="A8">
         <v>145</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <f>'L2'!C8*'L2'!D10-'L2'!D8*'L2'!C10</f>
         <v>-103.603603001749</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f>'L2'!D8*'L2'!B10-'L2'!B8*'L2'!D10</f>
         <v>178.43153864594</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <f>'L2'!B8*'L2'!C10-'L2'!C8*'L2'!B10</f>
         <v>310.75</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <f t="shared" si="0"/>
         <v>373.010835014885</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <f t="shared" si="1"/>
         <v>-13.17644010584</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <f t="shared" si="2"/>
         <v>22.6931536533667</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f t="shared" si="3"/>
         <v>-39.5215865496554</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <f t="shared" si="4"/>
         <v>-23.6763646574306</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <f t="shared" si="5"/>
         <v>41.1094071546692</v>
       </c>
@@ -21430,39 +21427,39 @@
       <c r="A9">
         <v>165</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <f>'L2'!C9*'L2'!D11-'L2'!D9*'L2'!C11</f>
         <v>-193.745647385913</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f>'L2'!D9*'L2'!B11-'L2'!B9*'L2'!D11</f>
         <v>66.4427350621318</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <f>'L2'!B9*'L2'!C11-'L2'!C9*'L2'!B11</f>
         <v>324.5</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <f t="shared" si="0"/>
         <v>383.734625651013</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <f t="shared" si="1"/>
         <v>-23.9522130597272</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <f t="shared" si="2"/>
         <v>8.21412283554039</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f t="shared" si="3"/>
         <v>-40.1169948473722</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <f t="shared" si="4"/>
         <v>-36.3033468523216</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <f t="shared" si="5"/>
         <v>30.5388376877712</v>
       </c>
@@ -21475,39 +21472,39 @@
       <c r="A10">
         <v>185</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <f>'L2'!C10*'L2'!D12-'L2'!D10*'L2'!C12</f>
         <v>-157.657309059872</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f>'L2'!D10*'L2'!B12-'L2'!B10*'L2'!D12</f>
         <v>84.892397186085</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <f>'L2'!B10*'L2'!C12-'L2'!C10*'L2'!B12</f>
         <v>299.75</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <f t="shared" si="0"/>
         <v>349.159861238373</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <f t="shared" si="1"/>
         <v>-21.4207403888679</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <f t="shared" si="2"/>
         <v>11.534244824775</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <f t="shared" si="3"/>
         <v>-40.7267317313196</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <f t="shared" si="4"/>
         <v>-44.5560030448154</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <f t="shared" si="5"/>
         <v>16.2885294815216</v>
       </c>
@@ -21520,39 +21517,39 @@
       <c r="A11">
         <v>205</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <f>'L2'!C11*'L2'!D13-'L2'!D11*'L2'!C13</f>
         <v>-141.357368712002</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <f>'L2'!D11*'L2'!B13-'L2'!B11*'L2'!D13</f>
         <v>128.347601096585</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <f>'L2'!B11*'L2'!C13-'L2'!C11*'L2'!B13</f>
         <v>297.25</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <f t="shared" si="0"/>
         <v>353.288232037849</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <f t="shared" si="1"/>
         <v>-18.9816500057634</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <f t="shared" si="2"/>
         <v>17.2346816108205</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <f t="shared" si="3"/>
         <v>-39.9151138396516</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="9">
         <f t="shared" si="4"/>
         <v>-47.4399398331545</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="9">
         <f t="shared" si="5"/>
         <v>0.0755554543581351</v>
       </c>
@@ -21565,39 +21562,39 @@
       <c r="A12">
         <v>225</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <f>'L2'!C12*'L2'!D14-'L2'!D12*'L2'!C14</f>
         <v>-161.513643207402</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f>'L2'!D12*'L2'!B14-'L2'!B12*'L2'!D14</f>
         <v>39.4716580909189</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <f>'L2'!B12*'L2'!C14-'L2'!C12*'L2'!B14</f>
         <v>275.75</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <f t="shared" si="0"/>
         <v>321.998029861324</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <f t="shared" si="1"/>
         <v>-23.7958202323754</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <f t="shared" si="2"/>
         <v>5.81536309597809</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <f t="shared" si="3"/>
         <v>-40.6262734142624</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <f t="shared" si="4"/>
         <v>-44.6076608905174</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="9">
         <f t="shared" si="5"/>
         <v>-16.1465225320068</v>
       </c>
@@ -21610,39 +21607,39 @@
       <c r="A13">
         <v>245</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <f>'L2'!C13*'L2'!D15-'L2'!D13*'L2'!C15</f>
         <v>-169.363099197816</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f>'L2'!D13*'L2'!B15-'L2'!B13*'L2'!D15</f>
         <v>30.4344679753649</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <f>'L2'!B13*'L2'!C15-'L2'!C13*'L2'!B15</f>
         <v>291.75</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <f t="shared" si="0"/>
         <v>338.715483423526</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <f t="shared" si="1"/>
         <v>-23.7207503617366</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <f t="shared" si="2"/>
         <v>4.26260750219672</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <f t="shared" si="3"/>
         <v>-40.862082418281</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <f t="shared" si="4"/>
         <v>-36.4004380967454</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="9">
         <f t="shared" si="5"/>
         <v>-30.4230456457766</v>
       </c>
@@ -21655,39 +21652,39 @@
       <c r="A14">
         <v>265</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <f>'L2'!C14*'L2'!D16-'L2'!D14*'L2'!C16</f>
         <v>-189.528304235315</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f>'L2'!D14*'L2'!B16-'L2'!B14*'L2'!D16</f>
         <v>63.5192819464876</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <f>'L2'!B14*'L2'!C16-'L2'!C14*'L2'!B16</f>
         <v>330.25</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <f t="shared" si="0"/>
         <v>386.03204502387</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <f t="shared" si="1"/>
         <v>-23.2913895849433</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <f t="shared" si="2"/>
         <v>7.80597044826949</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <f t="shared" si="3"/>
         <v>-40.5848690593322</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <f t="shared" si="4"/>
         <v>-23.8071904135063</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="9">
         <f t="shared" si="5"/>
         <v>-41.0337822362874</v>
       </c>
@@ -21700,39 +21697,39 @@
       <c r="A15">
         <v>285</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <f>'L2'!C15*'L2'!D17-'L2'!D15*'L2'!C17</f>
         <v>-174.105825941859</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <f>'L2'!D15*'L2'!B17-'L2'!B15*'L2'!D17</f>
         <v>72.1426226733871</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <f>'L2'!B15*'L2'!C17-'L2'!C15*'L2'!B17</f>
         <v>309.25</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <f t="shared" si="0"/>
         <v>362.150464769951</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <f t="shared" si="1"/>
         <v>-22.8070406810841</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <f t="shared" si="2"/>
         <v>9.45034275131892</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="9">
         <f t="shared" si="3"/>
         <v>-40.5102890295042</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <f t="shared" si="4"/>
         <v>-8.3453253409821</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="9">
         <f t="shared" si="5"/>
         <v>-46.7002049776354</v>
       </c>
@@ -21745,39 +21742,39 @@
       <c r="A16">
         <v>305</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <f>'L2'!C16*'L2'!D18-'L2'!D16*'L2'!C18</f>
         <v>-165.834114361021</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f>'L2'!D16*'L2'!B18-'L2'!B16*'L2'!D18</f>
         <v>24.4042186991734</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <f>'L2'!B16*'L2'!C18-'L2'!C16*'L2'!B18</f>
         <v>287</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <f t="shared" si="0"/>
         <v>332.363534967694</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <f t="shared" si="1"/>
         <v>-23.6703776364984</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <f t="shared" si="2"/>
         <v>3.48334282580464</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="9">
         <f t="shared" si="3"/>
         <v>-40.9650234383367</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="9">
         <f t="shared" si="4"/>
         <v>8.12209918549612</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="9">
         <f t="shared" si="5"/>
         <v>-46.7395454066571</v>
       </c>
@@ -21790,39 +21787,39 @@
       <c r="A17">
         <v>325</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <f>'L2'!C17*'L2'!D19-'L2'!D17*'L2'!C19</f>
         <v>-160.065892535773</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f>'L2'!D17*'L2'!B19-'L2'!B17*'L2'!D19</f>
         <v>-27.417952821761</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <f>'L2'!B17*'L2'!C19-'L2'!C17*'L2'!B19</f>
         <v>292.5</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <f t="shared" si="0"/>
         <v>334.558042931582</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <f t="shared" si="1"/>
         <v>-22.6971854430951</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <f t="shared" si="2"/>
         <v>-3.88783862574884</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <f t="shared" si="3"/>
         <v>-41.4762110586525</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <f t="shared" si="4"/>
         <v>23.6108616121494</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <f t="shared" si="5"/>
         <v>-41.1470632479638</v>
       </c>
@@ -21835,39 +21832,39 @@
       <c r="A18">
         <v>345</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <f>-('L2'!C18*'L2'!D2-'L2'!D18*'L2'!C2)</f>
         <v>-997.719524035898</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f>-('L2'!D18*'L2'!B2-'L2'!B18*'L2'!D2)</f>
         <v>984.74301736936</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <f>-('L2'!B18*'L2'!C2-'L2'!C18*'L2'!B2)</f>
         <v>1528.25</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <f t="shared" si="0"/>
         <v>2073.81559483965</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <f t="shared" si="1"/>
         <v>-22.8235405009204</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <f t="shared" si="2"/>
         <v>22.5266937235153</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <f t="shared" si="3"/>
         <v>-34.9598007558651</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <f t="shared" si="4"/>
         <v>36.254663040877</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <f t="shared" si="5"/>
         <v>-30.5966175874469</v>
       </c>
@@ -21880,39 +21877,39 @@
       <c r="A19">
         <v>365</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <f>-('L2'!C19*'L2'!D3-'L2'!D19*'L2'!C3)</f>
         <v>-1078.35072351006</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f>-('L2'!D19*'L2'!B3-'L2'!B19*'L2'!D3)</f>
         <v>814.920121938485</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <f>-('L2'!B19*'L2'!C3-'L2'!C19*'L2'!B3)</f>
         <v>1579.5</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <f t="shared" si="0"/>
         <v>2078.88319489935</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <f t="shared" si="1"/>
         <v>-24.6079041135326</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <f t="shared" si="2"/>
         <v>18.596432295771</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <f t="shared" si="3"/>
         <v>-36.0441029990759</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <f t="shared" si="4"/>
         <v>44.5300045616798</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <f t="shared" si="5"/>
         <v>-16.3594710714245</v>
       </c>
@@ -21922,17 +21919,17 @@
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="J25" s="9" t="s">
+      <c r="J25" s="8" t="s">
         <v>40</v>
       </c>
     </row>
@@ -21951,33 +21948,33 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10" style="1"/>
-    <col min="2" max="2" width="12.8888888888889" style="8"/>
-    <col min="3" max="3" width="10" style="8"/>
-    <col min="4" max="4" width="23.8055555555556" style="8" customWidth="1"/>
-    <col min="5" max="6" width="10" style="8"/>
-    <col min="7" max="7" width="22.4814814814815" style="8" customWidth="1"/>
+    <col min="2" max="2" width="12.8888888888889" style="7"/>
+    <col min="3" max="3" width="10" style="7"/>
+    <col min="4" max="4" width="23.8055555555556" style="7" customWidth="1"/>
+    <col min="5" max="6" width="10" style="7"/>
+    <col min="7" max="7" width="22.4814814814815" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>46</v>
       </c>
     </row>
@@ -21985,23 +21982,23 @@
       <c r="A2" s="1">
         <v>25</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>884.558479532164</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>517.09649122807</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <f>SQRT((B2-'L1'!B2)^2+(C2-'L1'!C2)^2)</f>
         <v>0.905399335451789</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>884.556923951664</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>517.094107579775</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <f>SQRT((E2-'L1'!B2)^2+(F2-'L1'!C2)^2)</f>
         <v>0.907679135649873</v>
       </c>
@@ -22010,23 +22007,23 @@
       <c r="A3" s="1">
         <v>45</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>880.819573443412</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>519.536119711042</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <f>SQRT((B3-'L1'!B3)^2+(C3-'L1'!C3)^2)</f>
         <v>0.497733527910207</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>880.818200872383</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>519.534016491958</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <f>SQRT((E3-'L1'!B3)^2+(F3-'L1'!C3)^2)</f>
         <v>0.500191515891052</v>
       </c>
@@ -22035,23 +22032,23 @@
       <c r="A4" s="1">
         <v>65</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>877.080667354661</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>521.975748194014</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <f>SQRT((B4-'L1'!B4)^2+(C4-'L1'!C4)^2)</f>
         <v>0.420033352890632</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>877.079477793103</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>521.973925404142</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <f>SQRT((E4-'L1'!B4)^2+(F4-'L1'!C4)^2)</f>
         <v>0.42132981266777</v>
       </c>
@@ -22060,23 +22057,23 @@
       <c r="A5" s="1">
         <v>85</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>873.34176126591</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>524.415376676986</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <f>SQRT((B5-'L1'!B5)^2+(C5-'L1'!C5)^2)</f>
         <v>0.352082191646118</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>873.340754713822</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>524.413834316325</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <f>SQRT((E5-'L1'!B5)^2+(F5-'L1'!C5)^2)</f>
         <v>0.351480155961998</v>
       </c>
@@ -22085,23 +22082,23 @@
       <c r="A6" s="1">
         <v>105</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>869.602855177159</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>526.855005159959</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f>SQRT((B6-'L1'!B6)^2+(C6-'L1'!C6)^2)</f>
         <v>0.369604993291355</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>869.602031634541</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>526.853743228508</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <f>SQRT((E6-'L1'!B6)^2+(F6-'L1'!C6)^2)</f>
         <v>0.368163993571367</v>
       </c>
@@ -22110,23 +22107,23 @@
       <c r="A7" s="1">
         <v>125</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>865.863949088407</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>529.294633642931</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <f>SQRT((B7-'L1'!B7)^2+(C7-'L1'!C7)^2)</f>
         <v>0.468260528444466</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>865.86330855526</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>529.293652140692</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <f>SQRT((E7-'L1'!B7)^2+(F7-'L1'!C7)^2)</f>
         <v>0.467145251563241</v>
       </c>
@@ -22135,23 +22132,23 @@
       <c r="A8" s="1">
         <v>145</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>862.125042999656</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>531.734262125903</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <f>SQRT((B8-'L1'!B8)^2+(C8-'L1'!C8)^2)</f>
         <v>0.442121584792659</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>862.12458547598</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>531.733561052875</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <f>SQRT((E8-'L1'!B8)^2+(F8-'L1'!C8)^2)</f>
         <v>0.442138926430636</v>
       </c>
@@ -22160,23 +22157,23 @@
       <c r="A9" s="1">
         <v>165</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>858.386136910905</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>534.173890608875</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <f>SQRT((B9-'L1'!B9)^2+(C9-'L1'!C9)^2)</f>
         <v>0.683442284167582</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>858.385862396699</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>534.173469965058</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <f>SQRT((E9-'L1'!B9)^2+(F9-'L1'!C9)^2)</f>
         <v>0.68307333890473</v>
       </c>
@@ -22185,23 +22182,23 @@
       <c r="A10" s="1">
         <v>185</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>854.647230822153</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>536.613519091847</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <f>SQRT((B10-'L1'!B10)^2+(C10-'L1'!C10)^2)</f>
         <v>0.185912611744398</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>854.647139317418</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>536.613378877242</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <f>SQRT((E10-'L1'!B10)^2+(F10-'L1'!C10)^2)</f>
         <v>0.185754538396484</v>
       </c>
@@ -22210,23 +22207,23 @@
       <c r="A11" s="1">
         <v>205</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>850.908324733402</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>539.053147574819</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <f>SQRT((B11-'L1'!B11)^2+(C11-'L1'!C11)^2)</f>
         <v>0.10596706665264</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>850.908416238137</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <v>539.053287789425</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <f>SQRT((E11-'L1'!B11)^2+(F11-'L1'!C11)^2)</f>
         <v>0.105958359456848</v>
       </c>
@@ -22235,23 +22232,23 @@
       <c r="A12" s="1">
         <v>225</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>847.169418644651</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>541.492776057791</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <f>SQRT((B12-'L1'!B12)^2+(C12-'L1'!C12)^2)</f>
         <v>0.521086288715682</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>847.169693158857</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <v>541.493196701608</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <f>SQRT((E12-'L1'!B12)^2+(F12-'L1'!C12)^2)</f>
         <v>0.521573345407762</v>
       </c>
@@ -22260,23 +22257,23 @@
       <c r="A13" s="1">
         <v>245</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>843.430512555899</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>543.932404540764</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <f>SQRT((B13-'L1'!B13)^2+(C13-'L1'!C13)^2)</f>
         <v>0.610175997282732</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>843.430970079576</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <v>543.933105613792</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <f>SQRT((E13-'L1'!B13)^2+(F13-'L1'!C13)^2)</f>
         <v>0.610995648256113</v>
       </c>
@@ -22285,23 +22282,23 @@
       <c r="A14" s="1">
         <v>265</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>839.691606467148</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>546.372033023736</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <f>SQRT((B14-'L1'!B14)^2+(C14-'L1'!C14)^2)</f>
         <v>0.483234044594445</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>839.692247000295</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <v>546.373014525975</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="7">
         <f>SQRT((E14-'L1'!B14)^2+(F14-'L1'!C14)^2)</f>
         <v>0.483582201301707</v>
       </c>
@@ -22310,23 +22307,23 @@
       <c r="A15" s="1">
         <v>285</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>835.952700378397</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>548.811661506708</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <f>SQRT((B15-'L1'!B15)^2+(C15-'L1'!C15)^2)</f>
         <v>0.194187132064121</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>835.953523921014</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <v>548.812923438158</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="7">
         <f>SQRT((E15-'L1'!B15)^2+(F15-'L1'!C15)^2)</f>
         <v>0.192763237959237</v>
       </c>
@@ -22335,23 +22332,23 @@
       <c r="A16" s="1">
         <v>305</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>832.213794289646</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>551.25128998968</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <f>SQRT((B16-'L1'!B16)^2+(C16-'L1'!C16)^2)</f>
         <v>0.327970528429927</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <v>832.214800841734</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="7">
         <v>551.252832350341</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <f>SQRT((E16-'L1'!B16)^2+(F16-'L1'!C16)^2)</f>
         <v>0.327461827771715</v>
       </c>
@@ -22360,23 +22357,23 @@
       <c r="A17" s="1">
         <v>325</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>828.474888200894</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>553.690918472652</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <f>SQRT((B17-'L1'!B17)^2+(C17-'L1'!C17)^2)</f>
         <v>0.310099972592874</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>828.476077762453</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="7">
         <v>553.692741262525</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="7">
         <f>SQRT((E17-'L1'!B17)^2+(F17-'L1'!C17)^2)</f>
         <v>0.308188587076107</v>
       </c>
@@ -22385,23 +22382,23 @@
       <c r="A18" s="1">
         <v>345</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>824.735982112143</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>556.130546955624</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <f>SQRT((B18-'L1'!B18)^2+(C18-'L1'!C18)^2)</f>
         <v>0.454093599500305</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>824.737354683172</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="7">
         <v>556.132650174708</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="7">
         <f>SQRT((E18-'L1'!B18)^2+(F18-'L1'!C18)^2)</f>
         <v>0.451584384798342</v>
       </c>
@@ -22410,23 +22407,23 @@
       <c r="A19" s="1">
         <v>365</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>820.997076023392</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>558.570175438596</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <f>SQRT((B19-'L1'!B19)^2+(C19-'L1'!C19)^2)</f>
         <v>0.429834506787568</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <v>820.998631603891</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="7">
         <v>558.572559086891</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="7">
         <f>SQRT((E19-'L1'!B19)^2+(F19-'L1'!C19)^2)</f>
         <v>0.427443103473829</v>
       </c>
@@ -22647,14 +22644,12 @@
       <c r="AD2" s="1">
         <v>0.516945017795346</v>
       </c>
-      <c r="AE2" s="1"/>
       <c r="AF2" s="1">
         <v>-1.43072870375292</v>
       </c>
       <c r="AG2" s="1">
         <v>0.558975031626432</v>
       </c>
-      <c r="AH2" s="1"/>
       <c r="AI2" s="1">
         <v>-1.43600040891281</v>
       </c>
@@ -22748,14 +22743,12 @@
       <c r="AD3" s="1">
         <v>0.516920275841465</v>
       </c>
-      <c r="AE3" s="1"/>
       <c r="AF3" s="1">
         <v>-1.33130679796324</v>
       </c>
       <c r="AG3" s="1">
         <v>0.558932405093849</v>
       </c>
-      <c r="AH3" s="1"/>
       <c r="AI3" s="1">
         <v>-1.33672544208382</v>
       </c>
@@ -22846,14 +22839,12 @@
       <c r="AD4" s="1">
         <v>0.516895533887583</v>
       </c>
-      <c r="AE4" s="1"/>
       <c r="AF4" s="1">
         <v>-1.23188489217356</v>
       </c>
       <c r="AG4" s="1">
         <v>0.558889778561266</v>
       </c>
-      <c r="AH4" s="1"/>
       <c r="AI4" s="1">
         <v>-1.23745047525483</v>
       </c>
@@ -22935,14 +22926,12 @@
       <c r="AD5" s="1">
         <v>0.516870791933701</v>
       </c>
-      <c r="AE5" s="1"/>
       <c r="AF5" s="1">
         <v>-1.13246298638389</v>
       </c>
       <c r="AG5" s="1">
         <v>0.558847152028682</v>
       </c>
-      <c r="AH5" s="1"/>
       <c r="AI5" s="1">
         <v>-1.13817550842583</v>
       </c>
@@ -23020,14 +23009,12 @@
       <c r="AD6" s="1">
         <v>0.516846049979819</v>
       </c>
-      <c r="AE6" s="1"/>
       <c r="AF6" s="1">
         <v>-1.03304108059421</v>
       </c>
       <c r="AG6" s="1">
         <v>0.558804525496099</v>
       </c>
-      <c r="AH6" s="1"/>
       <c r="AI6" s="1">
         <v>-1.03890054159684</v>
       </c>
@@ -23109,14 +23096,12 @@
       <c r="AD7" s="1">
         <v>0.516821308025937</v>
       </c>
-      <c r="AE7" s="1"/>
       <c r="AF7" s="1">
         <v>-0.933619174804533</v>
       </c>
       <c r="AG7" s="1">
         <v>0.558761898963516</v>
       </c>
-      <c r="AH7" s="1"/>
       <c r="AI7" s="1">
         <v>-0.939625574767844</v>
       </c>
@@ -23198,14 +23183,12 @@
       <c r="AD8" s="1">
         <v>0.516796566072056</v>
       </c>
-      <c r="AE8" s="1"/>
       <c r="AF8" s="1">
         <v>-0.834197269014856</v>
       </c>
       <c r="AG8" s="1">
         <v>0.558719272430932</v>
       </c>
-      <c r="AH8" s="1"/>
       <c r="AI8" s="1">
         <v>-0.84035060793885</v>
       </c>
@@ -23287,14 +23270,12 @@
       <c r="AD9" s="1">
         <v>0.516771824118174</v>
       </c>
-      <c r="AE9" s="1"/>
       <c r="AF9" s="1">
         <v>-0.734775363225179</v>
       </c>
       <c r="AG9" s="1">
         <v>0.558676645898349</v>
       </c>
-      <c r="AH9" s="1"/>
       <c r="AI9" s="1">
         <v>-0.741075641109856</v>
       </c>
@@ -23376,14 +23357,12 @@
       <c r="AD10" s="1">
         <v>0.516747082164292</v>
       </c>
-      <c r="AE10" s="1"/>
       <c r="AF10" s="1">
         <v>-0.635353457435502</v>
       </c>
       <c r="AG10" s="1">
         <v>0.558634019365766</v>
       </c>
-      <c r="AH10" s="1"/>
       <c r="AI10" s="1">
         <v>-0.641800674280862</v>
       </c>
@@ -23461,14 +23440,12 @@
       <c r="AD11" s="1">
         <v>0.51672234021041</v>
       </c>
-      <c r="AE11" s="1"/>
       <c r="AF11" s="1">
         <v>-0.535931551645825</v>
       </c>
       <c r="AG11" s="1">
         <v>0.558591392833183</v>
       </c>
-      <c r="AH11" s="1"/>
       <c r="AI11" s="1">
         <v>-0.542525707451868</v>
       </c>
@@ -23546,14 +23523,12 @@
       <c r="AD12" s="1">
         <v>0.516697598256529</v>
       </c>
-      <c r="AE12" s="1"/>
       <c r="AF12" s="1">
         <v>-0.436509645856148</v>
       </c>
       <c r="AG12" s="1">
         <v>0.558548766300599</v>
       </c>
-      <c r="AH12" s="1"/>
       <c r="AI12" s="1">
         <v>-0.443250740622874</v>
       </c>
@@ -23631,14 +23606,12 @@
       <c r="AD13" s="1">
         <v>0.516672856302647</v>
       </c>
-      <c r="AE13" s="1"/>
       <c r="AF13" s="1">
         <v>-0.337087740066471</v>
       </c>
       <c r="AG13" s="1">
         <v>0.558506139768016</v>
       </c>
-      <c r="AH13" s="1"/>
       <c r="AI13" s="1">
         <v>-0.34397577379388</v>
       </c>
@@ -23716,14 +23689,12 @@
       <c r="AD14" s="1">
         <v>0.516648114348765</v>
       </c>
-      <c r="AE14" s="1"/>
       <c r="AF14" s="1">
         <v>-0.237665834276794</v>
       </c>
       <c r="AG14" s="1">
         <v>0.558463513235433</v>
       </c>
-      <c r="AH14" s="1"/>
       <c r="AI14" s="1">
         <v>-0.244700806964886</v>
       </c>
@@ -23801,14 +23772,12 @@
       <c r="AD15" s="1">
         <v>0.516623372394883</v>
       </c>
-      <c r="AE15" s="1"/>
       <c r="AF15" s="1">
         <v>-0.138243928487116</v>
       </c>
       <c r="AG15" s="1">
         <v>0.55842088670285</v>
       </c>
-      <c r="AH15" s="1"/>
       <c r="AI15" s="1">
         <v>-0.145425840135892</v>
       </c>
@@ -23886,14 +23855,12 @@
       <c r="AD16" s="1">
         <v>0.516598630441001</v>
       </c>
-      <c r="AE16" s="1"/>
       <c r="AF16" s="1">
         <v>-0.0388220226974394</v>
       </c>
       <c r="AG16" s="1">
         <v>0.558378260170266</v>
       </c>
-      <c r="AH16" s="1"/>
       <c r="AI16" s="1">
         <v>-0.046150873306898</v>
       </c>
@@ -23971,14 +23938,12 @@
       <c r="AD17" s="1">
         <v>0.516573888487119</v>
       </c>
-      <c r="AE17" s="1"/>
       <c r="AF17" s="1">
         <v>0.0605998830922378</v>
       </c>
       <c r="AG17" s="1">
         <v>0.558335633637683</v>
       </c>
-      <c r="AH17" s="1"/>
       <c r="AI17" s="1">
         <v>0.053124093522096</v>
       </c>
@@ -24056,14 +24021,12 @@
       <c r="AD18" s="1">
         <v>0.516549146533238</v>
       </c>
-      <c r="AE18" s="1"/>
       <c r="AF18" s="1">
         <v>0.160021788881915</v>
       </c>
       <c r="AG18" s="1">
         <v>0.5582930071051</v>
       </c>
-      <c r="AH18" s="1"/>
       <c r="AI18" s="1">
         <v>0.15239906035109</v>
       </c>
@@ -24141,14 +24104,12 @@
       <c r="AD19" s="1">
         <v>0.516524404579356</v>
       </c>
-      <c r="AE19" s="1"/>
       <c r="AF19" s="1">
         <v>0.259443694671592</v>
       </c>
       <c r="AG19" s="1">
         <v>0.558250380572516</v>
       </c>
-      <c r="AH19" s="1"/>
       <c r="AI19" s="1">
         <v>0.251674027180084</v>
       </c>
@@ -24163,38 +24124,38 @@
       <c r="AC20" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="AD20" s="6"/>
-      <c r="AE20" s="6"/>
-      <c r="AF20" s="6"/>
-      <c r="AG20" s="6"/>
-      <c r="AH20" s="6"/>
-      <c r="AI20" s="6"/>
-      <c r="AJ20" s="6"/>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="5"/>
+      <c r="AF20" s="5"/>
+      <c r="AG20" s="5"/>
+      <c r="AH20" s="5"/>
+      <c r="AI20" s="5"/>
+      <c r="AJ20" s="5"/>
     </row>
     <row r="21" spans="2:36">
       <c r="G21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AC21" s="6">
+      <c r="AC21" s="5">
         <v>0.0933771920465001</v>
       </c>
-      <c r="AD21" s="6">
+      <c r="AD21" s="5">
         <f>AC21*180/3.1415926</f>
         <v>5.3501190983102</v>
       </c>
-      <c r="AE21" s="6"/>
-      <c r="AF21" s="7">
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="6">
         <v>0.0994219057896799</v>
       </c>
-      <c r="AG21" s="6">
+      <c r="AG21" s="5">
         <f>AF21*180/3.1415926</f>
         <v>5.696455690067</v>
       </c>
-      <c r="AH21" s="6"/>
-      <c r="AI21" s="7">
+      <c r="AH21" s="5"/>
+      <c r="AI21" s="6">
         <v>0.0992749668289901</v>
       </c>
-      <c r="AJ21" s="6">
+      <c r="AJ21" s="5">
         <f>AI21*180/3.1415926</f>
         <v>5.68803670762982</v>
       </c>
